--- a/templates/Plantilla_Preventivo.xlsx
+++ b/templates/Plantilla_Preventivo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAC1CCA1-EFCF-4CFC-B6AB-BE97950DDC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B69B62F4-BBC8-42A2-9EA0-5A0D88709856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1537,20 +1537,329 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1561,12 +1870,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1579,18 +1882,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1620,297 +1911,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -2265,19 +2265,19 @@
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="33" customHeight="1"/>
-    <row r="3" spans="1:12" ht="33" customHeight="1"/>
+    <row r="1" spans="1:12" ht="30" customHeight="1"/>
+    <row r="3" spans="1:12" ht="30" customHeight="1"/>
     <row r="5" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="148" t="s">
+      <c r="D5" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="149"/>
-      <c r="F5" s="150"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="47"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2291,7 +2291,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="113"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="160"/>
       <c r="F6" s="160"/>
       <c r="G6" s="2"/>
@@ -2320,69 +2320,69 @@
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="114"/>
-      <c r="D8" s="151"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="151"/>
-      <c r="H8" s="151"/>
-      <c r="I8" s="151"/>
-      <c r="J8" s="151"/>
-      <c r="K8" s="151"/>
-      <c r="L8" s="152"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="50"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="115"/>
-      <c r="F9" s="115"/>
-      <c r="G9" s="115"/>
-      <c r="H9" s="115"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="115"/>
-      <c r="L9" s="116"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="52"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="70"/>
-      <c r="K10" s="70"/>
-      <c r="L10" s="71"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="54"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="105"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
-      <c r="L11" s="106"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="56"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -2413,9 +2413,9 @@
       <c r="I13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70"/>
-      <c r="L13" s="71"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="54"/>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="1"/>
@@ -2464,44 +2464,44 @@
       <c r="B17" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="139" t="s">
+      <c r="C17" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="141"/>
-      <c r="E17" s="45" t="s">
+      <c r="D17" s="94"/>
+      <c r="E17" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="50"/>
+      <c r="F17" s="89"/>
       <c r="G17" s="4"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="45" t="s">
+      <c r="I17" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="50"/>
+      <c r="J17" s="89"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="52"/>
+      <c r="L17" s="40"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="1"/>
       <c r="B18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="140"/>
-      <c r="D18" s="141"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="51"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="91"/>
       <c r="G18" s="4"/>
       <c r="H18" s="8"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="51"/>
+      <c r="I18" s="147"/>
+      <c r="J18" s="91"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="52"/>
+      <c r="L18" s="40"/>
     </row>
     <row r="19" spans="1:12" ht="15" hidden="1" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="9"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="141"/>
+      <c r="D19" s="94"/>
       <c r="E19" s="9"/>
       <c r="F19" s="11"/>
       <c r="G19" s="4"/>
@@ -2516,42 +2516,42 @@
       <c r="B20" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="48"/>
-      <c r="D20" s="135"/>
-      <c r="E20" s="45" t="s">
+      <c r="C20" s="149"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="50"/>
+      <c r="F20" s="89"/>
       <c r="G20" s="4"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="45" t="s">
+      <c r="I20" s="146" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="50"/>
+      <c r="J20" s="89"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="52"/>
+      <c r="L20" s="40"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="1"/>
       <c r="B21" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="135"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="49"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="90"/>
       <c r="G21" s="4"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="49"/>
+      <c r="I21" s="148"/>
+      <c r="J21" s="90"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="52"/>
+      <c r="L21" s="40"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="52"/>
+      <c r="D22" s="40"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -2577,19 +2577,19 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="1"/>
-      <c r="B24" s="136" t="s">
+      <c r="B24" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="137"/>
-      <c r="D24" s="137"/>
-      <c r="E24" s="137"/>
-      <c r="F24" s="137"/>
-      <c r="G24" s="137"/>
-      <c r="H24" s="137"/>
-      <c r="I24" s="137"/>
-      <c r="J24" s="137"/>
-      <c r="K24" s="137"/>
-      <c r="L24" s="138"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="87"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="88"/>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="1"/>
@@ -2610,54 +2610,54 @@
       <c r="B26" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="102"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="103"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="81"/>
       <c r="F26" s="13"/>
-      <c r="G26" s="104" t="s">
+      <c r="G26" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="105"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="108"/>
-      <c r="L26" s="109"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="95"/>
+      <c r="K26" s="96"/>
+      <c r="L26" s="97"/>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="1"/>
       <c r="B27" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="102"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="103"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="81"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="104" t="s">
+      <c r="G27" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="105"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="133"/>
-      <c r="L27" s="134"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="83"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="85"/>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="1"/>
       <c r="B28" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="102"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="103"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="81"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="104" t="s">
+      <c r="G28" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="105"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="102"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="114"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="80"/>
+      <c r="L28" s="48"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="1"/>
@@ -2678,74 +2678,74 @@
       <c r="B30" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="119"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="119"/>
-      <c r="L30" s="120"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="77"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="1"/>
-      <c r="B31" s="156"/>
-      <c r="C31" s="157"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="157"/>
-      <c r="F31" s="157"/>
-      <c r="G31" s="157"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="157"/>
-      <c r="J31" s="157"/>
-      <c r="K31" s="157"/>
-      <c r="L31" s="158"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="75"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="1"/>
-      <c r="B32" s="159" t="s">
+      <c r="B32" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="119"/>
-      <c r="H32" s="119"/>
-      <c r="I32" s="119"/>
-      <c r="J32" s="119"/>
-      <c r="K32" s="119"/>
-      <c r="L32" s="120"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="76"/>
+      <c r="K32" s="76"/>
+      <c r="L32" s="77"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="1"/>
-      <c r="B33" s="77"/>
-      <c r="C33" s="121"/>
-      <c r="D33" s="121"/>
-      <c r="E33" s="121"/>
-      <c r="F33" s="121"/>
-      <c r="G33" s="121"/>
-      <c r="H33" s="121"/>
-      <c r="I33" s="121"/>
-      <c r="J33" s="121"/>
-      <c r="K33" s="121"/>
-      <c r="L33" s="121"/>
+      <c r="B33" s="98"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="99"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="99"/>
+      <c r="K33" s="99"/>
+      <c r="L33" s="99"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="1"/>
-      <c r="B34" s="156"/>
-      <c r="C34" s="157"/>
-      <c r="D34" s="157"/>
-      <c r="E34" s="157"/>
-      <c r="F34" s="157"/>
-      <c r="G34" s="157"/>
-      <c r="H34" s="157"/>
-      <c r="I34" s="157"/>
-      <c r="J34" s="157"/>
-      <c r="K34" s="157"/>
-      <c r="L34" s="158"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="74"/>
+      <c r="L34" s="75"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="1"/>
@@ -2763,159 +2763,159 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="1"/>
-      <c r="B36" s="122" t="s">
+      <c r="B36" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="123"/>
-      <c r="D36" s="123"/>
-      <c r="E36" s="123"/>
-      <c r="F36" s="123"/>
-      <c r="G36" s="123"/>
-      <c r="H36" s="123"/>
-      <c r="I36" s="123"/>
-      <c r="J36" s="123"/>
-      <c r="K36" s="123"/>
-      <c r="L36" s="124"/>
+      <c r="C36" s="101"/>
+      <c r="D36" s="101"/>
+      <c r="E36" s="101"/>
+      <c r="F36" s="101"/>
+      <c r="G36" s="101"/>
+      <c r="H36" s="101"/>
+      <c r="I36" s="101"/>
+      <c r="J36" s="101"/>
+      <c r="K36" s="101"/>
+      <c r="L36" s="102"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="125"/>
-      <c r="C37" s="126"/>
-      <c r="D37" s="126"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="126"/>
-      <c r="G37" s="126"/>
-      <c r="H37" s="126"/>
-      <c r="I37" s="126"/>
-      <c r="J37" s="126"/>
-      <c r="K37" s="126"/>
-      <c r="L37" s="127"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="104"/>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="104"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="104"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="105"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="1"/>
-      <c r="B38" s="125"/>
-      <c r="C38" s="126"/>
-      <c r="D38" s="126"/>
-      <c r="E38" s="126"/>
-      <c r="F38" s="126"/>
-      <c r="G38" s="126"/>
-      <c r="H38" s="126"/>
-      <c r="I38" s="126"/>
-      <c r="J38" s="126"/>
-      <c r="K38" s="126"/>
-      <c r="L38" s="127"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="104"/>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="104"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="104"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="104"/>
+      <c r="K38" s="104"/>
+      <c r="L38" s="105"/>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="1"/>
-      <c r="B39" s="125"/>
-      <c r="C39" s="126"/>
-      <c r="D39" s="126"/>
-      <c r="E39" s="126"/>
-      <c r="F39" s="126"/>
-      <c r="G39" s="126"/>
-      <c r="H39" s="126"/>
-      <c r="I39" s="126"/>
-      <c r="J39" s="126"/>
-      <c r="K39" s="126"/>
-      <c r="L39" s="127"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="104"/>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="104"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="104"/>
+      <c r="L39" s="105"/>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="1"/>
-      <c r="B40" s="125"/>
-      <c r="C40" s="126"/>
-      <c r="D40" s="126"/>
-      <c r="E40" s="126"/>
-      <c r="F40" s="126"/>
-      <c r="G40" s="126"/>
-      <c r="H40" s="126"/>
-      <c r="I40" s="126"/>
-      <c r="J40" s="126"/>
-      <c r="K40" s="126"/>
-      <c r="L40" s="127"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="104"/>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="104"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="104"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="104"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="105"/>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="1"/>
-      <c r="B41" s="125"/>
-      <c r="C41" s="126"/>
-      <c r="D41" s="126"/>
-      <c r="E41" s="126"/>
-      <c r="F41" s="126"/>
-      <c r="G41" s="126"/>
-      <c r="H41" s="126"/>
-      <c r="I41" s="126"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="126"/>
-      <c r="L41" s="127"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="104"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="104"/>
+      <c r="I41" s="104"/>
+      <c r="J41" s="104"/>
+      <c r="K41" s="104"/>
+      <c r="L41" s="105"/>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="1"/>
-      <c r="B42" s="125"/>
-      <c r="C42" s="126"/>
-      <c r="D42" s="126"/>
-      <c r="E42" s="126"/>
-      <c r="F42" s="126"/>
-      <c r="G42" s="126"/>
-      <c r="H42" s="126"/>
-      <c r="I42" s="126"/>
-      <c r="J42" s="126"/>
-      <c r="K42" s="126"/>
-      <c r="L42" s="127"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="105"/>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="1"/>
-      <c r="B43" s="125"/>
-      <c r="C43" s="126"/>
-      <c r="D43" s="126"/>
-      <c r="E43" s="126"/>
-      <c r="F43" s="126"/>
-      <c r="G43" s="126"/>
-      <c r="H43" s="126"/>
-      <c r="I43" s="126"/>
-      <c r="J43" s="126"/>
-      <c r="K43" s="126"/>
-      <c r="L43" s="127"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="104"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="105"/>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="1"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="126"/>
-      <c r="D44" s="126"/>
-      <c r="E44" s="126"/>
-      <c r="F44" s="126"/>
-      <c r="G44" s="126"/>
-      <c r="H44" s="126"/>
-      <c r="I44" s="126"/>
-      <c r="J44" s="126"/>
-      <c r="K44" s="126"/>
-      <c r="L44" s="127"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="104"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="104"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="104"/>
+      <c r="K44" s="104"/>
+      <c r="L44" s="105"/>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="1"/>
-      <c r="B45" s="125"/>
-      <c r="C45" s="126"/>
-      <c r="D45" s="126"/>
-      <c r="E45" s="126"/>
-      <c r="F45" s="126"/>
-      <c r="G45" s="126"/>
-      <c r="H45" s="126"/>
-      <c r="I45" s="126"/>
-      <c r="J45" s="126"/>
-      <c r="K45" s="126"/>
-      <c r="L45" s="127"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="104"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="104"/>
+      <c r="K45" s="104"/>
+      <c r="L45" s="105"/>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="1"/>
-      <c r="B46" s="128"/>
-      <c r="C46" s="129"/>
-      <c r="D46" s="129"/>
-      <c r="E46" s="129"/>
-      <c r="F46" s="129"/>
-      <c r="G46" s="129"/>
-      <c r="H46" s="129"/>
-      <c r="I46" s="129"/>
-      <c r="J46" s="129"/>
-      <c r="K46" s="129"/>
-      <c r="L46" s="130"/>
+      <c r="B46" s="106"/>
+      <c r="C46" s="107"/>
+      <c r="D46" s="107"/>
+      <c r="E46" s="107"/>
+      <c r="F46" s="107"/>
+      <c r="G46" s="107"/>
+      <c r="H46" s="107"/>
+      <c r="I46" s="107"/>
+      <c r="J46" s="107"/>
+      <c r="K46" s="107"/>
+      <c r="L46" s="108"/>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="1"/>
@@ -2938,14 +2938,14 @@
       </c>
       <c r="C48" s="18"/>
       <c r="D48" s="18"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="64"/>
-      <c r="I48" s="64"/>
-      <c r="J48" s="64"/>
-      <c r="K48" s="64"/>
-      <c r="L48" s="65"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
+      <c r="L48" s="68"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="1"/>
@@ -3005,131 +3005,131 @@
     </row>
     <row r="53" spans="1:12" ht="30" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="131" t="s">
+      <c r="B53" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="131"/>
-      <c r="D53" s="131"/>
-      <c r="E53" s="131"/>
-      <c r="F53" s="131"/>
-      <c r="G53" s="131"/>
-      <c r="H53" s="131"/>
-      <c r="I53" s="131"/>
-      <c r="J53" s="131"/>
-      <c r="K53" s="131"/>
-      <c r="L53" s="131"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+      <c r="L53" s="43"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="1"/>
-      <c r="B54" s="63" t="s">
+      <c r="B54" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="65"/>
-      <c r="D54" s="63" t="s">
+      <c r="C54" s="68"/>
+      <c r="D54" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E54" s="64"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="63" t="s">
+      <c r="E54" s="69"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="H54" s="64"/>
-      <c r="I54" s="64"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="63" t="s">
+      <c r="H54" s="69"/>
+      <c r="I54" s="69"/>
+      <c r="J54" s="68"/>
+      <c r="K54" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="L54" s="65"/>
+      <c r="L54" s="68"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="1"/>
-      <c r="B55" s="63"/>
-      <c r="C55" s="65"/>
-      <c r="D55" s="63"/>
-      <c r="E55" s="64"/>
-      <c r="F55" s="65"/>
-      <c r="G55" s="153"/>
-      <c r="H55" s="154"/>
-      <c r="I55" s="154"/>
-      <c r="J55" s="155"/>
-      <c r="K55" s="153"/>
-      <c r="L55" s="155"/>
+      <c r="B55" s="67"/>
+      <c r="C55" s="68"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="68"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="70"/>
+      <c r="L55" s="72"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="1"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="153"/>
-      <c r="H56" s="154"/>
-      <c r="I56" s="154"/>
-      <c r="J56" s="155"/>
-      <c r="K56" s="153"/>
-      <c r="L56" s="155"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="68"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="69"/>
+      <c r="F56" s="68"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="70"/>
+      <c r="L56" s="72"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="1"/>
-      <c r="B57" s="79"/>
-      <c r="C57" s="80"/>
-      <c r="D57" s="79"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="80"/>
-      <c r="G57" s="88"/>
-      <c r="H57" s="89"/>
-      <c r="I57" s="89"/>
-      <c r="J57" s="90"/>
-      <c r="K57" s="88"/>
-      <c r="L57" s="90"/>
+      <c r="B57" s="58"/>
+      <c r="C57" s="59"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="64"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="109"/>
+      <c r="H57" s="110"/>
+      <c r="I57" s="110"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="109"/>
+      <c r="L57" s="111"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="B58" s="81"/>
-      <c r="C58" s="82"/>
-      <c r="D58" s="81"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="91"/>
-      <c r="H58" s="92"/>
-      <c r="I58" s="92"/>
-      <c r="J58" s="93"/>
-      <c r="K58" s="91"/>
-      <c r="L58" s="93"/>
+      <c r="B58" s="60"/>
+      <c r="C58" s="61"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="65"/>
+      <c r="F58" s="61"/>
+      <c r="G58" s="112"/>
+      <c r="H58" s="113"/>
+      <c r="I58" s="113"/>
+      <c r="J58" s="114"/>
+      <c r="K58" s="112"/>
+      <c r="L58" s="114"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="B59" s="83"/>
-      <c r="C59" s="84"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="87"/>
-      <c r="F59" s="84"/>
-      <c r="G59" s="94"/>
-      <c r="H59" s="95"/>
-      <c r="I59" s="95"/>
-      <c r="J59" s="96"/>
-      <c r="K59" s="111"/>
-      <c r="L59" s="112"/>
+      <c r="B59" s="62"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="62"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="115"/>
+      <c r="H59" s="116"/>
+      <c r="I59" s="116"/>
+      <c r="J59" s="117"/>
+      <c r="K59" s="118"/>
+      <c r="L59" s="119"/>
     </row>
     <row r="60" spans="1:12" s="34" customFormat="1" ht="90.75" customHeight="1">
       <c r="A60" s="33"/>
-      <c r="B60" s="37" t="s">
+      <c r="B60" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="C60" s="39"/>
-      <c r="D60" s="37" t="s">
+      <c r="C60" s="124"/>
+      <c r="D60" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="E60" s="38"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="37" t="s">
+      <c r="E60" s="125"/>
+      <c r="F60" s="124"/>
+      <c r="G60" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
-      <c r="J60" s="39"/>
-      <c r="K60" s="117" t="s">
+      <c r="H60" s="125"/>
+      <c r="I60" s="125"/>
+      <c r="J60" s="124"/>
+      <c r="K60" s="126" t="s">
         <v>35</v>
       </c>
-      <c r="L60" s="118"/>
+      <c r="L60" s="127"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1"/>
     <row r="62" spans="1:12" ht="27" customHeight="1"/>
@@ -3144,11 +3144,11 @@
         <v>0</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="43" t="s">
+      <c r="D68" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="E68" s="72"/>
-      <c r="F68" s="44"/>
+      <c r="E68" s="121"/>
+      <c r="F68" s="122"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -3162,9 +3162,9 @@
         <v>2</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="113"/>
-      <c r="E69" s="113"/>
-      <c r="F69" s="113"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="35"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -3191,69 +3191,69 @@
       <c r="B71" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="67"/>
-      <c r="D71" s="67"/>
-      <c r="E71" s="67"/>
-      <c r="F71" s="67"/>
-      <c r="G71" s="67"/>
-      <c r="H71" s="67"/>
-      <c r="I71" s="67"/>
-      <c r="J71" s="67"/>
-      <c r="K71" s="67"/>
-      <c r="L71" s="114"/>
+      <c r="C71" s="80"/>
+      <c r="D71" s="80"/>
+      <c r="E71" s="80"/>
+      <c r="F71" s="80"/>
+      <c r="G71" s="80"/>
+      <c r="H71" s="80"/>
+      <c r="I71" s="80"/>
+      <c r="J71" s="80"/>
+      <c r="K71" s="80"/>
+      <c r="L71" s="48"/>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="1"/>
       <c r="B72" s="4"/>
-      <c r="C72" s="115"/>
-      <c r="D72" s="115"/>
-      <c r="E72" s="115"/>
-      <c r="F72" s="115"/>
-      <c r="G72" s="115"/>
-      <c r="H72" s="115"/>
-      <c r="I72" s="115"/>
-      <c r="J72" s="115"/>
-      <c r="K72" s="115"/>
-      <c r="L72" s="116"/>
+      <c r="C72" s="51"/>
+      <c r="D72" s="51"/>
+      <c r="E72" s="51"/>
+      <c r="F72" s="51"/>
+      <c r="G72" s="51"/>
+      <c r="H72" s="51"/>
+      <c r="I72" s="51"/>
+      <c r="J72" s="51"/>
+      <c r="K72" s="51"/>
+      <c r="L72" s="52"/>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="1"/>
       <c r="B73" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C73" s="70"/>
-      <c r="D73" s="70"/>
-      <c r="E73" s="70"/>
-      <c r="F73" s="70"/>
-      <c r="G73" s="70"/>
-      <c r="H73" s="70"/>
-      <c r="I73" s="70"/>
-      <c r="J73" s="70"/>
-      <c r="K73" s="70"/>
-      <c r="L73" s="71"/>
+      <c r="C73" s="53"/>
+      <c r="D73" s="53"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53"/>
+      <c r="H73" s="53"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="54"/>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="1"/>
       <c r="B74" s="4"/>
-      <c r="C74" s="105"/>
-      <c r="D74" s="105"/>
-      <c r="E74" s="105"/>
-      <c r="F74" s="105"/>
-      <c r="G74" s="105"/>
-      <c r="H74" s="105"/>
-      <c r="I74" s="105"/>
-      <c r="J74" s="105"/>
-      <c r="K74" s="105"/>
-      <c r="L74" s="106"/>
+      <c r="C74" s="55"/>
+      <c r="D74" s="55"/>
+      <c r="E74" s="55"/>
+      <c r="F74" s="55"/>
+      <c r="G74" s="55"/>
+      <c r="H74" s="55"/>
+      <c r="I74" s="55"/>
+      <c r="J74" s="55"/>
+      <c r="K74" s="55"/>
+      <c r="L74" s="56"/>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="1"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="110"/>
-      <c r="D75" s="110"/>
-      <c r="E75" s="110"/>
-      <c r="F75" s="110"/>
-      <c r="G75" s="110"/>
+      <c r="C75" s="57"/>
+      <c r="D75" s="57"/>
+      <c r="E75" s="57"/>
+      <c r="F75" s="57"/>
+      <c r="G75" s="57"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3274,9 +3274,9 @@
       <c r="I76" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J76" s="70"/>
-      <c r="K76" s="70"/>
-      <c r="L76" s="71"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="53"/>
+      <c r="L76" s="54"/>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="1"/>
@@ -3322,19 +3322,19 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="1"/>
-      <c r="B80" s="63" t="s">
+      <c r="B80" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C80" s="64"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="64"/>
-      <c r="H80" s="64"/>
-      <c r="I80" s="64"/>
-      <c r="J80" s="64"/>
-      <c r="K80" s="64"/>
-      <c r="L80" s="65"/>
+      <c r="C80" s="69"/>
+      <c r="D80" s="69"/>
+      <c r="E80" s="69"/>
+      <c r="F80" s="69"/>
+      <c r="G80" s="69"/>
+      <c r="H80" s="69"/>
+      <c r="I80" s="69"/>
+      <c r="J80" s="69"/>
+      <c r="K80" s="69"/>
+      <c r="L80" s="68"/>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="1"/>
@@ -3355,54 +3355,54 @@
       <c r="B82" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C82" s="102"/>
-      <c r="D82" s="67"/>
-      <c r="E82" s="103"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="80"/>
+      <c r="E82" s="81"/>
       <c r="F82" s="13"/>
-      <c r="G82" s="104" t="s">
+      <c r="G82" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="H82" s="105"/>
-      <c r="I82" s="106"/>
-      <c r="J82" s="107"/>
-      <c r="K82" s="108"/>
-      <c r="L82" s="109"/>
+      <c r="H82" s="55"/>
+      <c r="I82" s="56"/>
+      <c r="J82" s="95"/>
+      <c r="K82" s="96"/>
+      <c r="L82" s="97"/>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="1"/>
       <c r="B83" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="102"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="103"/>
+      <c r="C83" s="79"/>
+      <c r="D83" s="80"/>
+      <c r="E83" s="81"/>
       <c r="F83" s="2"/>
-      <c r="G83" s="104" t="s">
+      <c r="G83" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="H83" s="105"/>
-      <c r="I83" s="106"/>
-      <c r="J83" s="107"/>
-      <c r="K83" s="108"/>
-      <c r="L83" s="109"/>
+      <c r="H83" s="55"/>
+      <c r="I83" s="56"/>
+      <c r="J83" s="95"/>
+      <c r="K83" s="96"/>
+      <c r="L83" s="97"/>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="1"/>
       <c r="B84" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="102"/>
-      <c r="D84" s="67"/>
-      <c r="E84" s="103"/>
+      <c r="C84" s="79"/>
+      <c r="D84" s="80"/>
+      <c r="E84" s="81"/>
       <c r="F84" s="8"/>
-      <c r="G84" s="104" t="s">
+      <c r="G84" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="H84" s="105"/>
-      <c r="I84" s="106"/>
-      <c r="J84" s="107"/>
-      <c r="K84" s="108"/>
-      <c r="L84" s="109"/>
+      <c r="H84" s="55"/>
+      <c r="I84" s="56"/>
+      <c r="J84" s="95"/>
+      <c r="K84" s="96"/>
+      <c r="L84" s="97"/>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="1"/>
@@ -3434,525 +3434,525 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="1"/>
-      <c r="B87" s="63" t="s">
+      <c r="B87" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="64"/>
-      <c r="D87" s="64"/>
-      <c r="E87" s="64"/>
-      <c r="F87" s="64"/>
-      <c r="G87" s="64"/>
-      <c r="H87" s="64"/>
-      <c r="I87" s="64"/>
-      <c r="J87" s="65"/>
-      <c r="K87" s="63" t="s">
+      <c r="C87" s="69"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="69"/>
+      <c r="F87" s="69"/>
+      <c r="G87" s="69"/>
+      <c r="H87" s="69"/>
+      <c r="I87" s="69"/>
+      <c r="J87" s="68"/>
+      <c r="K87" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="L87" s="65"/>
+      <c r="L87" s="68"/>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="1"/>
-      <c r="B88" s="97" t="s">
+      <c r="B88" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="C88" s="98"/>
-      <c r="D88" s="98"/>
-      <c r="E88" s="98"/>
-      <c r="F88" s="98"/>
-      <c r="G88" s="98"/>
-      <c r="H88" s="98"/>
-      <c r="I88" s="98"/>
-      <c r="J88" s="99"/>
-      <c r="K88" s="100"/>
-      <c r="L88" s="101"/>
+      <c r="C88" s="129"/>
+      <c r="D88" s="129"/>
+      <c r="E88" s="129"/>
+      <c r="F88" s="129"/>
+      <c r="G88" s="129"/>
+      <c r="H88" s="129"/>
+      <c r="I88" s="129"/>
+      <c r="J88" s="130"/>
+      <c r="K88" s="131"/>
+      <c r="L88" s="132"/>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" s="1"/>
-      <c r="B89" s="74" t="s">
+      <c r="B89" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="C89" s="75"/>
-      <c r="D89" s="75"/>
-      <c r="E89" s="75"/>
-      <c r="F89" s="75"/>
-      <c r="G89" s="75"/>
-      <c r="H89" s="75"/>
-      <c r="I89" s="75"/>
-      <c r="J89" s="76"/>
-      <c r="K89" s="77"/>
-      <c r="L89" s="78"/>
+      <c r="C89" s="134"/>
+      <c r="D89" s="134"/>
+      <c r="E89" s="134"/>
+      <c r="F89" s="134"/>
+      <c r="G89" s="134"/>
+      <c r="H89" s="134"/>
+      <c r="I89" s="134"/>
+      <c r="J89" s="135"/>
+      <c r="K89" s="98"/>
+      <c r="L89" s="136"/>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="1"/>
-      <c r="B90" s="74" t="s">
+      <c r="B90" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="C90" s="75"/>
-      <c r="D90" s="75"/>
-      <c r="E90" s="75"/>
-      <c r="F90" s="75"/>
-      <c r="G90" s="75"/>
-      <c r="H90" s="75"/>
-      <c r="I90" s="75"/>
-      <c r="J90" s="76"/>
-      <c r="K90" s="77"/>
-      <c r="L90" s="78"/>
+      <c r="C90" s="134"/>
+      <c r="D90" s="134"/>
+      <c r="E90" s="134"/>
+      <c r="F90" s="134"/>
+      <c r="G90" s="134"/>
+      <c r="H90" s="134"/>
+      <c r="I90" s="134"/>
+      <c r="J90" s="135"/>
+      <c r="K90" s="98"/>
+      <c r="L90" s="136"/>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="1"/>
-      <c r="B91" s="74" t="s">
+      <c r="B91" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="C91" s="75"/>
-      <c r="D91" s="75"/>
-      <c r="E91" s="75"/>
-      <c r="F91" s="75"/>
-      <c r="G91" s="75"/>
-      <c r="H91" s="75"/>
-      <c r="I91" s="75"/>
-      <c r="J91" s="76"/>
-      <c r="K91" s="77"/>
-      <c r="L91" s="78"/>
+      <c r="C91" s="134"/>
+      <c r="D91" s="134"/>
+      <c r="E91" s="134"/>
+      <c r="F91" s="134"/>
+      <c r="G91" s="134"/>
+      <c r="H91" s="134"/>
+      <c r="I91" s="134"/>
+      <c r="J91" s="135"/>
+      <c r="K91" s="98"/>
+      <c r="L91" s="136"/>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="1"/>
-      <c r="B92" s="74" t="s">
+      <c r="B92" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="C92" s="75"/>
-      <c r="D92" s="75"/>
-      <c r="E92" s="75"/>
-      <c r="F92" s="75"/>
-      <c r="G92" s="75"/>
-      <c r="H92" s="75"/>
-      <c r="I92" s="75"/>
-      <c r="J92" s="76"/>
-      <c r="K92" s="77"/>
-      <c r="L92" s="78"/>
+      <c r="C92" s="134"/>
+      <c r="D92" s="134"/>
+      <c r="E92" s="134"/>
+      <c r="F92" s="134"/>
+      <c r="G92" s="134"/>
+      <c r="H92" s="134"/>
+      <c r="I92" s="134"/>
+      <c r="J92" s="135"/>
+      <c r="K92" s="98"/>
+      <c r="L92" s="136"/>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="1"/>
-      <c r="B93" s="74" t="s">
+      <c r="B93" s="133" t="s">
         <v>43</v>
       </c>
-      <c r="C93" s="75"/>
-      <c r="D93" s="75"/>
-      <c r="E93" s="75"/>
-      <c r="F93" s="75"/>
-      <c r="G93" s="75"/>
-      <c r="H93" s="75"/>
-      <c r="I93" s="75"/>
-      <c r="J93" s="76"/>
-      <c r="K93" s="77"/>
-      <c r="L93" s="78"/>
+      <c r="C93" s="134"/>
+      <c r="D93" s="134"/>
+      <c r="E93" s="134"/>
+      <c r="F93" s="134"/>
+      <c r="G93" s="134"/>
+      <c r="H93" s="134"/>
+      <c r="I93" s="134"/>
+      <c r="J93" s="135"/>
+      <c r="K93" s="98"/>
+      <c r="L93" s="136"/>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" s="1"/>
-      <c r="B94" s="74" t="s">
+      <c r="B94" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="C94" s="75"/>
-      <c r="D94" s="75"/>
-      <c r="E94" s="75"/>
-      <c r="F94" s="75"/>
-      <c r="G94" s="75"/>
-      <c r="H94" s="75"/>
-      <c r="I94" s="75"/>
-      <c r="J94" s="76"/>
-      <c r="K94" s="77"/>
-      <c r="L94" s="78"/>
+      <c r="C94" s="134"/>
+      <c r="D94" s="134"/>
+      <c r="E94" s="134"/>
+      <c r="F94" s="134"/>
+      <c r="G94" s="134"/>
+      <c r="H94" s="134"/>
+      <c r="I94" s="134"/>
+      <c r="J94" s="135"/>
+      <c r="K94" s="98"/>
+      <c r="L94" s="136"/>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="1"/>
-      <c r="B95" s="74" t="s">
+      <c r="B95" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="C95" s="75"/>
-      <c r="D95" s="75"/>
-      <c r="E95" s="75"/>
-      <c r="F95" s="75"/>
-      <c r="G95" s="75"/>
-      <c r="H95" s="75"/>
-      <c r="I95" s="75"/>
-      <c r="J95" s="76"/>
-      <c r="K95" s="77"/>
-      <c r="L95" s="78"/>
+      <c r="C95" s="134"/>
+      <c r="D95" s="134"/>
+      <c r="E95" s="134"/>
+      <c r="F95" s="134"/>
+      <c r="G95" s="134"/>
+      <c r="H95" s="134"/>
+      <c r="I95" s="134"/>
+      <c r="J95" s="135"/>
+      <c r="K95" s="98"/>
+      <c r="L95" s="136"/>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="1"/>
-      <c r="B96" s="74" t="s">
+      <c r="B96" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="C96" s="75"/>
-      <c r="D96" s="75"/>
-      <c r="E96" s="75"/>
-      <c r="F96" s="75"/>
-      <c r="G96" s="75"/>
-      <c r="H96" s="75"/>
-      <c r="I96" s="75"/>
-      <c r="J96" s="76"/>
-      <c r="K96" s="77"/>
-      <c r="L96" s="78"/>
+      <c r="C96" s="134"/>
+      <c r="D96" s="134"/>
+      <c r="E96" s="134"/>
+      <c r="F96" s="134"/>
+      <c r="G96" s="134"/>
+      <c r="H96" s="134"/>
+      <c r="I96" s="134"/>
+      <c r="J96" s="135"/>
+      <c r="K96" s="98"/>
+      <c r="L96" s="136"/>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="1"/>
-      <c r="B97" s="74" t="s">
+      <c r="B97" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="C97" s="75"/>
-      <c r="D97" s="75"/>
-      <c r="E97" s="75"/>
-      <c r="F97" s="75"/>
-      <c r="G97" s="75"/>
-      <c r="H97" s="75"/>
-      <c r="I97" s="75"/>
-      <c r="J97" s="76"/>
-      <c r="K97" s="77"/>
-      <c r="L97" s="78"/>
+      <c r="C97" s="134"/>
+      <c r="D97" s="134"/>
+      <c r="E97" s="134"/>
+      <c r="F97" s="134"/>
+      <c r="G97" s="134"/>
+      <c r="H97" s="134"/>
+      <c r="I97" s="134"/>
+      <c r="J97" s="135"/>
+      <c r="K97" s="98"/>
+      <c r="L97" s="136"/>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="1"/>
-      <c r="B98" s="74" t="s">
+      <c r="B98" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="C98" s="75"/>
-      <c r="D98" s="75"/>
-      <c r="E98" s="75"/>
-      <c r="F98" s="75"/>
-      <c r="G98" s="75"/>
-      <c r="H98" s="75"/>
-      <c r="I98" s="75"/>
-      <c r="J98" s="76"/>
-      <c r="K98" s="77"/>
-      <c r="L98" s="78"/>
+      <c r="C98" s="134"/>
+      <c r="D98" s="134"/>
+      <c r="E98" s="134"/>
+      <c r="F98" s="134"/>
+      <c r="G98" s="134"/>
+      <c r="H98" s="134"/>
+      <c r="I98" s="134"/>
+      <c r="J98" s="135"/>
+      <c r="K98" s="98"/>
+      <c r="L98" s="136"/>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="1"/>
-      <c r="B99" s="74" t="s">
+      <c r="B99" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
-      <c r="E99" s="75"/>
-      <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
-      <c r="H99" s="75"/>
-      <c r="I99" s="75"/>
-      <c r="J99" s="76"/>
-      <c r="K99" s="77"/>
-      <c r="L99" s="78"/>
+      <c r="C99" s="134"/>
+      <c r="D99" s="134"/>
+      <c r="E99" s="134"/>
+      <c r="F99" s="134"/>
+      <c r="G99" s="134"/>
+      <c r="H99" s="134"/>
+      <c r="I99" s="134"/>
+      <c r="J99" s="135"/>
+      <c r="K99" s="98"/>
+      <c r="L99" s="136"/>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="1"/>
-      <c r="B100" s="74" t="s">
+      <c r="B100" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="C100" s="75"/>
-      <c r="D100" s="75"/>
-      <c r="E100" s="75"/>
-      <c r="F100" s="75"/>
-      <c r="G100" s="75"/>
-      <c r="H100" s="75"/>
-      <c r="I100" s="75"/>
-      <c r="J100" s="76"/>
-      <c r="K100" s="77"/>
-      <c r="L100" s="78"/>
+      <c r="C100" s="134"/>
+      <c r="D100" s="134"/>
+      <c r="E100" s="134"/>
+      <c r="F100" s="134"/>
+      <c r="G100" s="134"/>
+      <c r="H100" s="134"/>
+      <c r="I100" s="134"/>
+      <c r="J100" s="135"/>
+      <c r="K100" s="98"/>
+      <c r="L100" s="136"/>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" s="1"/>
-      <c r="B101" s="74" t="s">
+      <c r="B101" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="C101" s="75"/>
-      <c r="D101" s="75"/>
-      <c r="E101" s="75"/>
-      <c r="F101" s="75"/>
-      <c r="G101" s="75"/>
-      <c r="H101" s="75"/>
-      <c r="I101" s="75"/>
-      <c r="J101" s="76"/>
-      <c r="K101" s="77"/>
-      <c r="L101" s="78"/>
+      <c r="C101" s="134"/>
+      <c r="D101" s="134"/>
+      <c r="E101" s="134"/>
+      <c r="F101" s="134"/>
+      <c r="G101" s="134"/>
+      <c r="H101" s="134"/>
+      <c r="I101" s="134"/>
+      <c r="J101" s="135"/>
+      <c r="K101" s="98"/>
+      <c r="L101" s="136"/>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" s="1"/>
-      <c r="B102" s="74" t="s">
+      <c r="B102" s="133" t="s">
         <v>52</v>
       </c>
-      <c r="C102" s="75"/>
-      <c r="D102" s="75"/>
-      <c r="E102" s="75"/>
-      <c r="F102" s="75"/>
-      <c r="G102" s="75"/>
-      <c r="H102" s="75"/>
-      <c r="I102" s="75"/>
-      <c r="J102" s="76"/>
-      <c r="K102" s="77"/>
-      <c r="L102" s="78"/>
+      <c r="C102" s="134"/>
+      <c r="D102" s="134"/>
+      <c r="E102" s="134"/>
+      <c r="F102" s="134"/>
+      <c r="G102" s="134"/>
+      <c r="H102" s="134"/>
+      <c r="I102" s="134"/>
+      <c r="J102" s="135"/>
+      <c r="K102" s="98"/>
+      <c r="L102" s="136"/>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" s="1"/>
-      <c r="B103" s="74" t="s">
+      <c r="B103" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="C103" s="75"/>
-      <c r="D103" s="75"/>
-      <c r="E103" s="75"/>
-      <c r="F103" s="75"/>
-      <c r="G103" s="75"/>
-      <c r="H103" s="75"/>
-      <c r="I103" s="75"/>
-      <c r="J103" s="76"/>
-      <c r="K103" s="77"/>
-      <c r="L103" s="78"/>
+      <c r="C103" s="134"/>
+      <c r="D103" s="134"/>
+      <c r="E103" s="134"/>
+      <c r="F103" s="134"/>
+      <c r="G103" s="134"/>
+      <c r="H103" s="134"/>
+      <c r="I103" s="134"/>
+      <c r="J103" s="135"/>
+      <c r="K103" s="98"/>
+      <c r="L103" s="136"/>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" s="1"/>
-      <c r="B104" s="74" t="s">
+      <c r="B104" s="133" t="s">
         <v>54</v>
       </c>
-      <c r="C104" s="75"/>
-      <c r="D104" s="75"/>
-      <c r="E104" s="75"/>
-      <c r="F104" s="75"/>
-      <c r="G104" s="75"/>
-      <c r="H104" s="75"/>
-      <c r="I104" s="75"/>
-      <c r="J104" s="76"/>
-      <c r="K104" s="77"/>
-      <c r="L104" s="78"/>
+      <c r="C104" s="134"/>
+      <c r="D104" s="134"/>
+      <c r="E104" s="134"/>
+      <c r="F104" s="134"/>
+      <c r="G104" s="134"/>
+      <c r="H104" s="134"/>
+      <c r="I104" s="134"/>
+      <c r="J104" s="135"/>
+      <c r="K104" s="98"/>
+      <c r="L104" s="136"/>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" s="1"/>
-      <c r="B105" s="74" t="s">
+      <c r="B105" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="C105" s="75"/>
-      <c r="D105" s="75"/>
-      <c r="E105" s="75"/>
-      <c r="F105" s="75"/>
-      <c r="G105" s="75"/>
-      <c r="H105" s="75"/>
-      <c r="I105" s="75"/>
-      <c r="J105" s="76"/>
-      <c r="K105" s="77"/>
-      <c r="L105" s="78"/>
+      <c r="C105" s="134"/>
+      <c r="D105" s="134"/>
+      <c r="E105" s="134"/>
+      <c r="F105" s="134"/>
+      <c r="G105" s="134"/>
+      <c r="H105" s="134"/>
+      <c r="I105" s="134"/>
+      <c r="J105" s="135"/>
+      <c r="K105" s="98"/>
+      <c r="L105" s="136"/>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" s="1"/>
-      <c r="B106" s="74" t="s">
+      <c r="B106" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="C106" s="75"/>
-      <c r="D106" s="75"/>
-      <c r="E106" s="75"/>
-      <c r="F106" s="75"/>
-      <c r="G106" s="75"/>
-      <c r="H106" s="75"/>
-      <c r="I106" s="75"/>
-      <c r="J106" s="76"/>
-      <c r="K106" s="77"/>
-      <c r="L106" s="78"/>
+      <c r="C106" s="134"/>
+      <c r="D106" s="134"/>
+      <c r="E106" s="134"/>
+      <c r="F106" s="134"/>
+      <c r="G106" s="134"/>
+      <c r="H106" s="134"/>
+      <c r="I106" s="134"/>
+      <c r="J106" s="135"/>
+      <c r="K106" s="98"/>
+      <c r="L106" s="136"/>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="1"/>
-      <c r="B107" s="74" t="s">
+      <c r="B107" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="C107" s="75"/>
-      <c r="D107" s="75"/>
-      <c r="E107" s="75"/>
-      <c r="F107" s="75"/>
-      <c r="G107" s="75"/>
-      <c r="H107" s="75"/>
-      <c r="I107" s="75"/>
-      <c r="J107" s="76"/>
-      <c r="K107" s="77"/>
-      <c r="L107" s="78"/>
+      <c r="C107" s="134"/>
+      <c r="D107" s="134"/>
+      <c r="E107" s="134"/>
+      <c r="F107" s="134"/>
+      <c r="G107" s="134"/>
+      <c r="H107" s="134"/>
+      <c r="I107" s="134"/>
+      <c r="J107" s="135"/>
+      <c r="K107" s="98"/>
+      <c r="L107" s="136"/>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" s="1"/>
-      <c r="B108" s="74" t="s">
+      <c r="B108" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="C108" s="75"/>
-      <c r="D108" s="75"/>
-      <c r="E108" s="75"/>
-      <c r="F108" s="75"/>
-      <c r="G108" s="75"/>
-      <c r="H108" s="75"/>
-      <c r="I108" s="75"/>
-      <c r="J108" s="76"/>
-      <c r="K108" s="77"/>
-      <c r="L108" s="78"/>
+      <c r="C108" s="134"/>
+      <c r="D108" s="134"/>
+      <c r="E108" s="134"/>
+      <c r="F108" s="134"/>
+      <c r="G108" s="134"/>
+      <c r="H108" s="134"/>
+      <c r="I108" s="134"/>
+      <c r="J108" s="135"/>
+      <c r="K108" s="98"/>
+      <c r="L108" s="136"/>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" s="1"/>
-      <c r="B109" s="74" t="s">
+      <c r="B109" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="C109" s="75"/>
-      <c r="D109" s="75"/>
-      <c r="E109" s="75"/>
-      <c r="F109" s="75"/>
-      <c r="G109" s="75"/>
-      <c r="H109" s="75"/>
-      <c r="I109" s="75"/>
-      <c r="J109" s="76"/>
-      <c r="K109" s="77"/>
-      <c r="L109" s="78"/>
+      <c r="C109" s="134"/>
+      <c r="D109" s="134"/>
+      <c r="E109" s="134"/>
+      <c r="F109" s="134"/>
+      <c r="G109" s="134"/>
+      <c r="H109" s="134"/>
+      <c r="I109" s="134"/>
+      <c r="J109" s="135"/>
+      <c r="K109" s="98"/>
+      <c r="L109" s="136"/>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" s="1"/>
-      <c r="B110" s="74" t="s">
+      <c r="B110" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="C110" s="75"/>
-      <c r="D110" s="75"/>
-      <c r="E110" s="75"/>
-      <c r="F110" s="75"/>
-      <c r="G110" s="75"/>
-      <c r="H110" s="75"/>
-      <c r="I110" s="75"/>
-      <c r="J110" s="76"/>
-      <c r="K110" s="77"/>
-      <c r="L110" s="78"/>
+      <c r="C110" s="134"/>
+      <c r="D110" s="134"/>
+      <c r="E110" s="134"/>
+      <c r="F110" s="134"/>
+      <c r="G110" s="134"/>
+      <c r="H110" s="134"/>
+      <c r="I110" s="134"/>
+      <c r="J110" s="135"/>
+      <c r="K110" s="98"/>
+      <c r="L110" s="136"/>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" s="1"/>
-      <c r="B111" s="74" t="s">
+      <c r="B111" s="133" t="s">
         <v>61</v>
       </c>
-      <c r="C111" s="75"/>
-      <c r="D111" s="75"/>
-      <c r="E111" s="75"/>
-      <c r="F111" s="75"/>
-      <c r="G111" s="75"/>
-      <c r="H111" s="75"/>
-      <c r="I111" s="75"/>
-      <c r="J111" s="76"/>
-      <c r="K111" s="77"/>
-      <c r="L111" s="78"/>
+      <c r="C111" s="134"/>
+      <c r="D111" s="134"/>
+      <c r="E111" s="134"/>
+      <c r="F111" s="134"/>
+      <c r="G111" s="134"/>
+      <c r="H111" s="134"/>
+      <c r="I111" s="134"/>
+      <c r="J111" s="135"/>
+      <c r="K111" s="98"/>
+      <c r="L111" s="136"/>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" s="1"/>
-      <c r="B112" s="74" t="s">
+      <c r="B112" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="C112" s="75"/>
-      <c r="D112" s="75"/>
-      <c r="E112" s="75"/>
-      <c r="F112" s="75"/>
-      <c r="G112" s="75"/>
-      <c r="H112" s="75"/>
-      <c r="I112" s="75"/>
-      <c r="J112" s="76"/>
-      <c r="K112" s="77"/>
-      <c r="L112" s="78"/>
+      <c r="C112" s="134"/>
+      <c r="D112" s="134"/>
+      <c r="E112" s="134"/>
+      <c r="F112" s="134"/>
+      <c r="G112" s="134"/>
+      <c r="H112" s="134"/>
+      <c r="I112" s="134"/>
+      <c r="J112" s="135"/>
+      <c r="K112" s="98"/>
+      <c r="L112" s="136"/>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" s="1"/>
-      <c r="B113" s="74" t="s">
+      <c r="B113" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="C113" s="75"/>
-      <c r="D113" s="75"/>
-      <c r="E113" s="75"/>
-      <c r="F113" s="75"/>
-      <c r="G113" s="75"/>
-      <c r="H113" s="75"/>
-      <c r="I113" s="75"/>
-      <c r="J113" s="76"/>
-      <c r="K113" s="77"/>
-      <c r="L113" s="78"/>
+      <c r="C113" s="134"/>
+      <c r="D113" s="134"/>
+      <c r="E113" s="134"/>
+      <c r="F113" s="134"/>
+      <c r="G113" s="134"/>
+      <c r="H113" s="134"/>
+      <c r="I113" s="134"/>
+      <c r="J113" s="135"/>
+      <c r="K113" s="98"/>
+      <c r="L113" s="136"/>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" s="1"/>
-      <c r="B114" s="74" t="s">
+      <c r="B114" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="C114" s="75"/>
-      <c r="D114" s="75"/>
-      <c r="E114" s="75"/>
-      <c r="F114" s="75"/>
-      <c r="G114" s="75"/>
-      <c r="H114" s="75"/>
-      <c r="I114" s="75"/>
-      <c r="J114" s="76"/>
-      <c r="K114" s="77"/>
-      <c r="L114" s="78"/>
+      <c r="C114" s="134"/>
+      <c r="D114" s="134"/>
+      <c r="E114" s="134"/>
+      <c r="F114" s="134"/>
+      <c r="G114" s="134"/>
+      <c r="H114" s="134"/>
+      <c r="I114" s="134"/>
+      <c r="J114" s="135"/>
+      <c r="K114" s="98"/>
+      <c r="L114" s="136"/>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" s="1"/>
-      <c r="B115" s="74" t="s">
+      <c r="B115" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="C115" s="75"/>
-      <c r="D115" s="75"/>
-      <c r="E115" s="75"/>
-      <c r="F115" s="75"/>
-      <c r="G115" s="75"/>
-      <c r="H115" s="75"/>
-      <c r="I115" s="75"/>
-      <c r="J115" s="76"/>
-      <c r="K115" s="77"/>
-      <c r="L115" s="78"/>
+      <c r="C115" s="134"/>
+      <c r="D115" s="134"/>
+      <c r="E115" s="134"/>
+      <c r="F115" s="134"/>
+      <c r="G115" s="134"/>
+      <c r="H115" s="134"/>
+      <c r="I115" s="134"/>
+      <c r="J115" s="135"/>
+      <c r="K115" s="98"/>
+      <c r="L115" s="136"/>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" s="1"/>
-      <c r="B116" s="142"/>
-      <c r="C116" s="143"/>
-      <c r="D116" s="143"/>
-      <c r="E116" s="143"/>
-      <c r="F116" s="143"/>
-      <c r="G116" s="143"/>
-      <c r="H116" s="143"/>
-      <c r="I116" s="143"/>
-      <c r="J116" s="144"/>
-      <c r="K116" s="142"/>
-      <c r="L116" s="144"/>
+      <c r="B116" s="36"/>
+      <c r="C116" s="37"/>
+      <c r="D116" s="37"/>
+      <c r="E116" s="37"/>
+      <c r="F116" s="37"/>
+      <c r="G116" s="37"/>
+      <c r="H116" s="37"/>
+      <c r="I116" s="37"/>
+      <c r="J116" s="38"/>
+      <c r="K116" s="36"/>
+      <c r="L116" s="38"/>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" s="1"/>
-      <c r="B117" s="135"/>
-      <c r="C117" s="52"/>
-      <c r="D117" s="52"/>
-      <c r="E117" s="52"/>
-      <c r="F117" s="52"/>
-      <c r="G117" s="52"/>
-      <c r="H117" s="52"/>
-      <c r="I117" s="52"/>
-      <c r="J117" s="145"/>
-      <c r="K117" s="135"/>
-      <c r="L117" s="145"/>
+      <c r="B117" s="39"/>
+      <c r="C117" s="40"/>
+      <c r="D117" s="40"/>
+      <c r="E117" s="40"/>
+      <c r="F117" s="40"/>
+      <c r="G117" s="40"/>
+      <c r="H117" s="40"/>
+      <c r="I117" s="40"/>
+      <c r="J117" s="41"/>
+      <c r="K117" s="39"/>
+      <c r="L117" s="41"/>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" s="1"/>
-      <c r="B118" s="135"/>
-      <c r="C118" s="52"/>
-      <c r="D118" s="52"/>
-      <c r="E118" s="52"/>
-      <c r="F118" s="52"/>
-      <c r="G118" s="52"/>
-      <c r="H118" s="52"/>
-      <c r="I118" s="52"/>
-      <c r="J118" s="145"/>
-      <c r="K118" s="135"/>
-      <c r="L118" s="145"/>
+      <c r="B118" s="39"/>
+      <c r="C118" s="40"/>
+      <c r="D118" s="40"/>
+      <c r="E118" s="40"/>
+      <c r="F118" s="40"/>
+      <c r="G118" s="40"/>
+      <c r="H118" s="40"/>
+      <c r="I118" s="40"/>
+      <c r="J118" s="41"/>
+      <c r="K118" s="39"/>
+      <c r="L118" s="41"/>
     </row>
     <row r="119" spans="1:12" ht="45" customHeight="1">
       <c r="A119" s="1"/>
-      <c r="B119" s="146"/>
-      <c r="C119" s="131"/>
-      <c r="D119" s="131"/>
-      <c r="E119" s="131"/>
-      <c r="F119" s="131"/>
-      <c r="G119" s="131"/>
-      <c r="H119" s="131"/>
-      <c r="I119" s="131"/>
-      <c r="J119" s="147"/>
-      <c r="K119" s="146"/>
-      <c r="L119" s="147"/>
+      <c r="B119" s="42"/>
+      <c r="C119" s="43"/>
+      <c r="D119" s="43"/>
+      <c r="E119" s="43"/>
+      <c r="F119" s="43"/>
+      <c r="G119" s="43"/>
+      <c r="H119" s="43"/>
+      <c r="I119" s="43"/>
+      <c r="J119" s="44"/>
+      <c r="K119" s="42"/>
+      <c r="L119" s="44"/>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" s="1"/>
@@ -3970,65 +3970,65 @@
     </row>
     <row r="121" spans="1:12" ht="30" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="79"/>
-      <c r="C121" s="80"/>
-      <c r="D121" s="79"/>
-      <c r="E121" s="85"/>
-      <c r="F121" s="80"/>
-      <c r="G121" s="88"/>
-      <c r="H121" s="89"/>
-      <c r="I121" s="89"/>
-      <c r="J121" s="90"/>
-      <c r="K121" s="88"/>
-      <c r="L121" s="90"/>
+      <c r="B121" s="58"/>
+      <c r="C121" s="59"/>
+      <c r="D121" s="58"/>
+      <c r="E121" s="64"/>
+      <c r="F121" s="59"/>
+      <c r="G121" s="109"/>
+      <c r="H121" s="110"/>
+      <c r="I121" s="110"/>
+      <c r="J121" s="111"/>
+      <c r="K121" s="109"/>
+      <c r="L121" s="111"/>
     </row>
     <row r="122" spans="1:12">
-      <c r="B122" s="81"/>
-      <c r="C122" s="82"/>
-      <c r="D122" s="81"/>
-      <c r="E122" s="86"/>
-      <c r="F122" s="82"/>
-      <c r="G122" s="91"/>
-      <c r="H122" s="92"/>
-      <c r="I122" s="92"/>
-      <c r="J122" s="93"/>
-      <c r="K122" s="91"/>
-      <c r="L122" s="93"/>
+      <c r="B122" s="60"/>
+      <c r="C122" s="61"/>
+      <c r="D122" s="60"/>
+      <c r="E122" s="65"/>
+      <c r="F122" s="61"/>
+      <c r="G122" s="112"/>
+      <c r="H122" s="113"/>
+      <c r="I122" s="113"/>
+      <c r="J122" s="114"/>
+      <c r="K122" s="112"/>
+      <c r="L122" s="114"/>
     </row>
     <row r="123" spans="1:12">
-      <c r="B123" s="83"/>
-      <c r="C123" s="84"/>
-      <c r="D123" s="83"/>
-      <c r="E123" s="87"/>
-      <c r="F123" s="84"/>
-      <c r="G123" s="94"/>
-      <c r="H123" s="95"/>
-      <c r="I123" s="95"/>
-      <c r="J123" s="96"/>
-      <c r="K123" s="94"/>
-      <c r="L123" s="96"/>
+      <c r="B123" s="62"/>
+      <c r="C123" s="63"/>
+      <c r="D123" s="62"/>
+      <c r="E123" s="66"/>
+      <c r="F123" s="63"/>
+      <c r="G123" s="115"/>
+      <c r="H123" s="116"/>
+      <c r="I123" s="116"/>
+      <c r="J123" s="117"/>
+      <c r="K123" s="115"/>
+      <c r="L123" s="117"/>
     </row>
     <row r="124" spans="1:12" s="31" customFormat="1" ht="47.25" customHeight="1">
       <c r="A124" s="25"/>
-      <c r="B124" s="35" t="s">
+      <c r="B124" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="C124" s="36"/>
-      <c r="D124" s="37" t="s">
+      <c r="C124" s="138"/>
+      <c r="D124" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="E124" s="38"/>
-      <c r="F124" s="39"/>
-      <c r="G124" s="37" t="s">
+      <c r="E124" s="125"/>
+      <c r="F124" s="124"/>
+      <c r="G124" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="H124" s="38"/>
-      <c r="I124" s="38"/>
-      <c r="J124" s="39"/>
-      <c r="K124" s="37" t="s">
+      <c r="H124" s="125"/>
+      <c r="I124" s="125"/>
+      <c r="J124" s="124"/>
+      <c r="K124" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="L124" s="39"/>
+      <c r="L124" s="124"/>
     </row>
     <row r="126" spans="1:12" ht="27" customHeight="1"/>
     <row r="127" spans="1:12" ht="27" customHeight="1"/>
@@ -4042,13 +4042,13 @@
         <v>0</v>
       </c>
       <c r="C132" s="2"/>
-      <c r="D132" s="43" t="str">
+      <c r="D132" s="120" t="str">
         <f>D68</f>
         <v>MHOS-SSM-EL-0001</v>
       </c>
-      <c r="E132" s="72"/>
-      <c r="F132" s="72"/>
-      <c r="G132" s="44"/>
+      <c r="E132" s="121"/>
+      <c r="F132" s="121"/>
+      <c r="G132" s="122"/>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
@@ -4061,10 +4061,10 @@
         <v>2</v>
       </c>
       <c r="C133" s="2"/>
-      <c r="D133" s="73"/>
-      <c r="E133" s="73"/>
-      <c r="F133" s="73"/>
-      <c r="G133" s="73"/>
+      <c r="D133" s="139"/>
+      <c r="E133" s="139"/>
+      <c r="F133" s="139"/>
+      <c r="G133" s="139"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
@@ -4090,11 +4090,11 @@
       <c r="B135" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C135" s="67"/>
-      <c r="D135" s="67"/>
-      <c r="E135" s="67"/>
-      <c r="F135" s="67"/>
-      <c r="G135" s="67"/>
+      <c r="C135" s="80"/>
+      <c r="D135" s="80"/>
+      <c r="E135" s="80"/>
+      <c r="F135" s="80"/>
+      <c r="G135" s="80"/>
       <c r="H135" s="23"/>
       <c r="I135" s="23"/>
       <c r="J135" s="23"/>
@@ -4104,34 +4104,34 @@
     <row r="136" spans="1:12">
       <c r="A136" s="1"/>
       <c r="B136" s="4"/>
-      <c r="C136" s="68"/>
-      <c r="D136" s="68"/>
+      <c r="C136" s="141"/>
+      <c r="D136" s="141"/>
       <c r="E136" s="2"/>
-      <c r="F136" s="68"/>
-      <c r="G136" s="68"/>
+      <c r="F136" s="141"/>
+      <c r="G136" s="141"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
-      <c r="J136" s="68"/>
-      <c r="K136" s="68"/>
-      <c r="L136" s="69"/>
+      <c r="J136" s="141"/>
+      <c r="K136" s="141"/>
+      <c r="L136" s="142"/>
     </row>
     <row r="137" spans="1:12">
       <c r="A137" s="1"/>
       <c r="B137" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C137" s="70"/>
-      <c r="D137" s="70"/>
-      <c r="E137" s="70"/>
-      <c r="F137" s="70"/>
-      <c r="G137" s="70"/>
+      <c r="C137" s="53"/>
+      <c r="D137" s="53"/>
+      <c r="E137" s="53"/>
+      <c r="F137" s="53"/>
+      <c r="G137" s="53"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J137" s="70"/>
-      <c r="K137" s="70"/>
-      <c r="L137" s="71"/>
+      <c r="J137" s="53"/>
+      <c r="K137" s="53"/>
+      <c r="L137" s="54"/>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="1"/>
@@ -4163,19 +4163,19 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="1"/>
-      <c r="B140" s="63" t="s">
+      <c r="B140" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="C140" s="64"/>
-      <c r="D140" s="64"/>
-      <c r="E140" s="64"/>
-      <c r="F140" s="64"/>
-      <c r="G140" s="64"/>
-      <c r="H140" s="64"/>
-      <c r="I140" s="64"/>
-      <c r="J140" s="64"/>
-      <c r="K140" s="64"/>
-      <c r="L140" s="65"/>
+      <c r="C140" s="69"/>
+      <c r="D140" s="69"/>
+      <c r="E140" s="69"/>
+      <c r="F140" s="69"/>
+      <c r="G140" s="69"/>
+      <c r="H140" s="69"/>
+      <c r="I140" s="69"/>
+      <c r="J140" s="69"/>
+      <c r="K140" s="69"/>
+      <c r="L140" s="68"/>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" s="1"/>
@@ -4207,115 +4207,115 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" s="1"/>
-      <c r="B143" s="66"/>
-      <c r="C143" s="66"/>
-      <c r="D143" s="66"/>
-      <c r="E143" s="66"/>
-      <c r="F143" s="66"/>
-      <c r="G143" s="66"/>
-      <c r="H143" s="66"/>
-      <c r="I143" s="66"/>
-      <c r="J143" s="66"/>
-      <c r="K143" s="66"/>
-      <c r="L143" s="66"/>
+      <c r="B143" s="140"/>
+      <c r="C143" s="140"/>
+      <c r="D143" s="140"/>
+      <c r="E143" s="140"/>
+      <c r="F143" s="140"/>
+      <c r="G143" s="140"/>
+      <c r="H143" s="140"/>
+      <c r="I143" s="140"/>
+      <c r="J143" s="140"/>
+      <c r="K143" s="140"/>
+      <c r="L143" s="140"/>
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="1"/>
-      <c r="B144" s="66"/>
-      <c r="C144" s="66"/>
-      <c r="D144" s="66"/>
-      <c r="E144" s="66"/>
-      <c r="F144" s="66"/>
-      <c r="G144" s="66"/>
-      <c r="H144" s="66"/>
-      <c r="I144" s="66"/>
-      <c r="J144" s="66"/>
-      <c r="K144" s="66"/>
-      <c r="L144" s="66"/>
+      <c r="B144" s="140"/>
+      <c r="C144" s="140"/>
+      <c r="D144" s="140"/>
+      <c r="E144" s="140"/>
+      <c r="F144" s="140"/>
+      <c r="G144" s="140"/>
+      <c r="H144" s="140"/>
+      <c r="I144" s="140"/>
+      <c r="J144" s="140"/>
+      <c r="K144" s="140"/>
+      <c r="L144" s="140"/>
     </row>
     <row r="145" spans="1:12">
       <c r="A145" s="1"/>
-      <c r="B145" s="66"/>
-      <c r="C145" s="66"/>
-      <c r="D145" s="66"/>
-      <c r="E145" s="66"/>
-      <c r="F145" s="66"/>
-      <c r="G145" s="66"/>
-      <c r="H145" s="66"/>
-      <c r="I145" s="66"/>
-      <c r="J145" s="66"/>
-      <c r="K145" s="66"/>
-      <c r="L145" s="66"/>
+      <c r="B145" s="140"/>
+      <c r="C145" s="140"/>
+      <c r="D145" s="140"/>
+      <c r="E145" s="140"/>
+      <c r="F145" s="140"/>
+      <c r="G145" s="140"/>
+      <c r="H145" s="140"/>
+      <c r="I145" s="140"/>
+      <c r="J145" s="140"/>
+      <c r="K145" s="140"/>
+      <c r="L145" s="140"/>
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="1"/>
-      <c r="B146" s="66"/>
-      <c r="C146" s="66"/>
-      <c r="D146" s="66"/>
-      <c r="E146" s="66"/>
-      <c r="F146" s="66"/>
-      <c r="G146" s="66"/>
-      <c r="H146" s="66"/>
-      <c r="I146" s="66"/>
-      <c r="J146" s="66"/>
-      <c r="K146" s="66"/>
-      <c r="L146" s="66"/>
+      <c r="B146" s="140"/>
+      <c r="C146" s="140"/>
+      <c r="D146" s="140"/>
+      <c r="E146" s="140"/>
+      <c r="F146" s="140"/>
+      <c r="G146" s="140"/>
+      <c r="H146" s="140"/>
+      <c r="I146" s="140"/>
+      <c r="J146" s="140"/>
+      <c r="K146" s="140"/>
+      <c r="L146" s="140"/>
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="1"/>
-      <c r="B147" s="66"/>
-      <c r="C147" s="66"/>
-      <c r="D147" s="66"/>
-      <c r="E147" s="66"/>
-      <c r="F147" s="66"/>
-      <c r="G147" s="66"/>
-      <c r="H147" s="66"/>
-      <c r="I147" s="66"/>
-      <c r="J147" s="66"/>
-      <c r="K147" s="66"/>
-      <c r="L147" s="66"/>
+      <c r="B147" s="140"/>
+      <c r="C147" s="140"/>
+      <c r="D147" s="140"/>
+      <c r="E147" s="140"/>
+      <c r="F147" s="140"/>
+      <c r="G147" s="140"/>
+      <c r="H147" s="140"/>
+      <c r="I147" s="140"/>
+      <c r="J147" s="140"/>
+      <c r="K147" s="140"/>
+      <c r="L147" s="140"/>
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="1"/>
-      <c r="B148" s="66"/>
-      <c r="C148" s="66"/>
-      <c r="D148" s="66"/>
-      <c r="E148" s="66"/>
-      <c r="F148" s="66"/>
-      <c r="G148" s="66"/>
-      <c r="H148" s="66"/>
-      <c r="I148" s="66"/>
-      <c r="J148" s="66"/>
-      <c r="K148" s="66"/>
-      <c r="L148" s="66"/>
+      <c r="B148" s="140"/>
+      <c r="C148" s="140"/>
+      <c r="D148" s="140"/>
+      <c r="E148" s="140"/>
+      <c r="F148" s="140"/>
+      <c r="G148" s="140"/>
+      <c r="H148" s="140"/>
+      <c r="I148" s="140"/>
+      <c r="J148" s="140"/>
+      <c r="K148" s="140"/>
+      <c r="L148" s="140"/>
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="1"/>
-      <c r="B149" s="66"/>
-      <c r="C149" s="66"/>
-      <c r="D149" s="66"/>
-      <c r="E149" s="66"/>
-      <c r="F149" s="66"/>
-      <c r="G149" s="66"/>
-      <c r="H149" s="66"/>
-      <c r="I149" s="66"/>
-      <c r="J149" s="66"/>
-      <c r="K149" s="66"/>
-      <c r="L149" s="66"/>
+      <c r="B149" s="140"/>
+      <c r="C149" s="140"/>
+      <c r="D149" s="140"/>
+      <c r="E149" s="140"/>
+      <c r="F149" s="140"/>
+      <c r="G149" s="140"/>
+      <c r="H149" s="140"/>
+      <c r="I149" s="140"/>
+      <c r="J149" s="140"/>
+      <c r="K149" s="140"/>
+      <c r="L149" s="140"/>
     </row>
     <row r="150" spans="1:12" ht="31.5" customHeight="1">
       <c r="A150" s="1"/>
-      <c r="B150" s="66"/>
-      <c r="C150" s="66"/>
-      <c r="D150" s="66"/>
-      <c r="E150" s="66"/>
-      <c r="F150" s="66"/>
-      <c r="G150" s="66"/>
-      <c r="H150" s="66"/>
-      <c r="I150" s="66"/>
-      <c r="J150" s="66"/>
-      <c r="K150" s="66"/>
-      <c r="L150" s="66"/>
+      <c r="B150" s="140"/>
+      <c r="C150" s="140"/>
+      <c r="D150" s="140"/>
+      <c r="E150" s="140"/>
+      <c r="F150" s="140"/>
+      <c r="G150" s="140"/>
+      <c r="H150" s="140"/>
+      <c r="I150" s="140"/>
+      <c r="J150" s="140"/>
+      <c r="K150" s="140"/>
+      <c r="L150" s="140"/>
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="1"/>
@@ -4333,19 +4333,19 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" s="1"/>
-      <c r="B152" s="52" t="s">
+      <c r="B152" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C152" s="52"/>
+      <c r="C152" s="40"/>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
-      <c r="I152" s="52" t="s">
+      <c r="I152" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="J152" s="52"/>
+      <c r="J152" s="40"/>
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
     </row>
@@ -4395,117 +4395,117 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" s="1"/>
-      <c r="B156" s="62"/>
-      <c r="C156" s="62"/>
-      <c r="D156" s="52"/>
-      <c r="E156" s="52"/>
-      <c r="F156" s="52"/>
+      <c r="B156" s="159"/>
+      <c r="C156" s="159"/>
+      <c r="D156" s="40"/>
+      <c r="E156" s="40"/>
+      <c r="F156" s="40"/>
       <c r="G156" s="2"/>
-      <c r="H156" s="52"/>
-      <c r="I156" s="52"/>
-      <c r="J156" s="52"/>
-      <c r="K156" s="52"/>
-      <c r="L156" s="52"/>
+      <c r="H156" s="40"/>
+      <c r="I156" s="40"/>
+      <c r="J156" s="40"/>
+      <c r="K156" s="40"/>
+      <c r="L156" s="40"/>
     </row>
     <row r="157" spans="1:12">
       <c r="A157" s="1"/>
-      <c r="B157" s="62"/>
-      <c r="C157" s="62"/>
-      <c r="D157" s="52"/>
-      <c r="E157" s="52"/>
-      <c r="F157" s="52"/>
+      <c r="B157" s="159"/>
+      <c r="C157" s="159"/>
+      <c r="D157" s="40"/>
+      <c r="E157" s="40"/>
+      <c r="F157" s="40"/>
       <c r="G157" s="2"/>
-      <c r="H157" s="52"/>
-      <c r="I157" s="52"/>
-      <c r="J157" s="52"/>
-      <c r="K157" s="52"/>
-      <c r="L157" s="52"/>
+      <c r="H157" s="40"/>
+      <c r="I157" s="40"/>
+      <c r="J157" s="40"/>
+      <c r="K157" s="40"/>
+      <c r="L157" s="40"/>
     </row>
     <row r="158" spans="1:12">
       <c r="A158" s="1"/>
-      <c r="B158" s="62"/>
-      <c r="C158" s="62"/>
-      <c r="D158" s="52"/>
-      <c r="E158" s="52"/>
-      <c r="F158" s="52"/>
+      <c r="B158" s="159"/>
+      <c r="C158" s="159"/>
+      <c r="D158" s="40"/>
+      <c r="E158" s="40"/>
+      <c r="F158" s="40"/>
       <c r="G158" s="2"/>
-      <c r="H158" s="52"/>
-      <c r="I158" s="52"/>
-      <c r="J158" s="52"/>
-      <c r="K158" s="52"/>
-      <c r="L158" s="52"/>
+      <c r="H158" s="40"/>
+      <c r="I158" s="40"/>
+      <c r="J158" s="40"/>
+      <c r="K158" s="40"/>
+      <c r="L158" s="40"/>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" s="1"/>
-      <c r="B159" s="62"/>
-      <c r="C159" s="62"/>
-      <c r="D159" s="52"/>
-      <c r="E159" s="52"/>
-      <c r="F159" s="52"/>
+      <c r="B159" s="159"/>
+      <c r="C159" s="159"/>
+      <c r="D159" s="40"/>
+      <c r="E159" s="40"/>
+      <c r="F159" s="40"/>
       <c r="G159" s="2"/>
-      <c r="H159" s="52"/>
-      <c r="I159" s="52"/>
-      <c r="J159" s="52"/>
-      <c r="K159" s="52"/>
-      <c r="L159" s="52"/>
+      <c r="H159" s="40"/>
+      <c r="I159" s="40"/>
+      <c r="J159" s="40"/>
+      <c r="K159" s="40"/>
+      <c r="L159" s="40"/>
     </row>
     <row r="160" spans="1:12">
       <c r="A160" s="1"/>
-      <c r="B160" s="62"/>
-      <c r="C160" s="62"/>
-      <c r="D160" s="52"/>
-      <c r="E160" s="52"/>
-      <c r="F160" s="52"/>
+      <c r="B160" s="159"/>
+      <c r="C160" s="159"/>
+      <c r="D160" s="40"/>
+      <c r="E160" s="40"/>
+      <c r="F160" s="40"/>
       <c r="G160" s="2"/>
-      <c r="H160" s="52"/>
-      <c r="I160" s="52"/>
-      <c r="J160" s="52"/>
-      <c r="K160" s="52"/>
-      <c r="L160" s="52"/>
+      <c r="H160" s="40"/>
+      <c r="I160" s="40"/>
+      <c r="J160" s="40"/>
+      <c r="K160" s="40"/>
+      <c r="L160" s="40"/>
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="1"/>
-      <c r="B161" s="62"/>
-      <c r="C161" s="62"/>
-      <c r="D161" s="52"/>
-      <c r="E161" s="52"/>
-      <c r="F161" s="52"/>
+      <c r="B161" s="159"/>
+      <c r="C161" s="159"/>
+      <c r="D161" s="40"/>
+      <c r="E161" s="40"/>
+      <c r="F161" s="40"/>
       <c r="G161" s="2"/>
-      <c r="H161" s="52"/>
-      <c r="I161" s="52"/>
-      <c r="J161" s="52"/>
-      <c r="K161" s="52"/>
-      <c r="L161" s="52"/>
+      <c r="H161" s="40"/>
+      <c r="I161" s="40"/>
+      <c r="J161" s="40"/>
+      <c r="K161" s="40"/>
+      <c r="L161" s="40"/>
     </row>
     <row r="162" spans="1:12" ht="51" customHeight="1">
       <c r="A162" s="1"/>
-      <c r="B162" s="62"/>
-      <c r="C162" s="62"/>
-      <c r="D162" s="52"/>
-      <c r="E162" s="52"/>
-      <c r="F162" s="52"/>
+      <c r="B162" s="159"/>
+      <c r="C162" s="159"/>
+      <c r="D162" s="40"/>
+      <c r="E162" s="40"/>
+      <c r="F162" s="40"/>
       <c r="G162" s="2"/>
-      <c r="H162" s="52"/>
-      <c r="I162" s="52"/>
-      <c r="J162" s="52"/>
-      <c r="K162" s="52"/>
-      <c r="L162" s="52"/>
+      <c r="H162" s="40"/>
+      <c r="I162" s="40"/>
+      <c r="J162" s="40"/>
+      <c r="K162" s="40"/>
+      <c r="L162" s="40"/>
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="1"/>
-      <c r="B163" s="52" t="s">
+      <c r="B163" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C163" s="52"/>
+      <c r="C163" s="40"/>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
-      <c r="I163" s="52" t="s">
+      <c r="I163" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="J163" s="52"/>
+      <c r="J163" s="40"/>
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
     </row>
@@ -4567,15 +4567,15 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="1"/>
-      <c r="B168" s="52"/>
-      <c r="C168" s="52"/>
+      <c r="B168" s="40"/>
+      <c r="C168" s="40"/>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
-      <c r="I168" s="52"/>
-      <c r="J168" s="52"/>
+      <c r="I168" s="40"/>
+      <c r="J168" s="40"/>
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
     </row>
@@ -4665,67 +4665,67 @@
     </row>
     <row r="175" spans="1:12">
       <c r="A175" s="1"/>
-      <c r="B175" s="53"/>
-      <c r="C175" s="54"/>
-      <c r="D175" s="53"/>
-      <c r="E175" s="59"/>
-      <c r="F175" s="54"/>
-      <c r="G175" s="53"/>
-      <c r="H175" s="59"/>
-      <c r="I175" s="59"/>
-      <c r="J175" s="54"/>
-      <c r="K175" s="53"/>
-      <c r="L175" s="54"/>
+      <c r="B175" s="150"/>
+      <c r="C175" s="151"/>
+      <c r="D175" s="150"/>
+      <c r="E175" s="156"/>
+      <c r="F175" s="151"/>
+      <c r="G175" s="150"/>
+      <c r="H175" s="156"/>
+      <c r="I175" s="156"/>
+      <c r="J175" s="151"/>
+      <c r="K175" s="150"/>
+      <c r="L175" s="151"/>
     </row>
     <row r="176" spans="1:12">
       <c r="A176" s="1"/>
-      <c r="B176" s="55"/>
-      <c r="C176" s="56"/>
-      <c r="D176" s="55"/>
-      <c r="E176" s="60"/>
-      <c r="F176" s="56"/>
-      <c r="G176" s="55"/>
-      <c r="H176" s="60"/>
-      <c r="I176" s="60"/>
-      <c r="J176" s="56"/>
-      <c r="K176" s="55"/>
-      <c r="L176" s="56"/>
+      <c r="B176" s="152"/>
+      <c r="C176" s="153"/>
+      <c r="D176" s="152"/>
+      <c r="E176" s="157"/>
+      <c r="F176" s="153"/>
+      <c r="G176" s="152"/>
+      <c r="H176" s="157"/>
+      <c r="I176" s="157"/>
+      <c r="J176" s="153"/>
+      <c r="K176" s="152"/>
+      <c r="L176" s="153"/>
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="1"/>
-      <c r="B177" s="57"/>
-      <c r="C177" s="58"/>
-      <c r="D177" s="57"/>
-      <c r="E177" s="61"/>
-      <c r="F177" s="58"/>
-      <c r="G177" s="57"/>
-      <c r="H177" s="61"/>
-      <c r="I177" s="61"/>
-      <c r="J177" s="58"/>
-      <c r="K177" s="57"/>
-      <c r="L177" s="58"/>
+      <c r="B177" s="154"/>
+      <c r="C177" s="155"/>
+      <c r="D177" s="154"/>
+      <c r="E177" s="158"/>
+      <c r="F177" s="155"/>
+      <c r="G177" s="154"/>
+      <c r="H177" s="158"/>
+      <c r="I177" s="158"/>
+      <c r="J177" s="155"/>
+      <c r="K177" s="154"/>
+      <c r="L177" s="155"/>
     </row>
     <row r="178" spans="1:12">
       <c r="A178" s="25"/>
-      <c r="B178" s="35" t="s">
+      <c r="B178" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="C178" s="36"/>
-      <c r="D178" s="37" t="s">
+      <c r="C178" s="138"/>
+      <c r="D178" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="E178" s="38"/>
-      <c r="F178" s="39"/>
-      <c r="G178" s="40" t="s">
+      <c r="E178" s="125"/>
+      <c r="F178" s="124"/>
+      <c r="G178" s="143" t="s">
         <v>72</v>
       </c>
-      <c r="H178" s="41"/>
-      <c r="I178" s="41"/>
-      <c r="J178" s="42"/>
-      <c r="K178" s="43" t="s">
+      <c r="H178" s="144"/>
+      <c r="I178" s="144"/>
+      <c r="J178" s="145"/>
+      <c r="K178" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="L178" s="44"/>
+      <c r="L178" s="122"/>
     </row>
     <row r="187" spans="1:12" ht="30" customHeight="1"/>
     <row r="188" spans="1:12" ht="30" customHeight="1"/>
@@ -4733,6 +4733,158 @@
     <row r="191" spans="1:12" ht="27" customHeight="1"/>
   </sheetData>
   <mergeCells count="176">
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="D178:F178"/>
+    <mergeCell ref="G178:J178"/>
+    <mergeCell ref="K178:L178"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="I168:J168"/>
+    <mergeCell ref="B175:C177"/>
+    <mergeCell ref="D175:F177"/>
+    <mergeCell ref="G175:J177"/>
+    <mergeCell ref="K175:L177"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="I152:J152"/>
+    <mergeCell ref="B156:C162"/>
+    <mergeCell ref="D156:F162"/>
+    <mergeCell ref="H156:L162"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="B140:L140"/>
+    <mergeCell ref="B143:B150"/>
+    <mergeCell ref="C143:D150"/>
+    <mergeCell ref="E143:F150"/>
+    <mergeCell ref="G143:I150"/>
+    <mergeCell ref="J143:L150"/>
+    <mergeCell ref="C135:G135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="J136:L136"/>
+    <mergeCell ref="C137:G137"/>
+    <mergeCell ref="J137:L137"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="K124:L124"/>
+    <mergeCell ref="D132:G132"/>
+    <mergeCell ref="D133:G133"/>
+    <mergeCell ref="B114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="B115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="B121:C123"/>
+    <mergeCell ref="D121:F123"/>
+    <mergeCell ref="G121:J123"/>
+    <mergeCell ref="K121:L123"/>
+    <mergeCell ref="B111:J111"/>
+    <mergeCell ref="K111:L111"/>
+    <mergeCell ref="B112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="B113:J113"/>
+    <mergeCell ref="K113:L113"/>
+    <mergeCell ref="B108:J108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="B109:J109"/>
+    <mergeCell ref="K109:L109"/>
+    <mergeCell ref="B110:J110"/>
+    <mergeCell ref="K110:L110"/>
+    <mergeCell ref="B105:J105"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="B106:J106"/>
+    <mergeCell ref="K106:L106"/>
+    <mergeCell ref="B107:J107"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="B102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="B103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="K104:L104"/>
+    <mergeCell ref="B99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="B100:J100"/>
+    <mergeCell ref="K100:L100"/>
+    <mergeCell ref="B101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="B96:J96"/>
+    <mergeCell ref="K96:L96"/>
+    <mergeCell ref="B97:J97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="B98:J98"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="B93:J93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="B94:J94"/>
+    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="B95:J95"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="B90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="B91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="B88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="G83:I83"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="B36:L46"/>
+    <mergeCell ref="E48:L48"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="B80:L80"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="G57:J59"/>
+    <mergeCell ref="K57:L59"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="C71:L71"/>
+    <mergeCell ref="C72:L73"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="G60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="B53:L53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="B24:L24"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="D32:L32"/>
+    <mergeCell ref="B33:L33"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="B116:J119"/>
     <mergeCell ref="K116:L119"/>
@@ -4757,158 +4909,6 @@
     <mergeCell ref="B31:L31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B53:L53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="G54:J54"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="B24:L24"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="D32:L32"/>
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="B36:L46"/>
-    <mergeCell ref="E48:L48"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="B80:L80"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="G82:I82"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="G57:J59"/>
-    <mergeCell ref="K57:L59"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="C71:L71"/>
-    <mergeCell ref="C72:L73"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="G60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="B88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="G83:I83"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="G84:I84"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="B93:J93"/>
-    <mergeCell ref="K93:L93"/>
-    <mergeCell ref="B94:J94"/>
-    <mergeCell ref="K94:L94"/>
-    <mergeCell ref="B95:J95"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="B90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="B91:J91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="K92:L92"/>
-    <mergeCell ref="B99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="B100:J100"/>
-    <mergeCell ref="K100:L100"/>
-    <mergeCell ref="B101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="B96:J96"/>
-    <mergeCell ref="K96:L96"/>
-    <mergeCell ref="B97:J97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="B98:J98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="B105:J105"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="B106:J106"/>
-    <mergeCell ref="K106:L106"/>
-    <mergeCell ref="B107:J107"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="B102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="B103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="B104:J104"/>
-    <mergeCell ref="K104:L104"/>
-    <mergeCell ref="B111:J111"/>
-    <mergeCell ref="K111:L111"/>
-    <mergeCell ref="B112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="B113:J113"/>
-    <mergeCell ref="K113:L113"/>
-    <mergeCell ref="B108:J108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="B109:J109"/>
-    <mergeCell ref="K109:L109"/>
-    <mergeCell ref="B110:J110"/>
-    <mergeCell ref="K110:L110"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="K124:L124"/>
-    <mergeCell ref="D132:G132"/>
-    <mergeCell ref="D133:G133"/>
-    <mergeCell ref="B114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="B115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="B121:C123"/>
-    <mergeCell ref="D121:F123"/>
-    <mergeCell ref="G121:J123"/>
-    <mergeCell ref="K121:L123"/>
-    <mergeCell ref="B143:B150"/>
-    <mergeCell ref="C143:D150"/>
-    <mergeCell ref="E143:F150"/>
-    <mergeCell ref="G143:I150"/>
-    <mergeCell ref="J143:L150"/>
-    <mergeCell ref="C135:G135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="J136:L136"/>
-    <mergeCell ref="C137:G137"/>
-    <mergeCell ref="J137:L137"/>
-    <mergeCell ref="B178:C178"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="G178:J178"/>
-    <mergeCell ref="K178:L178"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="B168:C168"/>
-    <mergeCell ref="I168:J168"/>
-    <mergeCell ref="B175:C177"/>
-    <mergeCell ref="D175:F177"/>
-    <mergeCell ref="G175:J177"/>
-    <mergeCell ref="K175:L177"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="I152:J152"/>
-    <mergeCell ref="B156:C162"/>
-    <mergeCell ref="D156:F162"/>
-    <mergeCell ref="H156:L162"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="B140:L140"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>

--- a/templates/Plantilla_Preventivo.xlsx
+++ b/templates/Plantilla_Preventivo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B69B62F4-BBC8-42A2-9EA0-5A0D88709856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13FFFCB0-1493-488A-941C-5B8186D15D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2250,7 +2250,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L191"/>
+  <dimension ref="A1:L192"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
@@ -3134,10 +3134,10 @@
     <row r="61" spans="1:12" ht="15" customHeight="1"/>
     <row r="62" spans="1:12" ht="27" customHeight="1"/>
     <row r="63" spans="1:12" ht="27" customHeight="1"/>
-    <row r="64" spans="1:12" ht="33" customHeight="1"/>
-    <row r="65" spans="1:12" ht="15" customHeight="1"/>
-    <row r="66" spans="1:12" ht="33" customHeight="1"/>
-    <row r="67" spans="1:12" ht="15" customHeight="1"/>
+    <row r="64" spans="1:12" ht="15" customHeight="1"/>
+    <row r="65" spans="1:12" ht="33" customHeight="1"/>
+    <row r="66" spans="1:12" ht="15" customHeight="1"/>
+    <row r="67" spans="1:12" ht="33" customHeight="1"/>
     <row r="68" spans="1:12">
       <c r="A68" s="1"/>
       <c r="B68" s="2" t="s">
@@ -4032,10 +4032,10 @@
     </row>
     <row r="126" spans="1:12" ht="27" customHeight="1"/>
     <row r="127" spans="1:12" ht="27" customHeight="1"/>
-    <row r="128" spans="1:12" ht="33" customHeight="1"/>
-    <row r="129" spans="1:12" ht="15" customHeight="1"/>
-    <row r="130" spans="1:12" ht="33" customHeight="1"/>
-    <row r="131" spans="1:12" ht="15" customHeight="1"/>
+    <row r="128" spans="1:12" ht="15" customHeight="1"/>
+    <row r="129" spans="1:12" ht="33" customHeight="1"/>
+    <row r="130" spans="1:12" ht="15" customHeight="1"/>
+    <row r="131" spans="1:12" ht="33" customHeight="1"/>
     <row r="132" spans="1:12">
       <c r="A132" s="1"/>
       <c r="B132" s="2" t="s">
@@ -4729,8 +4729,9 @@
     </row>
     <row r="187" spans="1:12" ht="30" customHeight="1"/>
     <row r="188" spans="1:12" ht="30" customHeight="1"/>
-    <row r="190" spans="1:12" ht="27" customHeight="1"/>
-    <row r="191" spans="1:12" ht="27" customHeight="1"/>
+    <row r="190" spans="1:12" ht="15" customHeight="1"/>
+    <row r="191" spans="1:12" ht="30" customHeight="1"/>
+    <row r="192" spans="1:12" ht="27" customHeight="1"/>
   </sheetData>
   <mergeCells count="176">
     <mergeCell ref="B178:C178"/>

--- a/templates/Plantilla_Preventivo.xlsx
+++ b/templates/Plantilla_Preventivo.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13FFFCB0-1493-488A-941C-5B8186D15D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6BDA8F7-DF90-43CC-BEAF-1C7AEAD024BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1537,6 +1537,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1552,9 +1579,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1660,24 +1684,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1725,12 +1731,6 @@
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2273,11 +2273,11 @@
         <v>0</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="47"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="55"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2291,7 +2291,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="35"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="160"/>
       <c r="F6" s="160"/>
       <c r="G6" s="2"/>
@@ -2320,69 +2320,69 @@
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="50"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="58"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="52"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="60"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="54"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="62"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="56"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="64"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -2413,9 +2413,9 @@
       <c r="I13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="54"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="62"/>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="1"/>
@@ -2464,20 +2464,20 @@
       <c r="B17" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="94"/>
+      <c r="D17" s="96"/>
       <c r="E17" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="89"/>
+      <c r="F17" s="91"/>
       <c r="G17" s="4"/>
       <c r="H17" s="8"/>
       <c r="I17" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="89"/>
+      <c r="J17" s="91"/>
       <c r="K17" s="4"/>
       <c r="L17" s="40"/>
     </row>
@@ -2486,14 +2486,14 @@
       <c r="B18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="93"/>
-      <c r="D18" s="94"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="96"/>
       <c r="E18" s="147"/>
-      <c r="F18" s="91"/>
+      <c r="F18" s="93"/>
       <c r="G18" s="4"/>
       <c r="H18" s="8"/>
       <c r="I18" s="147"/>
-      <c r="J18" s="91"/>
+      <c r="J18" s="93"/>
       <c r="K18" s="4"/>
       <c r="L18" s="40"/>
     </row>
@@ -2501,7 +2501,7 @@
       <c r="A19" s="1"/>
       <c r="B19" s="9"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="94"/>
+      <c r="D19" s="96"/>
       <c r="E19" s="9"/>
       <c r="F19" s="11"/>
       <c r="G19" s="4"/>
@@ -2517,17 +2517,17 @@
         <v>8</v>
       </c>
       <c r="C20" s="149"/>
-      <c r="D20" s="39"/>
+      <c r="D20" s="48"/>
       <c r="E20" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="89"/>
+      <c r="F20" s="91"/>
       <c r="G20" s="4"/>
       <c r="H20" s="8"/>
       <c r="I20" s="146" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="89"/>
+      <c r="J20" s="91"/>
       <c r="K20" s="4"/>
       <c r="L20" s="40"/>
     </row>
@@ -2536,14 +2536,14 @@
       <c r="B21" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="90"/>
-      <c r="D21" s="39"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="48"/>
       <c r="E21" s="148"/>
-      <c r="F21" s="90"/>
+      <c r="F21" s="92"/>
       <c r="G21" s="4"/>
       <c r="H21" s="8"/>
       <c r="I21" s="148"/>
-      <c r="J21" s="90"/>
+      <c r="J21" s="92"/>
       <c r="K21" s="4"/>
       <c r="L21" s="40"/>
     </row>
@@ -2577,19 +2577,19 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="1"/>
-      <c r="B24" s="86" t="s">
+      <c r="B24" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="87"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="K24" s="87"/>
-      <c r="L24" s="88"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="89"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="90"/>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="1"/>
@@ -2610,54 +2610,54 @@
       <c r="B26" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="81"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="39"/>
       <c r="F26" s="13"/>
-      <c r="G26" s="82" t="s">
+      <c r="G26" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="55"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="95"/>
-      <c r="K26" s="96"/>
-      <c r="L26" s="97"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="97"/>
+      <c r="K26" s="98"/>
+      <c r="L26" s="99"/>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="1"/>
       <c r="B27" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="79"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="81"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="39"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="82" t="s">
+      <c r="G27" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="55"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="85"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="86"/>
+      <c r="L27" s="87"/>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="1"/>
       <c r="B28" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="81"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="39"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="82" t="s">
+      <c r="G28" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="55"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="80"/>
-      <c r="L28" s="48"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="56"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="1"/>
@@ -2678,74 +2678,74 @@
       <c r="B30" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="76"/>
-      <c r="D30" s="76"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="77"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="41"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="1"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="75"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="82"/>
+      <c r="K31" s="82"/>
+      <c r="L31" s="83"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="1"/>
-      <c r="B32" s="78" t="s">
+      <c r="B32" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="76"/>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="76"/>
-      <c r="L32" s="77"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="41"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="1"/>
-      <c r="B33" s="98"/>
-      <c r="C33" s="99"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="99"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="99"/>
-      <c r="L33" s="99"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="1"/>
-      <c r="B34" s="73"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="74"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="74"/>
-      <c r="L34" s="75"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="83"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="1"/>
@@ -2938,14 +2938,14 @@
       </c>
       <c r="C48" s="18"/>
       <c r="D48" s="18"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="69"/>
-      <c r="I48" s="69"/>
-      <c r="J48" s="69"/>
-      <c r="K48" s="69"/>
-      <c r="L48" s="68"/>
+      <c r="E48" s="77"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="77"/>
+      <c r="I48" s="77"/>
+      <c r="J48" s="77"/>
+      <c r="K48" s="77"/>
+      <c r="L48" s="76"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="1"/>
@@ -3005,77 +3005,77 @@
     </row>
     <row r="53" spans="1:12" ht="30" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="43" t="s">
+      <c r="B53" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="43"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="43"/>
-      <c r="I53" s="43"/>
-      <c r="J53" s="43"/>
-      <c r="K53" s="43"/>
-      <c r="L53" s="43"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="51"/>
+      <c r="G53" s="51"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="51"/>
+      <c r="K53" s="51"/>
+      <c r="L53" s="51"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="1"/>
-      <c r="B54" s="67" t="s">
+      <c r="B54" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="68"/>
-      <c r="D54" s="67" t="s">
+      <c r="C54" s="76"/>
+      <c r="D54" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="E54" s="69"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="67" t="s">
+      <c r="E54" s="77"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="H54" s="69"/>
-      <c r="I54" s="69"/>
-      <c r="J54" s="68"/>
-      <c r="K54" s="67" t="s">
+      <c r="H54" s="77"/>
+      <c r="I54" s="77"/>
+      <c r="J54" s="76"/>
+      <c r="K54" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="L54" s="68"/>
+      <c r="L54" s="76"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="1"/>
-      <c r="B55" s="67"/>
-      <c r="C55" s="68"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="69"/>
-      <c r="F55" s="68"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="71"/>
-      <c r="I55" s="71"/>
-      <c r="J55" s="72"/>
-      <c r="K55" s="70"/>
-      <c r="L55" s="72"/>
+      <c r="B55" s="75"/>
+      <c r="C55" s="76"/>
+      <c r="D55" s="75"/>
+      <c r="E55" s="77"/>
+      <c r="F55" s="76"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="79"/>
+      <c r="I55" s="79"/>
+      <c r="J55" s="80"/>
+      <c r="K55" s="78"/>
+      <c r="L55" s="80"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="1"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="68"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="69"/>
-      <c r="F56" s="68"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="71"/>
-      <c r="I56" s="71"/>
-      <c r="J56" s="72"/>
-      <c r="K56" s="70"/>
-      <c r="L56" s="72"/>
+      <c r="B56" s="75"/>
+      <c r="C56" s="76"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="77"/>
+      <c r="F56" s="76"/>
+      <c r="G56" s="78"/>
+      <c r="H56" s="79"/>
+      <c r="I56" s="79"/>
+      <c r="J56" s="80"/>
+      <c r="K56" s="78"/>
+      <c r="L56" s="80"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="1"/>
-      <c r="B57" s="58"/>
-      <c r="C57" s="59"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="59"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="67"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="67"/>
       <c r="G57" s="109"/>
       <c r="H57" s="110"/>
       <c r="I57" s="110"/>
@@ -3084,11 +3084,11 @@
       <c r="L57" s="111"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="B58" s="60"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="60"/>
-      <c r="E58" s="65"/>
-      <c r="F58" s="61"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="69"/>
+      <c r="D58" s="68"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="69"/>
       <c r="G58" s="112"/>
       <c r="H58" s="113"/>
       <c r="I58" s="113"/>
@@ -3097,11 +3097,11 @@
       <c r="L58" s="114"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="B59" s="62"/>
-      <c r="C59" s="63"/>
-      <c r="D59" s="62"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="63"/>
+      <c r="B59" s="70"/>
+      <c r="C59" s="71"/>
+      <c r="D59" s="70"/>
+      <c r="E59" s="74"/>
+      <c r="F59" s="71"/>
       <c r="G59" s="115"/>
       <c r="H59" s="116"/>
       <c r="I59" s="116"/>
@@ -3162,9 +3162,9 @@
         <v>2</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="35"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="44"/>
+      <c r="F69" s="44"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -3191,69 +3191,69 @@
       <c r="B71" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="80"/>
-      <c r="D71" s="80"/>
-      <c r="E71" s="80"/>
-      <c r="F71" s="80"/>
-      <c r="G71" s="80"/>
-      <c r="H71" s="80"/>
-      <c r="I71" s="80"/>
-      <c r="J71" s="80"/>
-      <c r="K71" s="80"/>
-      <c r="L71" s="48"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
+      <c r="J71" s="38"/>
+      <c r="K71" s="38"/>
+      <c r="L71" s="56"/>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="1"/>
       <c r="B72" s="4"/>
-      <c r="C72" s="51"/>
-      <c r="D72" s="51"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="51"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="51"/>
-      <c r="I72" s="51"/>
-      <c r="J72" s="51"/>
-      <c r="K72" s="51"/>
-      <c r="L72" s="52"/>
+      <c r="C72" s="59"/>
+      <c r="D72" s="59"/>
+      <c r="E72" s="59"/>
+      <c r="F72" s="59"/>
+      <c r="G72" s="59"/>
+      <c r="H72" s="59"/>
+      <c r="I72" s="59"/>
+      <c r="J72" s="59"/>
+      <c r="K72" s="59"/>
+      <c r="L72" s="60"/>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="1"/>
       <c r="B73" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C73" s="53"/>
-      <c r="D73" s="53"/>
-      <c r="E73" s="53"/>
-      <c r="F73" s="53"/>
-      <c r="G73" s="53"/>
-      <c r="H73" s="53"/>
-      <c r="I73" s="53"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="53"/>
-      <c r="L73" s="54"/>
+      <c r="C73" s="61"/>
+      <c r="D73" s="61"/>
+      <c r="E73" s="61"/>
+      <c r="F73" s="61"/>
+      <c r="G73" s="61"/>
+      <c r="H73" s="61"/>
+      <c r="I73" s="61"/>
+      <c r="J73" s="61"/>
+      <c r="K73" s="61"/>
+      <c r="L73" s="62"/>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="1"/>
       <c r="B74" s="4"/>
-      <c r="C74" s="55"/>
-      <c r="D74" s="55"/>
-      <c r="E74" s="55"/>
-      <c r="F74" s="55"/>
-      <c r="G74" s="55"/>
-      <c r="H74" s="55"/>
-      <c r="I74" s="55"/>
-      <c r="J74" s="55"/>
-      <c r="K74" s="55"/>
-      <c r="L74" s="56"/>
+      <c r="C74" s="63"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="63"/>
+      <c r="F74" s="63"/>
+      <c r="G74" s="63"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="63"/>
+      <c r="J74" s="63"/>
+      <c r="K74" s="63"/>
+      <c r="L74" s="64"/>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="1"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="57"/>
-      <c r="D75" s="57"/>
-      <c r="E75" s="57"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57"/>
+      <c r="C75" s="65"/>
+      <c r="D75" s="65"/>
+      <c r="E75" s="65"/>
+      <c r="F75" s="65"/>
+      <c r="G75" s="65"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3274,9 +3274,9 @@
       <c r="I76" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J76" s="53"/>
-      <c r="K76" s="53"/>
-      <c r="L76" s="54"/>
+      <c r="J76" s="61"/>
+      <c r="K76" s="61"/>
+      <c r="L76" s="62"/>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="1"/>
@@ -3322,19 +3322,19 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="1"/>
-      <c r="B80" s="67" t="s">
+      <c r="B80" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="C80" s="69"/>
-      <c r="D80" s="69"/>
-      <c r="E80" s="69"/>
-      <c r="F80" s="69"/>
-      <c r="G80" s="69"/>
-      <c r="H80" s="69"/>
-      <c r="I80" s="69"/>
-      <c r="J80" s="69"/>
-      <c r="K80" s="69"/>
-      <c r="L80" s="68"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="77"/>
+      <c r="E80" s="77"/>
+      <c r="F80" s="77"/>
+      <c r="G80" s="77"/>
+      <c r="H80" s="77"/>
+      <c r="I80" s="77"/>
+      <c r="J80" s="77"/>
+      <c r="K80" s="77"/>
+      <c r="L80" s="76"/>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="1"/>
@@ -3355,54 +3355,54 @@
       <c r="B82" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C82" s="79"/>
-      <c r="D82" s="80"/>
-      <c r="E82" s="81"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="39"/>
       <c r="F82" s="13"/>
-      <c r="G82" s="82" t="s">
+      <c r="G82" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="H82" s="55"/>
-      <c r="I82" s="56"/>
-      <c r="J82" s="95"/>
-      <c r="K82" s="96"/>
-      <c r="L82" s="97"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="64"/>
+      <c r="J82" s="97"/>
+      <c r="K82" s="98"/>
+      <c r="L82" s="99"/>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="1"/>
       <c r="B83" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="79"/>
-      <c r="D83" s="80"/>
-      <c r="E83" s="81"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="39"/>
       <c r="F83" s="2"/>
-      <c r="G83" s="82" t="s">
+      <c r="G83" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="H83" s="55"/>
-      <c r="I83" s="56"/>
-      <c r="J83" s="95"/>
-      <c r="K83" s="96"/>
-      <c r="L83" s="97"/>
+      <c r="H83" s="63"/>
+      <c r="I83" s="64"/>
+      <c r="J83" s="97"/>
+      <c r="K83" s="98"/>
+      <c r="L83" s="99"/>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="1"/>
       <c r="B84" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="79"/>
-      <c r="D84" s="80"/>
-      <c r="E84" s="81"/>
+      <c r="C84" s="37"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="39"/>
       <c r="F84" s="8"/>
-      <c r="G84" s="82" t="s">
+      <c r="G84" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="H84" s="55"/>
-      <c r="I84" s="56"/>
-      <c r="J84" s="95"/>
-      <c r="K84" s="96"/>
-      <c r="L84" s="97"/>
+      <c r="H84" s="63"/>
+      <c r="I84" s="64"/>
+      <c r="J84" s="97"/>
+      <c r="K84" s="98"/>
+      <c r="L84" s="99"/>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="1"/>
@@ -3434,21 +3434,21 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="1"/>
-      <c r="B87" s="67" t="s">
+      <c r="B87" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="69"/>
-      <c r="D87" s="69"/>
-      <c r="E87" s="69"/>
-      <c r="F87" s="69"/>
-      <c r="G87" s="69"/>
-      <c r="H87" s="69"/>
-      <c r="I87" s="69"/>
-      <c r="J87" s="68"/>
-      <c r="K87" s="67" t="s">
+      <c r="C87" s="77"/>
+      <c r="D87" s="77"/>
+      <c r="E87" s="77"/>
+      <c r="F87" s="77"/>
+      <c r="G87" s="77"/>
+      <c r="H87" s="77"/>
+      <c r="I87" s="77"/>
+      <c r="J87" s="76"/>
+      <c r="K87" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="L87" s="68"/>
+      <c r="L87" s="76"/>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="1"/>
@@ -3479,7 +3479,7 @@
       <c r="H89" s="134"/>
       <c r="I89" s="134"/>
       <c r="J89" s="135"/>
-      <c r="K89" s="98"/>
+      <c r="K89" s="42"/>
       <c r="L89" s="136"/>
     </row>
     <row r="90" spans="1:12">
@@ -3495,7 +3495,7 @@
       <c r="H90" s="134"/>
       <c r="I90" s="134"/>
       <c r="J90" s="135"/>
-      <c r="K90" s="98"/>
+      <c r="K90" s="42"/>
       <c r="L90" s="136"/>
     </row>
     <row r="91" spans="1:12">
@@ -3511,7 +3511,7 @@
       <c r="H91" s="134"/>
       <c r="I91" s="134"/>
       <c r="J91" s="135"/>
-      <c r="K91" s="98"/>
+      <c r="K91" s="42"/>
       <c r="L91" s="136"/>
     </row>
     <row r="92" spans="1:12">
@@ -3527,7 +3527,7 @@
       <c r="H92" s="134"/>
       <c r="I92" s="134"/>
       <c r="J92" s="135"/>
-      <c r="K92" s="98"/>
+      <c r="K92" s="42"/>
       <c r="L92" s="136"/>
     </row>
     <row r="93" spans="1:12">
@@ -3543,7 +3543,7 @@
       <c r="H93" s="134"/>
       <c r="I93" s="134"/>
       <c r="J93" s="135"/>
-      <c r="K93" s="98"/>
+      <c r="K93" s="42"/>
       <c r="L93" s="136"/>
     </row>
     <row r="94" spans="1:12">
@@ -3559,7 +3559,7 @@
       <c r="H94" s="134"/>
       <c r="I94" s="134"/>
       <c r="J94" s="135"/>
-      <c r="K94" s="98"/>
+      <c r="K94" s="42"/>
       <c r="L94" s="136"/>
     </row>
     <row r="95" spans="1:12">
@@ -3575,7 +3575,7 @@
       <c r="H95" s="134"/>
       <c r="I95" s="134"/>
       <c r="J95" s="135"/>
-      <c r="K95" s="98"/>
+      <c r="K95" s="42"/>
       <c r="L95" s="136"/>
     </row>
     <row r="96" spans="1:12">
@@ -3591,7 +3591,7 @@
       <c r="H96" s="134"/>
       <c r="I96" s="134"/>
       <c r="J96" s="135"/>
-      <c r="K96" s="98"/>
+      <c r="K96" s="42"/>
       <c r="L96" s="136"/>
     </row>
     <row r="97" spans="1:12">
@@ -3607,7 +3607,7 @@
       <c r="H97" s="134"/>
       <c r="I97" s="134"/>
       <c r="J97" s="135"/>
-      <c r="K97" s="98"/>
+      <c r="K97" s="42"/>
       <c r="L97" s="136"/>
     </row>
     <row r="98" spans="1:12">
@@ -3623,7 +3623,7 @@
       <c r="H98" s="134"/>
       <c r="I98" s="134"/>
       <c r="J98" s="135"/>
-      <c r="K98" s="98"/>
+      <c r="K98" s="42"/>
       <c r="L98" s="136"/>
     </row>
     <row r="99" spans="1:12">
@@ -3639,7 +3639,7 @@
       <c r="H99" s="134"/>
       <c r="I99" s="134"/>
       <c r="J99" s="135"/>
-      <c r="K99" s="98"/>
+      <c r="K99" s="42"/>
       <c r="L99" s="136"/>
     </row>
     <row r="100" spans="1:12">
@@ -3655,7 +3655,7 @@
       <c r="H100" s="134"/>
       <c r="I100" s="134"/>
       <c r="J100" s="135"/>
-      <c r="K100" s="98"/>
+      <c r="K100" s="42"/>
       <c r="L100" s="136"/>
     </row>
     <row r="101" spans="1:12">
@@ -3671,7 +3671,7 @@
       <c r="H101" s="134"/>
       <c r="I101" s="134"/>
       <c r="J101" s="135"/>
-      <c r="K101" s="98"/>
+      <c r="K101" s="42"/>
       <c r="L101" s="136"/>
     </row>
     <row r="102" spans="1:12">
@@ -3687,7 +3687,7 @@
       <c r="H102" s="134"/>
       <c r="I102" s="134"/>
       <c r="J102" s="135"/>
-      <c r="K102" s="98"/>
+      <c r="K102" s="42"/>
       <c r="L102" s="136"/>
     </row>
     <row r="103" spans="1:12">
@@ -3703,7 +3703,7 @@
       <c r="H103" s="134"/>
       <c r="I103" s="134"/>
       <c r="J103" s="135"/>
-      <c r="K103" s="98"/>
+      <c r="K103" s="42"/>
       <c r="L103" s="136"/>
     </row>
     <row r="104" spans="1:12">
@@ -3719,7 +3719,7 @@
       <c r="H104" s="134"/>
       <c r="I104" s="134"/>
       <c r="J104" s="135"/>
-      <c r="K104" s="98"/>
+      <c r="K104" s="42"/>
       <c r="L104" s="136"/>
     </row>
     <row r="105" spans="1:12">
@@ -3735,7 +3735,7 @@
       <c r="H105" s="134"/>
       <c r="I105" s="134"/>
       <c r="J105" s="135"/>
-      <c r="K105" s="98"/>
+      <c r="K105" s="42"/>
       <c r="L105" s="136"/>
     </row>
     <row r="106" spans="1:12">
@@ -3751,7 +3751,7 @@
       <c r="H106" s="134"/>
       <c r="I106" s="134"/>
       <c r="J106" s="135"/>
-      <c r="K106" s="98"/>
+      <c r="K106" s="42"/>
       <c r="L106" s="136"/>
     </row>
     <row r="107" spans="1:12">
@@ -3767,7 +3767,7 @@
       <c r="H107" s="134"/>
       <c r="I107" s="134"/>
       <c r="J107" s="135"/>
-      <c r="K107" s="98"/>
+      <c r="K107" s="42"/>
       <c r="L107" s="136"/>
     </row>
     <row r="108" spans="1:12">
@@ -3783,7 +3783,7 @@
       <c r="H108" s="134"/>
       <c r="I108" s="134"/>
       <c r="J108" s="135"/>
-      <c r="K108" s="98"/>
+      <c r="K108" s="42"/>
       <c r="L108" s="136"/>
     </row>
     <row r="109" spans="1:12">
@@ -3799,7 +3799,7 @@
       <c r="H109" s="134"/>
       <c r="I109" s="134"/>
       <c r="J109" s="135"/>
-      <c r="K109" s="98"/>
+      <c r="K109" s="42"/>
       <c r="L109" s="136"/>
     </row>
     <row r="110" spans="1:12">
@@ -3815,7 +3815,7 @@
       <c r="H110" s="134"/>
       <c r="I110" s="134"/>
       <c r="J110" s="135"/>
-      <c r="K110" s="98"/>
+      <c r="K110" s="42"/>
       <c r="L110" s="136"/>
     </row>
     <row r="111" spans="1:12">
@@ -3831,7 +3831,7 @@
       <c r="H111" s="134"/>
       <c r="I111" s="134"/>
       <c r="J111" s="135"/>
-      <c r="K111" s="98"/>
+      <c r="K111" s="42"/>
       <c r="L111" s="136"/>
     </row>
     <row r="112" spans="1:12">
@@ -3847,7 +3847,7 @@
       <c r="H112" s="134"/>
       <c r="I112" s="134"/>
       <c r="J112" s="135"/>
-      <c r="K112" s="98"/>
+      <c r="K112" s="42"/>
       <c r="L112" s="136"/>
     </row>
     <row r="113" spans="1:12">
@@ -3863,7 +3863,7 @@
       <c r="H113" s="134"/>
       <c r="I113" s="134"/>
       <c r="J113" s="135"/>
-      <c r="K113" s="98"/>
+      <c r="K113" s="42"/>
       <c r="L113" s="136"/>
     </row>
     <row r="114" spans="1:12">
@@ -3879,7 +3879,7 @@
       <c r="H114" s="134"/>
       <c r="I114" s="134"/>
       <c r="J114" s="135"/>
-      <c r="K114" s="98"/>
+      <c r="K114" s="42"/>
       <c r="L114" s="136"/>
     </row>
     <row r="115" spans="1:12">
@@ -3895,26 +3895,26 @@
       <c r="H115" s="134"/>
       <c r="I115" s="134"/>
       <c r="J115" s="135"/>
-      <c r="K115" s="98"/>
+      <c r="K115" s="42"/>
       <c r="L115" s="136"/>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" s="1"/>
-      <c r="B116" s="36"/>
-      <c r="C116" s="37"/>
-      <c r="D116" s="37"/>
-      <c r="E116" s="37"/>
-      <c r="F116" s="37"/>
-      <c r="G116" s="37"/>
-      <c r="H116" s="37"/>
-      <c r="I116" s="37"/>
-      <c r="J116" s="38"/>
-      <c r="K116" s="36"/>
-      <c r="L116" s="38"/>
+      <c r="B116" s="45"/>
+      <c r="C116" s="46"/>
+      <c r="D116" s="46"/>
+      <c r="E116" s="46"/>
+      <c r="F116" s="46"/>
+      <c r="G116" s="46"/>
+      <c r="H116" s="46"/>
+      <c r="I116" s="46"/>
+      <c r="J116" s="47"/>
+      <c r="K116" s="45"/>
+      <c r="L116" s="47"/>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" s="1"/>
-      <c r="B117" s="39"/>
+      <c r="B117" s="48"/>
       <c r="C117" s="40"/>
       <c r="D117" s="40"/>
       <c r="E117" s="40"/>
@@ -3922,13 +3922,13 @@
       <c r="G117" s="40"/>
       <c r="H117" s="40"/>
       <c r="I117" s="40"/>
-      <c r="J117" s="41"/>
-      <c r="K117" s="39"/>
-      <c r="L117" s="41"/>
+      <c r="J117" s="49"/>
+      <c r="K117" s="48"/>
+      <c r="L117" s="49"/>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" s="1"/>
-      <c r="B118" s="39"/>
+      <c r="B118" s="48"/>
       <c r="C118" s="40"/>
       <c r="D118" s="40"/>
       <c r="E118" s="40"/>
@@ -3936,23 +3936,23 @@
       <c r="G118" s="40"/>
       <c r="H118" s="40"/>
       <c r="I118" s="40"/>
-      <c r="J118" s="41"/>
-      <c r="K118" s="39"/>
-      <c r="L118" s="41"/>
+      <c r="J118" s="49"/>
+      <c r="K118" s="48"/>
+      <c r="L118" s="49"/>
     </row>
     <row r="119" spans="1:12" ht="45" customHeight="1">
       <c r="A119" s="1"/>
-      <c r="B119" s="42"/>
-      <c r="C119" s="43"/>
-      <c r="D119" s="43"/>
-      <c r="E119" s="43"/>
-      <c r="F119" s="43"/>
-      <c r="G119" s="43"/>
-      <c r="H119" s="43"/>
-      <c r="I119" s="43"/>
-      <c r="J119" s="44"/>
-      <c r="K119" s="42"/>
-      <c r="L119" s="44"/>
+      <c r="B119" s="50"/>
+      <c r="C119" s="51"/>
+      <c r="D119" s="51"/>
+      <c r="E119" s="51"/>
+      <c r="F119" s="51"/>
+      <c r="G119" s="51"/>
+      <c r="H119" s="51"/>
+      <c r="I119" s="51"/>
+      <c r="J119" s="52"/>
+      <c r="K119" s="50"/>
+      <c r="L119" s="52"/>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" s="1"/>
@@ -3970,11 +3970,11 @@
     </row>
     <row r="121" spans="1:12" ht="30" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="58"/>
-      <c r="C121" s="59"/>
-      <c r="D121" s="58"/>
-      <c r="E121" s="64"/>
-      <c r="F121" s="59"/>
+      <c r="B121" s="66"/>
+      <c r="C121" s="67"/>
+      <c r="D121" s="66"/>
+      <c r="E121" s="72"/>
+      <c r="F121" s="67"/>
       <c r="G121" s="109"/>
       <c r="H121" s="110"/>
       <c r="I121" s="110"/>
@@ -3983,11 +3983,11 @@
       <c r="L121" s="111"/>
     </row>
     <row r="122" spans="1:12">
-      <c r="B122" s="60"/>
-      <c r="C122" s="61"/>
-      <c r="D122" s="60"/>
-      <c r="E122" s="65"/>
-      <c r="F122" s="61"/>
+      <c r="B122" s="68"/>
+      <c r="C122" s="69"/>
+      <c r="D122" s="68"/>
+      <c r="E122" s="73"/>
+      <c r="F122" s="69"/>
       <c r="G122" s="112"/>
       <c r="H122" s="113"/>
       <c r="I122" s="113"/>
@@ -3996,11 +3996,11 @@
       <c r="L122" s="114"/>
     </row>
     <row r="123" spans="1:12">
-      <c r="B123" s="62"/>
-      <c r="C123" s="63"/>
-      <c r="D123" s="62"/>
-      <c r="E123" s="66"/>
-      <c r="F123" s="63"/>
+      <c r="B123" s="70"/>
+      <c r="C123" s="71"/>
+      <c r="D123" s="70"/>
+      <c r="E123" s="74"/>
+      <c r="F123" s="71"/>
       <c r="G123" s="115"/>
       <c r="H123" s="116"/>
       <c r="I123" s="116"/>
@@ -4090,11 +4090,11 @@
       <c r="B135" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C135" s="80"/>
-      <c r="D135" s="80"/>
-      <c r="E135" s="80"/>
-      <c r="F135" s="80"/>
-      <c r="G135" s="80"/>
+      <c r="C135" s="38"/>
+      <c r="D135" s="38"/>
+      <c r="E135" s="38"/>
+      <c r="F135" s="38"/>
+      <c r="G135" s="38"/>
       <c r="H135" s="23"/>
       <c r="I135" s="23"/>
       <c r="J135" s="23"/>
@@ -4120,18 +4120,18 @@
       <c r="B137" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C137" s="53"/>
-      <c r="D137" s="53"/>
-      <c r="E137" s="53"/>
-      <c r="F137" s="53"/>
-      <c r="G137" s="53"/>
+      <c r="C137" s="61"/>
+      <c r="D137" s="61"/>
+      <c r="E137" s="61"/>
+      <c r="F137" s="61"/>
+      <c r="G137" s="61"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J137" s="53"/>
-      <c r="K137" s="53"/>
-      <c r="L137" s="54"/>
+      <c r="J137" s="61"/>
+      <c r="K137" s="61"/>
+      <c r="L137" s="62"/>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="1"/>
@@ -4163,19 +4163,19 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="1"/>
-      <c r="B140" s="67" t="s">
+      <c r="B140" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="C140" s="69"/>
-      <c r="D140" s="69"/>
-      <c r="E140" s="69"/>
-      <c r="F140" s="69"/>
-      <c r="G140" s="69"/>
-      <c r="H140" s="69"/>
-      <c r="I140" s="69"/>
-      <c r="J140" s="69"/>
-      <c r="K140" s="69"/>
-      <c r="L140" s="68"/>
+      <c r="C140" s="77"/>
+      <c r="D140" s="77"/>
+      <c r="E140" s="77"/>
+      <c r="F140" s="77"/>
+      <c r="G140" s="77"/>
+      <c r="H140" s="77"/>
+      <c r="I140" s="77"/>
+      <c r="J140" s="77"/>
+      <c r="K140" s="77"/>
+      <c r="L140" s="76"/>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" s="1"/>
@@ -4337,17 +4337,17 @@
         <v>67</v>
       </c>
       <c r="C152" s="40"/>
-      <c r="D152" s="2"/>
-      <c r="E152" s="2"/>
+      <c r="D152" s="40"/>
+      <c r="E152" s="40"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-      <c r="H152" s="2"/>
-      <c r="I152" s="40" t="s">
+      <c r="G152" s="40" t="s">
         <v>68</v>
       </c>
+      <c r="H152" s="40"/>
+      <c r="I152" s="40"/>
       <c r="J152" s="40"/>
-      <c r="K152" s="2"/>
-      <c r="L152" s="2"/>
+      <c r="K152" s="40"/>
+      <c r="L152" s="40"/>
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="1"/>
@@ -4750,8 +4750,6 @@
     <mergeCell ref="D175:F177"/>
     <mergeCell ref="G175:J177"/>
     <mergeCell ref="K175:L177"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="I152:J152"/>
     <mergeCell ref="B156:C162"/>
     <mergeCell ref="D156:F162"/>
     <mergeCell ref="H156:L162"/>
@@ -4819,8 +4817,6 @@
     <mergeCell ref="K97:L97"/>
     <mergeCell ref="B98:J98"/>
     <mergeCell ref="K98:L98"/>
-    <mergeCell ref="B93:J93"/>
-    <mergeCell ref="K93:L93"/>
     <mergeCell ref="B94:J94"/>
     <mergeCell ref="K94:L94"/>
     <mergeCell ref="B95:J95"/>
@@ -4831,10 +4827,6 @@
     <mergeCell ref="K91:L91"/>
     <mergeCell ref="B92:J92"/>
     <mergeCell ref="K92:L92"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="B88:J88"/>
-    <mergeCell ref="K88:L88"/>
     <mergeCell ref="B89:J89"/>
     <mergeCell ref="K89:L89"/>
     <mergeCell ref="C83:E83"/>
@@ -4843,9 +4835,17 @@
     <mergeCell ref="C84:E84"/>
     <mergeCell ref="G84:I84"/>
     <mergeCell ref="J84:L84"/>
-    <mergeCell ref="B36:L46"/>
-    <mergeCell ref="E48:L48"/>
-    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="B93:J93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="B53:L53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="B88:J88"/>
+    <mergeCell ref="K88:L88"/>
     <mergeCell ref="C75:G75"/>
     <mergeCell ref="J76:L76"/>
     <mergeCell ref="B80:L80"/>
@@ -4862,33 +4862,6 @@
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="K60:L60"/>
-    <mergeCell ref="B53:L53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="G54:J54"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="B24:L24"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="D32:L32"/>
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="B116:J119"/>
-    <mergeCell ref="K116:L119"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="C8:L8"/>
     <mergeCell ref="C9:L10"/>
@@ -4908,8 +4881,35 @@
     <mergeCell ref="K55:L55"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="B31:L31"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="D20:D22"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="C27:E27"/>
+    <mergeCell ref="B152:E152"/>
+    <mergeCell ref="G152:L152"/>
+    <mergeCell ref="D32:L32"/>
+    <mergeCell ref="B33:L33"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="B116:J119"/>
+    <mergeCell ref="K116:L119"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="B24:L24"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="B36:L46"/>
+    <mergeCell ref="E48:L48"/>
+    <mergeCell ref="C74:L74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>

--- a/templates/Plantilla_Preventivo.xlsx
+++ b/templates/Plantilla_Preventivo.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6BDA8F7-DF90-43CC-BEAF-1C7AEAD024BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4E2C88A-0712-4AA2-854F-3F4F4214B47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,12 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
   <si>
     <t xml:space="preserve">Orden/Reporte de Servicio </t>
-  </si>
-  <si>
-    <t>MHOS-SSM-EL-0001</t>
   </si>
   <si>
     <t>Fecha</t>
@@ -246,6 +243,9 @@
   </si>
   <si>
     <t>Sello de la Unidad</t>
+  </si>
+  <si>
+    <t>MHOS-SSM-EL-0001</t>
   </si>
   <si>
     <t>Rutina de anexo técnico</t>
@@ -2273,9 +2273,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="53" t="s">
-        <v>1</v>
-      </c>
+      <c r="D5" s="53"/>
       <c r="E5" s="54"/>
       <c r="F5" s="55"/>
       <c r="G5" s="2"/>
@@ -2288,7 +2286,7 @@
     <row r="6" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="44"/>
@@ -2318,7 +2316,7 @@
     <row r="8" spans="1:12">
       <c r="A8" s="1"/>
       <c r="B8" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="56"/>
       <c r="D8" s="57"/>
@@ -2348,7 +2346,7 @@
     <row r="10" spans="1:12">
       <c r="A10" s="1"/>
       <c r="B10" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="61"/>
       <c r="D10" s="61"/>
@@ -2392,26 +2390,26 @@
     <row r="13" spans="1:12">
       <c r="A13" s="1"/>
       <c r="B13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>6</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J13" s="61"/>
       <c r="K13" s="61"/>
@@ -2462,20 +2460,20 @@
     <row r="17" spans="1:12">
       <c r="A17" s="1"/>
       <c r="B17" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="94" t="s">
         <v>8</v>
-      </c>
-      <c r="C17" s="94" t="s">
-        <v>9</v>
       </c>
       <c r="D17" s="96"/>
       <c r="E17" s="146" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" s="91"/>
       <c r="G17" s="4"/>
       <c r="H17" s="8"/>
       <c r="I17" s="146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="91"/>
       <c r="K17" s="4"/>
@@ -2484,7 +2482,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="1"/>
       <c r="B18" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="95"/>
       <c r="D18" s="96"/>
@@ -2514,18 +2512,18 @@
     <row r="20" spans="1:12">
       <c r="A20" s="1"/>
       <c r="B20" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="149"/>
       <c r="D20" s="48"/>
       <c r="E20" s="146" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" s="91"/>
       <c r="G20" s="4"/>
       <c r="H20" s="8"/>
       <c r="I20" s="146" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J20" s="91"/>
       <c r="K20" s="4"/>
@@ -2534,7 +2532,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="1"/>
       <c r="B21" s="32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="92"/>
       <c r="D21" s="48"/>
@@ -2578,7 +2576,7 @@
     <row r="24" spans="1:12">
       <c r="A24" s="1"/>
       <c r="B24" s="88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" s="89"/>
       <c r="D24" s="89"/>
@@ -2608,14 +2606,14 @@
     <row r="26" spans="1:12">
       <c r="A26" s="1"/>
       <c r="B26" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="37"/>
       <c r="D26" s="38"/>
       <c r="E26" s="39"/>
       <c r="F26" s="13"/>
       <c r="G26" s="84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H26" s="63"/>
       <c r="I26" s="64"/>
@@ -2626,14 +2624,14 @@
     <row r="27" spans="1:12">
       <c r="A27" s="1"/>
       <c r="B27" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="38"/>
       <c r="E27" s="39"/>
       <c r="F27" s="2"/>
       <c r="G27" s="84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H27" s="63"/>
       <c r="I27" s="64"/>
@@ -2644,14 +2642,14 @@
     <row r="28" spans="1:12">
       <c r="A28" s="1"/>
       <c r="B28" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="38"/>
       <c r="E28" s="39"/>
       <c r="F28" s="8"/>
       <c r="G28" s="84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H28" s="63"/>
       <c r="I28" s="64"/>
@@ -2676,7 +2674,7 @@
     <row r="30" spans="1:12">
       <c r="A30" s="1"/>
       <c r="B30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" s="36"/>
       <c r="D30" s="36"/>
@@ -2706,7 +2704,7 @@
     <row r="32" spans="1:12">
       <c r="A32" s="1"/>
       <c r="B32" s="35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" s="36"/>
       <c r="D32" s="36"/>
@@ -2764,7 +2762,7 @@
     <row r="36" spans="1:12">
       <c r="A36" s="1"/>
       <c r="B36" s="100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C36" s="101"/>
       <c r="D36" s="101"/>
@@ -2934,7 +2932,7 @@
     <row r="48" spans="1:12">
       <c r="A48" s="1"/>
       <c r="B48" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C48" s="18"/>
       <c r="D48" s="18"/>
@@ -3006,7 +3004,7 @@
     <row r="53" spans="1:12" ht="30" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C53" s="51"/>
       <c r="D53" s="51"/>
@@ -3022,22 +3020,22 @@
     <row r="54" spans="1:12">
       <c r="A54" s="1"/>
       <c r="B54" s="75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C54" s="76"/>
       <c r="D54" s="75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E54" s="77"/>
       <c r="F54" s="76"/>
       <c r="G54" s="75" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H54" s="77"/>
       <c r="I54" s="77"/>
       <c r="J54" s="76"/>
       <c r="K54" s="75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L54" s="76"/>
     </row>
@@ -3112,22 +3110,22 @@
     <row r="60" spans="1:12" s="34" customFormat="1" ht="90.75" customHeight="1">
       <c r="A60" s="33"/>
       <c r="B60" s="123" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C60" s="124"/>
       <c r="D60" s="123" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E60" s="125"/>
       <c r="F60" s="124"/>
       <c r="G60" s="123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H60" s="125"/>
       <c r="I60" s="125"/>
       <c r="J60" s="124"/>
       <c r="K60" s="126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L60" s="127"/>
     </row>
@@ -3145,7 +3143,7 @@
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="120" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="E68" s="121"/>
       <c r="F68" s="122"/>
@@ -3159,7 +3157,7 @@
     <row r="69" spans="1:12">
       <c r="A69" s="1"/>
       <c r="B69" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="44"/>
@@ -3189,7 +3187,7 @@
     <row r="71" spans="1:12">
       <c r="A71" s="1"/>
       <c r="B71" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71" s="38"/>
       <c r="D71" s="38"/>
@@ -3219,7 +3217,7 @@
     <row r="73" spans="1:12">
       <c r="A73" s="1"/>
       <c r="B73" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73" s="61"/>
       <c r="D73" s="61"/>
@@ -3263,7 +3261,7 @@
     <row r="76" spans="1:12">
       <c r="A76" s="1"/>
       <c r="B76" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="26"/>
@@ -3272,7 +3270,7 @@
       <c r="G76" s="27"/>
       <c r="H76" s="5"/>
       <c r="I76" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J76" s="61"/>
       <c r="K76" s="61"/>
@@ -3323,7 +3321,7 @@
     <row r="80" spans="1:12">
       <c r="A80" s="1"/>
       <c r="B80" s="75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C80" s="77"/>
       <c r="D80" s="77"/>
@@ -3353,14 +3351,14 @@
     <row r="82" spans="1:12">
       <c r="A82" s="1"/>
       <c r="B82" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C82" s="37"/>
       <c r="D82" s="38"/>
       <c r="E82" s="39"/>
       <c r="F82" s="13"/>
       <c r="G82" s="84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H82" s="63"/>
       <c r="I82" s="64"/>
@@ -3371,14 +3369,14 @@
     <row r="83" spans="1:12">
       <c r="A83" s="1"/>
       <c r="B83" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C83" s="37"/>
       <c r="D83" s="38"/>
       <c r="E83" s="39"/>
       <c r="F83" s="2"/>
       <c r="G83" s="84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H83" s="63"/>
       <c r="I83" s="64"/>
@@ -3389,14 +3387,14 @@
     <row r="84" spans="1:12">
       <c r="A84" s="1"/>
       <c r="B84" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="38"/>
       <c r="E84" s="39"/>
       <c r="F84" s="8"/>
       <c r="G84" s="84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H84" s="63"/>
       <c r="I84" s="64"/>
@@ -4011,22 +4009,22 @@
     <row r="124" spans="1:12" s="31" customFormat="1" ht="47.25" customHeight="1">
       <c r="A124" s="25"/>
       <c r="B124" s="137" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C124" s="138"/>
       <c r="D124" s="123" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E124" s="125"/>
       <c r="F124" s="124"/>
       <c r="G124" s="123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H124" s="125"/>
       <c r="I124" s="125"/>
       <c r="J124" s="124"/>
       <c r="K124" s="123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L124" s="124"/>
     </row>
@@ -4058,7 +4056,7 @@
     <row r="133" spans="1:12">
       <c r="A133" s="1"/>
       <c r="B133" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="139"/>
@@ -4088,7 +4086,7 @@
     <row r="135" spans="1:12">
       <c r="A135" s="1"/>
       <c r="B135" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C135" s="38"/>
       <c r="D135" s="38"/>
@@ -4118,7 +4116,7 @@
     <row r="137" spans="1:12">
       <c r="A137" s="1"/>
       <c r="B137" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C137" s="61"/>
       <c r="D137" s="61"/>
@@ -4127,7 +4125,7 @@
       <c r="G137" s="61"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J137" s="61"/>
       <c r="K137" s="61"/>
@@ -4708,11 +4706,11 @@
     <row r="178" spans="1:12">
       <c r="A178" s="25"/>
       <c r="B178" s="137" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C178" s="138"/>
       <c r="D178" s="123" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E178" s="125"/>
       <c r="F178" s="124"/>
@@ -4723,7 +4721,7 @@
       <c r="I178" s="144"/>
       <c r="J178" s="145"/>
       <c r="K178" s="120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L178" s="122"/>
     </row>
@@ -4733,7 +4731,7 @@
     <row r="191" spans="1:12" ht="30" customHeight="1"/>
     <row r="192" spans="1:12" ht="27" customHeight="1"/>
   </sheetData>
-  <mergeCells count="176">
+  <mergeCells count="177">
     <mergeCell ref="B178:C178"/>
     <mergeCell ref="D178:F178"/>
     <mergeCell ref="G178:J178"/>
@@ -4750,12 +4748,13 @@
     <mergeCell ref="D175:F177"/>
     <mergeCell ref="G175:J177"/>
     <mergeCell ref="K175:L177"/>
-    <mergeCell ref="B156:C162"/>
     <mergeCell ref="D156:F162"/>
     <mergeCell ref="H156:L162"/>
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="I163:J163"/>
     <mergeCell ref="B140:L140"/>
+    <mergeCell ref="B156:B162"/>
+    <mergeCell ref="C156:C162"/>
     <mergeCell ref="B143:B150"/>
     <mergeCell ref="C143:D150"/>
     <mergeCell ref="E143:F150"/>

--- a/templates/Plantilla_Preventivo.xlsx
+++ b/templates/Plantilla_Preventivo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4E2C88A-0712-4AA2-854F-3F4F4214B47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDD56DA4-7A03-4F04-A895-0D2F7C2456B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1473,7 +1473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1537,6 +1537,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1852,9 +1856,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1909,10 +1910,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2269,13 +2268,6 @@
     <row r="3" spans="1:12" ht="30" customHeight="1"/>
     <row r="5" spans="1:12">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="55"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2286,12 +2278,12 @@
     <row r="6" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="160"/>
-      <c r="F6" s="160"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="57"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -2301,11 +2293,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -2318,69 +2312,69 @@
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="60"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="59"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="60"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="62"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1"/>
       <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="62"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="64"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="66"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -2411,9 +2405,9 @@
       <c r="I13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="62"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="64"/>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="1"/>
@@ -2462,44 +2456,44 @@
       <c r="B17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="96"/>
-      <c r="E17" s="146" t="s">
+      <c r="D17" s="98"/>
+      <c r="E17" s="147" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="91"/>
+      <c r="F17" s="93"/>
       <c r="G17" s="4"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="146" t="s">
+      <c r="I17" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="J17" s="91"/>
+      <c r="J17" s="93"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="40"/>
+      <c r="L17" s="42"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="1"/>
       <c r="B18" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="95"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="93"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="148"/>
+      <c r="F18" s="95"/>
       <c r="G18" s="4"/>
       <c r="H18" s="8"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="93"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="95"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="40"/>
+      <c r="L18" s="42"/>
     </row>
     <row r="19" spans="1:12" ht="15" hidden="1" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="9"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="96"/>
+      <c r="D19" s="98"/>
       <c r="E19" s="9"/>
       <c r="F19" s="11"/>
       <c r="G19" s="4"/>
@@ -2514,42 +2508,42 @@
       <c r="B20" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="149"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="146" t="s">
+      <c r="C20" s="150"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="91"/>
+      <c r="F20" s="93"/>
       <c r="G20" s="4"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="146" t="s">
+      <c r="I20" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="91"/>
+      <c r="J20" s="93"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="40"/>
+      <c r="L20" s="42"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="1"/>
       <c r="B21" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="92"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="92"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="94"/>
       <c r="G21" s="4"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="148"/>
-      <c r="J21" s="92"/>
+      <c r="I21" s="149"/>
+      <c r="J21" s="94"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="40"/>
+      <c r="L21" s="42"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="40"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -2575,19 +2569,19 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="1"/>
-      <c r="B24" s="88" t="s">
+      <c r="B24" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="90"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="91"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="92"/>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="1"/>
@@ -2608,54 +2602,54 @@
       <c r="B26" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="41"/>
       <c r="F26" s="13"/>
-      <c r="G26" s="84" t="s">
+      <c r="G26" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="63"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="98"/>
-      <c r="L26" s="99"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="101"/>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="1"/>
       <c r="B27" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="41"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="84" t="s">
+      <c r="G27" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="H27" s="63"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="87"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="87"/>
+      <c r="K27" s="88"/>
+      <c r="L27" s="89"/>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="1"/>
       <c r="B28" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="41"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="84" t="s">
+      <c r="G28" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="63"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="56"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="58"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="1"/>
@@ -2676,74 +2670,74 @@
       <c r="B30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="41"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="43"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="1"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="82"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="82"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="82"/>
-      <c r="H31" s="82"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="82"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="83"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="85"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="1"/>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="41"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="43"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="1"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="43"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="1"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="82"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="82"/>
-      <c r="H34" s="82"/>
-      <c r="I34" s="82"/>
-      <c r="J34" s="82"/>
-      <c r="K34" s="82"/>
-      <c r="L34" s="83"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="84"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="85"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="1"/>
@@ -2761,159 +2755,159 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="1"/>
-      <c r="B36" s="100" t="s">
+      <c r="B36" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="101"/>
-      <c r="D36" s="101"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="101"/>
-      <c r="G36" s="101"/>
-      <c r="H36" s="101"/>
-      <c r="I36" s="101"/>
-      <c r="J36" s="101"/>
-      <c r="K36" s="101"/>
-      <c r="L36" s="102"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="103"/>
+      <c r="J36" s="103"/>
+      <c r="K36" s="103"/>
+      <c r="L36" s="104"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="104"/>
-      <c r="D37" s="104"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="104"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="105"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="107"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="1"/>
-      <c r="B38" s="103"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="104"/>
-      <c r="E38" s="104"/>
-      <c r="F38" s="104"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="105"/>
+      <c r="B38" s="105"/>
+      <c r="C38" s="106"/>
+      <c r="D38" s="106"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="106"/>
+      <c r="H38" s="106"/>
+      <c r="I38" s="106"/>
+      <c r="J38" s="106"/>
+      <c r="K38" s="106"/>
+      <c r="L38" s="107"/>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="1"/>
-      <c r="B39" s="103"/>
-      <c r="C39" s="104"/>
-      <c r="D39" s="104"/>
-      <c r="E39" s="104"/>
-      <c r="F39" s="104"/>
-      <c r="G39" s="104"/>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="104"/>
-      <c r="K39" s="104"/>
-      <c r="L39" s="105"/>
+      <c r="B39" s="105"/>
+      <c r="C39" s="106"/>
+      <c r="D39" s="106"/>
+      <c r="E39" s="106"/>
+      <c r="F39" s="106"/>
+      <c r="G39" s="106"/>
+      <c r="H39" s="106"/>
+      <c r="I39" s="106"/>
+      <c r="J39" s="106"/>
+      <c r="K39" s="106"/>
+      <c r="L39" s="107"/>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="1"/>
-      <c r="B40" s="103"/>
-      <c r="C40" s="104"/>
-      <c r="D40" s="104"/>
-      <c r="E40" s="104"/>
-      <c r="F40" s="104"/>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="105"/>
+      <c r="B40" s="105"/>
+      <c r="C40" s="106"/>
+      <c r="D40" s="106"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="106"/>
+      <c r="G40" s="106"/>
+      <c r="H40" s="106"/>
+      <c r="I40" s="106"/>
+      <c r="J40" s="106"/>
+      <c r="K40" s="106"/>
+      <c r="L40" s="107"/>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="1"/>
-      <c r="B41" s="103"/>
-      <c r="C41" s="104"/>
-      <c r="D41" s="104"/>
-      <c r="E41" s="104"/>
-      <c r="F41" s="104"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="104"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="104"/>
-      <c r="K41" s="104"/>
-      <c r="L41" s="105"/>
+      <c r="B41" s="105"/>
+      <c r="C41" s="106"/>
+      <c r="D41" s="106"/>
+      <c r="E41" s="106"/>
+      <c r="F41" s="106"/>
+      <c r="G41" s="106"/>
+      <c r="H41" s="106"/>
+      <c r="I41" s="106"/>
+      <c r="J41" s="106"/>
+      <c r="K41" s="106"/>
+      <c r="L41" s="107"/>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="1"/>
-      <c r="B42" s="103"/>
-      <c r="C42" s="104"/>
-      <c r="D42" s="104"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="104"/>
-      <c r="L42" s="105"/>
+      <c r="B42" s="105"/>
+      <c r="C42" s="106"/>
+      <c r="D42" s="106"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="106"/>
+      <c r="G42" s="106"/>
+      <c r="H42" s="106"/>
+      <c r="I42" s="106"/>
+      <c r="J42" s="106"/>
+      <c r="K42" s="106"/>
+      <c r="L42" s="107"/>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="1"/>
-      <c r="B43" s="103"/>
-      <c r="C43" s="104"/>
-      <c r="D43" s="104"/>
-      <c r="E43" s="104"/>
-      <c r="F43" s="104"/>
-      <c r="G43" s="104"/>
-      <c r="H43" s="104"/>
-      <c r="I43" s="104"/>
-      <c r="J43" s="104"/>
-      <c r="K43" s="104"/>
-      <c r="L43" s="105"/>
+      <c r="B43" s="105"/>
+      <c r="C43" s="106"/>
+      <c r="D43" s="106"/>
+      <c r="E43" s="106"/>
+      <c r="F43" s="106"/>
+      <c r="G43" s="106"/>
+      <c r="H43" s="106"/>
+      <c r="I43" s="106"/>
+      <c r="J43" s="106"/>
+      <c r="K43" s="106"/>
+      <c r="L43" s="107"/>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="1"/>
-      <c r="B44" s="103"/>
-      <c r="C44" s="104"/>
-      <c r="D44" s="104"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="104"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="104"/>
-      <c r="K44" s="104"/>
-      <c r="L44" s="105"/>
+      <c r="B44" s="105"/>
+      <c r="C44" s="106"/>
+      <c r="D44" s="106"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="106"/>
+      <c r="H44" s="106"/>
+      <c r="I44" s="106"/>
+      <c r="J44" s="106"/>
+      <c r="K44" s="106"/>
+      <c r="L44" s="107"/>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="1"/>
-      <c r="B45" s="103"/>
-      <c r="C45" s="104"/>
-      <c r="D45" s="104"/>
-      <c r="E45" s="104"/>
-      <c r="F45" s="104"/>
-      <c r="G45" s="104"/>
-      <c r="H45" s="104"/>
-      <c r="I45" s="104"/>
-      <c r="J45" s="104"/>
-      <c r="K45" s="104"/>
-      <c r="L45" s="105"/>
+      <c r="B45" s="105"/>
+      <c r="C45" s="106"/>
+      <c r="D45" s="106"/>
+      <c r="E45" s="106"/>
+      <c r="F45" s="106"/>
+      <c r="G45" s="106"/>
+      <c r="H45" s="106"/>
+      <c r="I45" s="106"/>
+      <c r="J45" s="106"/>
+      <c r="K45" s="106"/>
+      <c r="L45" s="107"/>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="1"/>
-      <c r="B46" s="106"/>
-      <c r="C46" s="107"/>
-      <c r="D46" s="107"/>
-      <c r="E46" s="107"/>
-      <c r="F46" s="107"/>
-      <c r="G46" s="107"/>
-      <c r="H46" s="107"/>
-      <c r="I46" s="107"/>
-      <c r="J46" s="107"/>
-      <c r="K46" s="107"/>
-      <c r="L46" s="108"/>
+      <c r="B46" s="108"/>
+      <c r="C46" s="109"/>
+      <c r="D46" s="109"/>
+      <c r="E46" s="109"/>
+      <c r="F46" s="109"/>
+      <c r="G46" s="109"/>
+      <c r="H46" s="109"/>
+      <c r="I46" s="109"/>
+      <c r="J46" s="109"/>
+      <c r="K46" s="109"/>
+      <c r="L46" s="110"/>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="1"/>
@@ -2936,14 +2930,14 @@
       </c>
       <c r="C48" s="18"/>
       <c r="D48" s="18"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="77"/>
-      <c r="I48" s="77"/>
-      <c r="J48" s="77"/>
-      <c r="K48" s="77"/>
-      <c r="L48" s="76"/>
+      <c r="E48" s="79"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="79"/>
+      <c r="H48" s="79"/>
+      <c r="I48" s="79"/>
+      <c r="J48" s="79"/>
+      <c r="K48" s="79"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="1"/>
@@ -3003,131 +2997,131 @@
     </row>
     <row r="53" spans="1:12" ht="30" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="51" t="s">
+      <c r="B53" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="51"/>
-      <c r="G53" s="51"/>
-      <c r="H53" s="51"/>
-      <c r="I53" s="51"/>
-      <c r="J53" s="51"/>
-      <c r="K53" s="51"/>
-      <c r="L53" s="51"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="53"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="1"/>
-      <c r="B54" s="75" t="s">
+      <c r="B54" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C54" s="76"/>
-      <c r="D54" s="75" t="s">
+      <c r="C54" s="78"/>
+      <c r="D54" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="E54" s="77"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="75" t="s">
+      <c r="E54" s="79"/>
+      <c r="F54" s="78"/>
+      <c r="G54" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="H54" s="77"/>
-      <c r="I54" s="77"/>
-      <c r="J54" s="76"/>
-      <c r="K54" s="75" t="s">
+      <c r="H54" s="79"/>
+      <c r="I54" s="79"/>
+      <c r="J54" s="78"/>
+      <c r="K54" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="L54" s="76"/>
+      <c r="L54" s="78"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="1"/>
-      <c r="B55" s="75"/>
-      <c r="C55" s="76"/>
-      <c r="D55" s="75"/>
-      <c r="E55" s="77"/>
-      <c r="F55" s="76"/>
-      <c r="G55" s="78"/>
-      <c r="H55" s="79"/>
-      <c r="I55" s="79"/>
-      <c r="J55" s="80"/>
-      <c r="K55" s="78"/>
-      <c r="L55" s="80"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="77"/>
+      <c r="E55" s="79"/>
+      <c r="F55" s="78"/>
+      <c r="G55" s="80"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="82"/>
+      <c r="K55" s="80"/>
+      <c r="L55" s="82"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="1"/>
-      <c r="B56" s="75"/>
-      <c r="C56" s="76"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="77"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="78"/>
-      <c r="H56" s="79"/>
-      <c r="I56" s="79"/>
-      <c r="J56" s="80"/>
-      <c r="K56" s="78"/>
-      <c r="L56" s="80"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="78"/>
+      <c r="D56" s="77"/>
+      <c r="E56" s="79"/>
+      <c r="F56" s="78"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="82"/>
+      <c r="K56" s="80"/>
+      <c r="L56" s="82"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="1"/>
-      <c r="B57" s="66"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="109"/>
-      <c r="H57" s="110"/>
-      <c r="I57" s="110"/>
-      <c r="J57" s="111"/>
-      <c r="K57" s="109"/>
-      <c r="L57" s="111"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="68"/>
+      <c r="E57" s="74"/>
+      <c r="F57" s="69"/>
+      <c r="G57" s="111"/>
+      <c r="H57" s="112"/>
+      <c r="I57" s="112"/>
+      <c r="J57" s="113"/>
+      <c r="K57" s="111"/>
+      <c r="L57" s="113"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="B58" s="68"/>
-      <c r="C58" s="69"/>
-      <c r="D58" s="68"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="69"/>
-      <c r="G58" s="112"/>
-      <c r="H58" s="113"/>
-      <c r="I58" s="113"/>
-      <c r="J58" s="114"/>
-      <c r="K58" s="112"/>
-      <c r="L58" s="114"/>
+      <c r="B58" s="70"/>
+      <c r="C58" s="71"/>
+      <c r="D58" s="70"/>
+      <c r="E58" s="75"/>
+      <c r="F58" s="71"/>
+      <c r="G58" s="114"/>
+      <c r="H58" s="115"/>
+      <c r="I58" s="115"/>
+      <c r="J58" s="116"/>
+      <c r="K58" s="114"/>
+      <c r="L58" s="116"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="B59" s="70"/>
-      <c r="C59" s="71"/>
-      <c r="D59" s="70"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="71"/>
-      <c r="G59" s="115"/>
-      <c r="H59" s="116"/>
-      <c r="I59" s="116"/>
-      <c r="J59" s="117"/>
-      <c r="K59" s="118"/>
-      <c r="L59" s="119"/>
+      <c r="B59" s="72"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="72"/>
+      <c r="E59" s="76"/>
+      <c r="F59" s="73"/>
+      <c r="G59" s="117"/>
+      <c r="H59" s="118"/>
+      <c r="I59" s="118"/>
+      <c r="J59" s="119"/>
+      <c r="K59" s="120"/>
+      <c r="L59" s="121"/>
     </row>
     <row r="60" spans="1:12" s="34" customFormat="1" ht="90.75" customHeight="1">
       <c r="A60" s="33"/>
-      <c r="B60" s="123" t="s">
+      <c r="B60" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="124"/>
-      <c r="D60" s="123" t="s">
+      <c r="C60" s="126"/>
+      <c r="D60" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="E60" s="125"/>
-      <c r="F60" s="124"/>
-      <c r="G60" s="123" t="s">
+      <c r="E60" s="127"/>
+      <c r="F60" s="126"/>
+      <c r="G60" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="H60" s="125"/>
-      <c r="I60" s="125"/>
-      <c r="J60" s="124"/>
-      <c r="K60" s="126" t="s">
+      <c r="H60" s="127"/>
+      <c r="I60" s="127"/>
+      <c r="J60" s="126"/>
+      <c r="K60" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="L60" s="127"/>
+      <c r="L60" s="129"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1"/>
     <row r="62" spans="1:12" ht="27" customHeight="1"/>
@@ -3142,11 +3136,11 @@
         <v>0</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="120" t="s">
+      <c r="D68" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="E68" s="121"/>
-      <c r="F68" s="122"/>
+      <c r="E68" s="123"/>
+      <c r="F68" s="124"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -3160,9 +3154,9 @@
         <v>1</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="44"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="44"/>
+      <c r="D69" s="46"/>
+      <c r="E69" s="46"/>
+      <c r="F69" s="46"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -3189,69 +3183,69 @@
       <c r="B71" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C71" s="38"/>
-      <c r="D71" s="38"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="38"/>
-      <c r="H71" s="38"/>
-      <c r="I71" s="38"/>
-      <c r="J71" s="38"/>
-      <c r="K71" s="38"/>
-      <c r="L71" s="56"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="40"/>
+      <c r="I71" s="40"/>
+      <c r="J71" s="40"/>
+      <c r="K71" s="40"/>
+      <c r="L71" s="58"/>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="1"/>
       <c r="B72" s="4"/>
-      <c r="C72" s="59"/>
-      <c r="D72" s="59"/>
-      <c r="E72" s="59"/>
-      <c r="F72" s="59"/>
-      <c r="G72" s="59"/>
-      <c r="H72" s="59"/>
-      <c r="I72" s="59"/>
-      <c r="J72" s="59"/>
-      <c r="K72" s="59"/>
-      <c r="L72" s="60"/>
+      <c r="C72" s="61"/>
+      <c r="D72" s="61"/>
+      <c r="E72" s="61"/>
+      <c r="F72" s="61"/>
+      <c r="G72" s="61"/>
+      <c r="H72" s="61"/>
+      <c r="I72" s="61"/>
+      <c r="J72" s="61"/>
+      <c r="K72" s="61"/>
+      <c r="L72" s="62"/>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="1"/>
       <c r="B73" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C73" s="61"/>
-      <c r="D73" s="61"/>
-      <c r="E73" s="61"/>
-      <c r="F73" s="61"/>
-      <c r="G73" s="61"/>
-      <c r="H73" s="61"/>
-      <c r="I73" s="61"/>
-      <c r="J73" s="61"/>
-      <c r="K73" s="61"/>
-      <c r="L73" s="62"/>
+      <c r="C73" s="63"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="63"/>
+      <c r="F73" s="63"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="63"/>
+      <c r="J73" s="63"/>
+      <c r="K73" s="63"/>
+      <c r="L73" s="64"/>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="1"/>
       <c r="B74" s="4"/>
-      <c r="C74" s="63"/>
-      <c r="D74" s="63"/>
-      <c r="E74" s="63"/>
-      <c r="F74" s="63"/>
-      <c r="G74" s="63"/>
-      <c r="H74" s="63"/>
-      <c r="I74" s="63"/>
-      <c r="J74" s="63"/>
-      <c r="K74" s="63"/>
-      <c r="L74" s="64"/>
+      <c r="C74" s="65"/>
+      <c r="D74" s="65"/>
+      <c r="E74" s="65"/>
+      <c r="F74" s="65"/>
+      <c r="G74" s="65"/>
+      <c r="H74" s="65"/>
+      <c r="I74" s="65"/>
+      <c r="J74" s="65"/>
+      <c r="K74" s="65"/>
+      <c r="L74" s="66"/>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="1"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="65"/>
-      <c r="D75" s="65"/>
-      <c r="E75" s="65"/>
-      <c r="F75" s="65"/>
-      <c r="G75" s="65"/>
+      <c r="C75" s="67"/>
+      <c r="D75" s="67"/>
+      <c r="E75" s="67"/>
+      <c r="F75" s="67"/>
+      <c r="G75" s="67"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3272,9 +3266,9 @@
       <c r="I76" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J76" s="61"/>
-      <c r="K76" s="61"/>
-      <c r="L76" s="62"/>
+      <c r="J76" s="63"/>
+      <c r="K76" s="63"/>
+      <c r="L76" s="64"/>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="1"/>
@@ -3320,19 +3314,19 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="1"/>
-      <c r="B80" s="75" t="s">
+      <c r="B80" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="77"/>
-      <c r="D80" s="77"/>
-      <c r="E80" s="77"/>
-      <c r="F80" s="77"/>
-      <c r="G80" s="77"/>
-      <c r="H80" s="77"/>
-      <c r="I80" s="77"/>
-      <c r="J80" s="77"/>
-      <c r="K80" s="77"/>
-      <c r="L80" s="76"/>
+      <c r="C80" s="79"/>
+      <c r="D80" s="79"/>
+      <c r="E80" s="79"/>
+      <c r="F80" s="79"/>
+      <c r="G80" s="79"/>
+      <c r="H80" s="79"/>
+      <c r="I80" s="79"/>
+      <c r="J80" s="79"/>
+      <c r="K80" s="79"/>
+      <c r="L80" s="78"/>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="1"/>
@@ -3353,54 +3347,54 @@
       <c r="B82" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C82" s="37"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="39"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="41"/>
       <c r="F82" s="13"/>
-      <c r="G82" s="84" t="s">
+      <c r="G82" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="H82" s="63"/>
-      <c r="I82" s="64"/>
-      <c r="J82" s="97"/>
-      <c r="K82" s="98"/>
-      <c r="L82" s="99"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="66"/>
+      <c r="J82" s="99"/>
+      <c r="K82" s="100"/>
+      <c r="L82" s="101"/>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="1"/>
       <c r="B83" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C83" s="37"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="39"/>
+      <c r="C83" s="39"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="41"/>
       <c r="F83" s="2"/>
-      <c r="G83" s="84" t="s">
+      <c r="G83" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="H83" s="63"/>
-      <c r="I83" s="64"/>
-      <c r="J83" s="97"/>
-      <c r="K83" s="98"/>
-      <c r="L83" s="99"/>
+      <c r="H83" s="65"/>
+      <c r="I83" s="66"/>
+      <c r="J83" s="99"/>
+      <c r="K83" s="100"/>
+      <c r="L83" s="101"/>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="1"/>
       <c r="B84" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C84" s="37"/>
-      <c r="D84" s="38"/>
-      <c r="E84" s="39"/>
+      <c r="C84" s="39"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="41"/>
       <c r="F84" s="8"/>
-      <c r="G84" s="84" t="s">
+      <c r="G84" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H84" s="63"/>
-      <c r="I84" s="64"/>
-      <c r="J84" s="97"/>
-      <c r="K84" s="98"/>
-      <c r="L84" s="99"/>
+      <c r="H84" s="65"/>
+      <c r="I84" s="66"/>
+      <c r="J84" s="99"/>
+      <c r="K84" s="100"/>
+      <c r="L84" s="101"/>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="1"/>
@@ -3432,525 +3426,525 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="1"/>
-      <c r="B87" s="75" t="s">
+      <c r="B87" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="77"/>
-      <c r="D87" s="77"/>
-      <c r="E87" s="77"/>
-      <c r="F87" s="77"/>
-      <c r="G87" s="77"/>
-      <c r="H87" s="77"/>
-      <c r="I87" s="77"/>
-      <c r="J87" s="76"/>
-      <c r="K87" s="75" t="s">
+      <c r="C87" s="79"/>
+      <c r="D87" s="79"/>
+      <c r="E87" s="79"/>
+      <c r="F87" s="79"/>
+      <c r="G87" s="79"/>
+      <c r="H87" s="79"/>
+      <c r="I87" s="79"/>
+      <c r="J87" s="78"/>
+      <c r="K87" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="L87" s="76"/>
+      <c r="L87" s="78"/>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="1"/>
-      <c r="B88" s="128" t="s">
+      <c r="B88" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="C88" s="129"/>
-      <c r="D88" s="129"/>
-      <c r="E88" s="129"/>
-      <c r="F88" s="129"/>
-      <c r="G88" s="129"/>
-      <c r="H88" s="129"/>
-      <c r="I88" s="129"/>
-      <c r="J88" s="130"/>
-      <c r="K88" s="131"/>
-      <c r="L88" s="132"/>
+      <c r="C88" s="131"/>
+      <c r="D88" s="131"/>
+      <c r="E88" s="131"/>
+      <c r="F88" s="131"/>
+      <c r="G88" s="131"/>
+      <c r="H88" s="131"/>
+      <c r="I88" s="131"/>
+      <c r="J88" s="132"/>
+      <c r="K88" s="133"/>
+      <c r="L88" s="134"/>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" s="1"/>
-      <c r="B89" s="133" t="s">
+      <c r="B89" s="135" t="s">
         <v>39</v>
       </c>
-      <c r="C89" s="134"/>
-      <c r="D89" s="134"/>
-      <c r="E89" s="134"/>
-      <c r="F89" s="134"/>
-      <c r="G89" s="134"/>
-      <c r="H89" s="134"/>
-      <c r="I89" s="134"/>
-      <c r="J89" s="135"/>
-      <c r="K89" s="42"/>
-      <c r="L89" s="136"/>
+      <c r="C89" s="136"/>
+      <c r="D89" s="136"/>
+      <c r="E89" s="136"/>
+      <c r="F89" s="136"/>
+      <c r="G89" s="136"/>
+      <c r="H89" s="136"/>
+      <c r="I89" s="136"/>
+      <c r="J89" s="137"/>
+      <c r="K89" s="44"/>
+      <c r="L89" s="138"/>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="1"/>
-      <c r="B90" s="133" t="s">
+      <c r="B90" s="135" t="s">
         <v>40</v>
       </c>
-      <c r="C90" s="134"/>
-      <c r="D90" s="134"/>
-      <c r="E90" s="134"/>
-      <c r="F90" s="134"/>
-      <c r="G90" s="134"/>
-      <c r="H90" s="134"/>
-      <c r="I90" s="134"/>
-      <c r="J90" s="135"/>
-      <c r="K90" s="42"/>
-      <c r="L90" s="136"/>
+      <c r="C90" s="136"/>
+      <c r="D90" s="136"/>
+      <c r="E90" s="136"/>
+      <c r="F90" s="136"/>
+      <c r="G90" s="136"/>
+      <c r="H90" s="136"/>
+      <c r="I90" s="136"/>
+      <c r="J90" s="137"/>
+      <c r="K90" s="44"/>
+      <c r="L90" s="138"/>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="1"/>
-      <c r="B91" s="133" t="s">
+      <c r="B91" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="C91" s="134"/>
-      <c r="D91" s="134"/>
-      <c r="E91" s="134"/>
-      <c r="F91" s="134"/>
-      <c r="G91" s="134"/>
-      <c r="H91" s="134"/>
-      <c r="I91" s="134"/>
-      <c r="J91" s="135"/>
-      <c r="K91" s="42"/>
-      <c r="L91" s="136"/>
+      <c r="C91" s="136"/>
+      <c r="D91" s="136"/>
+      <c r="E91" s="136"/>
+      <c r="F91" s="136"/>
+      <c r="G91" s="136"/>
+      <c r="H91" s="136"/>
+      <c r="I91" s="136"/>
+      <c r="J91" s="137"/>
+      <c r="K91" s="44"/>
+      <c r="L91" s="138"/>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="1"/>
-      <c r="B92" s="133" t="s">
+      <c r="B92" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="C92" s="134"/>
-      <c r="D92" s="134"/>
-      <c r="E92" s="134"/>
-      <c r="F92" s="134"/>
-      <c r="G92" s="134"/>
-      <c r="H92" s="134"/>
-      <c r="I92" s="134"/>
-      <c r="J92" s="135"/>
-      <c r="K92" s="42"/>
-      <c r="L92" s="136"/>
+      <c r="C92" s="136"/>
+      <c r="D92" s="136"/>
+      <c r="E92" s="136"/>
+      <c r="F92" s="136"/>
+      <c r="G92" s="136"/>
+      <c r="H92" s="136"/>
+      <c r="I92" s="136"/>
+      <c r="J92" s="137"/>
+      <c r="K92" s="44"/>
+      <c r="L92" s="138"/>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="1"/>
-      <c r="B93" s="133" t="s">
+      <c r="B93" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="C93" s="134"/>
-      <c r="D93" s="134"/>
-      <c r="E93" s="134"/>
-      <c r="F93" s="134"/>
-      <c r="G93" s="134"/>
-      <c r="H93" s="134"/>
-      <c r="I93" s="134"/>
-      <c r="J93" s="135"/>
-      <c r="K93" s="42"/>
-      <c r="L93" s="136"/>
+      <c r="C93" s="136"/>
+      <c r="D93" s="136"/>
+      <c r="E93" s="136"/>
+      <c r="F93" s="136"/>
+      <c r="G93" s="136"/>
+      <c r="H93" s="136"/>
+      <c r="I93" s="136"/>
+      <c r="J93" s="137"/>
+      <c r="K93" s="44"/>
+      <c r="L93" s="138"/>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" s="1"/>
-      <c r="B94" s="133" t="s">
+      <c r="B94" s="135" t="s">
         <v>44</v>
       </c>
-      <c r="C94" s="134"/>
-      <c r="D94" s="134"/>
-      <c r="E94" s="134"/>
-      <c r="F94" s="134"/>
-      <c r="G94" s="134"/>
-      <c r="H94" s="134"/>
-      <c r="I94" s="134"/>
-      <c r="J94" s="135"/>
-      <c r="K94" s="42"/>
-      <c r="L94" s="136"/>
+      <c r="C94" s="136"/>
+      <c r="D94" s="136"/>
+      <c r="E94" s="136"/>
+      <c r="F94" s="136"/>
+      <c r="G94" s="136"/>
+      <c r="H94" s="136"/>
+      <c r="I94" s="136"/>
+      <c r="J94" s="137"/>
+      <c r="K94" s="44"/>
+      <c r="L94" s="138"/>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="1"/>
-      <c r="B95" s="133" t="s">
+      <c r="B95" s="135" t="s">
         <v>45</v>
       </c>
-      <c r="C95" s="134"/>
-      <c r="D95" s="134"/>
-      <c r="E95" s="134"/>
-      <c r="F95" s="134"/>
-      <c r="G95" s="134"/>
-      <c r="H95" s="134"/>
-      <c r="I95" s="134"/>
-      <c r="J95" s="135"/>
-      <c r="K95" s="42"/>
-      <c r="L95" s="136"/>
+      <c r="C95" s="136"/>
+      <c r="D95" s="136"/>
+      <c r="E95" s="136"/>
+      <c r="F95" s="136"/>
+      <c r="G95" s="136"/>
+      <c r="H95" s="136"/>
+      <c r="I95" s="136"/>
+      <c r="J95" s="137"/>
+      <c r="K95" s="44"/>
+      <c r="L95" s="138"/>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="1"/>
-      <c r="B96" s="133" t="s">
+      <c r="B96" s="135" t="s">
         <v>46</v>
       </c>
-      <c r="C96" s="134"/>
-      <c r="D96" s="134"/>
-      <c r="E96" s="134"/>
-      <c r="F96" s="134"/>
-      <c r="G96" s="134"/>
-      <c r="H96" s="134"/>
-      <c r="I96" s="134"/>
-      <c r="J96" s="135"/>
-      <c r="K96" s="42"/>
-      <c r="L96" s="136"/>
+      <c r="C96" s="136"/>
+      <c r="D96" s="136"/>
+      <c r="E96" s="136"/>
+      <c r="F96" s="136"/>
+      <c r="G96" s="136"/>
+      <c r="H96" s="136"/>
+      <c r="I96" s="136"/>
+      <c r="J96" s="137"/>
+      <c r="K96" s="44"/>
+      <c r="L96" s="138"/>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="1"/>
-      <c r="B97" s="133" t="s">
+      <c r="B97" s="135" t="s">
         <v>47</v>
       </c>
-      <c r="C97" s="134"/>
-      <c r="D97" s="134"/>
-      <c r="E97" s="134"/>
-      <c r="F97" s="134"/>
-      <c r="G97" s="134"/>
-      <c r="H97" s="134"/>
-      <c r="I97" s="134"/>
-      <c r="J97" s="135"/>
-      <c r="K97" s="42"/>
-      <c r="L97" s="136"/>
+      <c r="C97" s="136"/>
+      <c r="D97" s="136"/>
+      <c r="E97" s="136"/>
+      <c r="F97" s="136"/>
+      <c r="G97" s="136"/>
+      <c r="H97" s="136"/>
+      <c r="I97" s="136"/>
+      <c r="J97" s="137"/>
+      <c r="K97" s="44"/>
+      <c r="L97" s="138"/>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="1"/>
-      <c r="B98" s="133" t="s">
+      <c r="B98" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="C98" s="134"/>
-      <c r="D98" s="134"/>
-      <c r="E98" s="134"/>
-      <c r="F98" s="134"/>
-      <c r="G98" s="134"/>
-      <c r="H98" s="134"/>
-      <c r="I98" s="134"/>
-      <c r="J98" s="135"/>
-      <c r="K98" s="42"/>
-      <c r="L98" s="136"/>
+      <c r="C98" s="136"/>
+      <c r="D98" s="136"/>
+      <c r="E98" s="136"/>
+      <c r="F98" s="136"/>
+      <c r="G98" s="136"/>
+      <c r="H98" s="136"/>
+      <c r="I98" s="136"/>
+      <c r="J98" s="137"/>
+      <c r="K98" s="44"/>
+      <c r="L98" s="138"/>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="1"/>
-      <c r="B99" s="133" t="s">
+      <c r="B99" s="135" t="s">
         <v>49</v>
       </c>
-      <c r="C99" s="134"/>
-      <c r="D99" s="134"/>
-      <c r="E99" s="134"/>
-      <c r="F99" s="134"/>
-      <c r="G99" s="134"/>
-      <c r="H99" s="134"/>
-      <c r="I99" s="134"/>
-      <c r="J99" s="135"/>
-      <c r="K99" s="42"/>
-      <c r="L99" s="136"/>
+      <c r="C99" s="136"/>
+      <c r="D99" s="136"/>
+      <c r="E99" s="136"/>
+      <c r="F99" s="136"/>
+      <c r="G99" s="136"/>
+      <c r="H99" s="136"/>
+      <c r="I99" s="136"/>
+      <c r="J99" s="137"/>
+      <c r="K99" s="44"/>
+      <c r="L99" s="138"/>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="1"/>
-      <c r="B100" s="133" t="s">
+      <c r="B100" s="135" t="s">
         <v>50</v>
       </c>
-      <c r="C100" s="134"/>
-      <c r="D100" s="134"/>
-      <c r="E100" s="134"/>
-      <c r="F100" s="134"/>
-      <c r="G100" s="134"/>
-      <c r="H100" s="134"/>
-      <c r="I100" s="134"/>
-      <c r="J100" s="135"/>
-      <c r="K100" s="42"/>
-      <c r="L100" s="136"/>
+      <c r="C100" s="136"/>
+      <c r="D100" s="136"/>
+      <c r="E100" s="136"/>
+      <c r="F100" s="136"/>
+      <c r="G100" s="136"/>
+      <c r="H100" s="136"/>
+      <c r="I100" s="136"/>
+      <c r="J100" s="137"/>
+      <c r="K100" s="44"/>
+      <c r="L100" s="138"/>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" s="1"/>
-      <c r="B101" s="133" t="s">
+      <c r="B101" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="C101" s="134"/>
-      <c r="D101" s="134"/>
-      <c r="E101" s="134"/>
-      <c r="F101" s="134"/>
-      <c r="G101" s="134"/>
-      <c r="H101" s="134"/>
-      <c r="I101" s="134"/>
-      <c r="J101" s="135"/>
-      <c r="K101" s="42"/>
-      <c r="L101" s="136"/>
+      <c r="C101" s="136"/>
+      <c r="D101" s="136"/>
+      <c r="E101" s="136"/>
+      <c r="F101" s="136"/>
+      <c r="G101" s="136"/>
+      <c r="H101" s="136"/>
+      <c r="I101" s="136"/>
+      <c r="J101" s="137"/>
+      <c r="K101" s="44"/>
+      <c r="L101" s="138"/>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" s="1"/>
-      <c r="B102" s="133" t="s">
+      <c r="B102" s="135" t="s">
         <v>52</v>
       </c>
-      <c r="C102" s="134"/>
-      <c r="D102" s="134"/>
-      <c r="E102" s="134"/>
-      <c r="F102" s="134"/>
-      <c r="G102" s="134"/>
-      <c r="H102" s="134"/>
-      <c r="I102" s="134"/>
-      <c r="J102" s="135"/>
-      <c r="K102" s="42"/>
-      <c r="L102" s="136"/>
+      <c r="C102" s="136"/>
+      <c r="D102" s="136"/>
+      <c r="E102" s="136"/>
+      <c r="F102" s="136"/>
+      <c r="G102" s="136"/>
+      <c r="H102" s="136"/>
+      <c r="I102" s="136"/>
+      <c r="J102" s="137"/>
+      <c r="K102" s="44"/>
+      <c r="L102" s="138"/>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" s="1"/>
-      <c r="B103" s="133" t="s">
+      <c r="B103" s="135" t="s">
         <v>53</v>
       </c>
-      <c r="C103" s="134"/>
-      <c r="D103" s="134"/>
-      <c r="E103" s="134"/>
-      <c r="F103" s="134"/>
-      <c r="G103" s="134"/>
-      <c r="H103" s="134"/>
-      <c r="I103" s="134"/>
-      <c r="J103" s="135"/>
-      <c r="K103" s="42"/>
-      <c r="L103" s="136"/>
+      <c r="C103" s="136"/>
+      <c r="D103" s="136"/>
+      <c r="E103" s="136"/>
+      <c r="F103" s="136"/>
+      <c r="G103" s="136"/>
+      <c r="H103" s="136"/>
+      <c r="I103" s="136"/>
+      <c r="J103" s="137"/>
+      <c r="K103" s="44"/>
+      <c r="L103" s="138"/>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" s="1"/>
-      <c r="B104" s="133" t="s">
+      <c r="B104" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="C104" s="134"/>
-      <c r="D104" s="134"/>
-      <c r="E104" s="134"/>
-      <c r="F104" s="134"/>
-      <c r="G104" s="134"/>
-      <c r="H104" s="134"/>
-      <c r="I104" s="134"/>
-      <c r="J104" s="135"/>
-      <c r="K104" s="42"/>
-      <c r="L104" s="136"/>
+      <c r="C104" s="136"/>
+      <c r="D104" s="136"/>
+      <c r="E104" s="136"/>
+      <c r="F104" s="136"/>
+      <c r="G104" s="136"/>
+      <c r="H104" s="136"/>
+      <c r="I104" s="136"/>
+      <c r="J104" s="137"/>
+      <c r="K104" s="44"/>
+      <c r="L104" s="138"/>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" s="1"/>
-      <c r="B105" s="133" t="s">
+      <c r="B105" s="135" t="s">
         <v>55</v>
       </c>
-      <c r="C105" s="134"/>
-      <c r="D105" s="134"/>
-      <c r="E105" s="134"/>
-      <c r="F105" s="134"/>
-      <c r="G105" s="134"/>
-      <c r="H105" s="134"/>
-      <c r="I105" s="134"/>
-      <c r="J105" s="135"/>
-      <c r="K105" s="42"/>
-      <c r="L105" s="136"/>
+      <c r="C105" s="136"/>
+      <c r="D105" s="136"/>
+      <c r="E105" s="136"/>
+      <c r="F105" s="136"/>
+      <c r="G105" s="136"/>
+      <c r="H105" s="136"/>
+      <c r="I105" s="136"/>
+      <c r="J105" s="137"/>
+      <c r="K105" s="44"/>
+      <c r="L105" s="138"/>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" s="1"/>
-      <c r="B106" s="133" t="s">
+      <c r="B106" s="135" t="s">
         <v>56</v>
       </c>
-      <c r="C106" s="134"/>
-      <c r="D106" s="134"/>
-      <c r="E106" s="134"/>
-      <c r="F106" s="134"/>
-      <c r="G106" s="134"/>
-      <c r="H106" s="134"/>
-      <c r="I106" s="134"/>
-      <c r="J106" s="135"/>
-      <c r="K106" s="42"/>
-      <c r="L106" s="136"/>
+      <c r="C106" s="136"/>
+      <c r="D106" s="136"/>
+      <c r="E106" s="136"/>
+      <c r="F106" s="136"/>
+      <c r="G106" s="136"/>
+      <c r="H106" s="136"/>
+      <c r="I106" s="136"/>
+      <c r="J106" s="137"/>
+      <c r="K106" s="44"/>
+      <c r="L106" s="138"/>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="1"/>
-      <c r="B107" s="133" t="s">
+      <c r="B107" s="135" t="s">
         <v>57</v>
       </c>
-      <c r="C107" s="134"/>
-      <c r="D107" s="134"/>
-      <c r="E107" s="134"/>
-      <c r="F107" s="134"/>
-      <c r="G107" s="134"/>
-      <c r="H107" s="134"/>
-      <c r="I107" s="134"/>
-      <c r="J107" s="135"/>
-      <c r="K107" s="42"/>
-      <c r="L107" s="136"/>
+      <c r="C107" s="136"/>
+      <c r="D107" s="136"/>
+      <c r="E107" s="136"/>
+      <c r="F107" s="136"/>
+      <c r="G107" s="136"/>
+      <c r="H107" s="136"/>
+      <c r="I107" s="136"/>
+      <c r="J107" s="137"/>
+      <c r="K107" s="44"/>
+      <c r="L107" s="138"/>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" s="1"/>
-      <c r="B108" s="133" t="s">
+      <c r="B108" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="C108" s="134"/>
-      <c r="D108" s="134"/>
-      <c r="E108" s="134"/>
-      <c r="F108" s="134"/>
-      <c r="G108" s="134"/>
-      <c r="H108" s="134"/>
-      <c r="I108" s="134"/>
-      <c r="J108" s="135"/>
-      <c r="K108" s="42"/>
-      <c r="L108" s="136"/>
+      <c r="C108" s="136"/>
+      <c r="D108" s="136"/>
+      <c r="E108" s="136"/>
+      <c r="F108" s="136"/>
+      <c r="G108" s="136"/>
+      <c r="H108" s="136"/>
+      <c r="I108" s="136"/>
+      <c r="J108" s="137"/>
+      <c r="K108" s="44"/>
+      <c r="L108" s="138"/>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" s="1"/>
-      <c r="B109" s="133" t="s">
+      <c r="B109" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="C109" s="134"/>
-      <c r="D109" s="134"/>
-      <c r="E109" s="134"/>
-      <c r="F109" s="134"/>
-      <c r="G109" s="134"/>
-      <c r="H109" s="134"/>
-      <c r="I109" s="134"/>
-      <c r="J109" s="135"/>
-      <c r="K109" s="42"/>
-      <c r="L109" s="136"/>
+      <c r="C109" s="136"/>
+      <c r="D109" s="136"/>
+      <c r="E109" s="136"/>
+      <c r="F109" s="136"/>
+      <c r="G109" s="136"/>
+      <c r="H109" s="136"/>
+      <c r="I109" s="136"/>
+      <c r="J109" s="137"/>
+      <c r="K109" s="44"/>
+      <c r="L109" s="138"/>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" s="1"/>
-      <c r="B110" s="133" t="s">
+      <c r="B110" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="C110" s="134"/>
-      <c r="D110" s="134"/>
-      <c r="E110" s="134"/>
-      <c r="F110" s="134"/>
-      <c r="G110" s="134"/>
-      <c r="H110" s="134"/>
-      <c r="I110" s="134"/>
-      <c r="J110" s="135"/>
-      <c r="K110" s="42"/>
-      <c r="L110" s="136"/>
+      <c r="C110" s="136"/>
+      <c r="D110" s="136"/>
+      <c r="E110" s="136"/>
+      <c r="F110" s="136"/>
+      <c r="G110" s="136"/>
+      <c r="H110" s="136"/>
+      <c r="I110" s="136"/>
+      <c r="J110" s="137"/>
+      <c r="K110" s="44"/>
+      <c r="L110" s="138"/>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" s="1"/>
-      <c r="B111" s="133" t="s">
+      <c r="B111" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="C111" s="134"/>
-      <c r="D111" s="134"/>
-      <c r="E111" s="134"/>
-      <c r="F111" s="134"/>
-      <c r="G111" s="134"/>
-      <c r="H111" s="134"/>
-      <c r="I111" s="134"/>
-      <c r="J111" s="135"/>
-      <c r="K111" s="42"/>
-      <c r="L111" s="136"/>
+      <c r="C111" s="136"/>
+      <c r="D111" s="136"/>
+      <c r="E111" s="136"/>
+      <c r="F111" s="136"/>
+      <c r="G111" s="136"/>
+      <c r="H111" s="136"/>
+      <c r="I111" s="136"/>
+      <c r="J111" s="137"/>
+      <c r="K111" s="44"/>
+      <c r="L111" s="138"/>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" s="1"/>
-      <c r="B112" s="133" t="s">
+      <c r="B112" s="135" t="s">
         <v>62</v>
       </c>
-      <c r="C112" s="134"/>
-      <c r="D112" s="134"/>
-      <c r="E112" s="134"/>
-      <c r="F112" s="134"/>
-      <c r="G112" s="134"/>
-      <c r="H112" s="134"/>
-      <c r="I112" s="134"/>
-      <c r="J112" s="135"/>
-      <c r="K112" s="42"/>
-      <c r="L112" s="136"/>
+      <c r="C112" s="136"/>
+      <c r="D112" s="136"/>
+      <c r="E112" s="136"/>
+      <c r="F112" s="136"/>
+      <c r="G112" s="136"/>
+      <c r="H112" s="136"/>
+      <c r="I112" s="136"/>
+      <c r="J112" s="137"/>
+      <c r="K112" s="44"/>
+      <c r="L112" s="138"/>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" s="1"/>
-      <c r="B113" s="133" t="s">
+      <c r="B113" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="C113" s="134"/>
-      <c r="D113" s="134"/>
-      <c r="E113" s="134"/>
-      <c r="F113" s="134"/>
-      <c r="G113" s="134"/>
-      <c r="H113" s="134"/>
-      <c r="I113" s="134"/>
-      <c r="J113" s="135"/>
-      <c r="K113" s="42"/>
-      <c r="L113" s="136"/>
+      <c r="C113" s="136"/>
+      <c r="D113" s="136"/>
+      <c r="E113" s="136"/>
+      <c r="F113" s="136"/>
+      <c r="G113" s="136"/>
+      <c r="H113" s="136"/>
+      <c r="I113" s="136"/>
+      <c r="J113" s="137"/>
+      <c r="K113" s="44"/>
+      <c r="L113" s="138"/>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" s="1"/>
-      <c r="B114" s="133" t="s">
+      <c r="B114" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="C114" s="134"/>
-      <c r="D114" s="134"/>
-      <c r="E114" s="134"/>
-      <c r="F114" s="134"/>
-      <c r="G114" s="134"/>
-      <c r="H114" s="134"/>
-      <c r="I114" s="134"/>
-      <c r="J114" s="135"/>
-      <c r="K114" s="42"/>
-      <c r="L114" s="136"/>
+      <c r="C114" s="136"/>
+      <c r="D114" s="136"/>
+      <c r="E114" s="136"/>
+      <c r="F114" s="136"/>
+      <c r="G114" s="136"/>
+      <c r="H114" s="136"/>
+      <c r="I114" s="136"/>
+      <c r="J114" s="137"/>
+      <c r="K114" s="44"/>
+      <c r="L114" s="138"/>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" s="1"/>
-      <c r="B115" s="133" t="s">
+      <c r="B115" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="C115" s="134"/>
-      <c r="D115" s="134"/>
-      <c r="E115" s="134"/>
-      <c r="F115" s="134"/>
-      <c r="G115" s="134"/>
-      <c r="H115" s="134"/>
-      <c r="I115" s="134"/>
-      <c r="J115" s="135"/>
-      <c r="K115" s="42"/>
-      <c r="L115" s="136"/>
+      <c r="C115" s="136"/>
+      <c r="D115" s="136"/>
+      <c r="E115" s="136"/>
+      <c r="F115" s="136"/>
+      <c r="G115" s="136"/>
+      <c r="H115" s="136"/>
+      <c r="I115" s="136"/>
+      <c r="J115" s="137"/>
+      <c r="K115" s="44"/>
+      <c r="L115" s="138"/>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" s="1"/>
-      <c r="B116" s="45"/>
-      <c r="C116" s="46"/>
-      <c r="D116" s="46"/>
-      <c r="E116" s="46"/>
-      <c r="F116" s="46"/>
-      <c r="G116" s="46"/>
-      <c r="H116" s="46"/>
-      <c r="I116" s="46"/>
-      <c r="J116" s="47"/>
-      <c r="K116" s="45"/>
-      <c r="L116" s="47"/>
+      <c r="B116" s="47"/>
+      <c r="C116" s="48"/>
+      <c r="D116" s="48"/>
+      <c r="E116" s="48"/>
+      <c r="F116" s="48"/>
+      <c r="G116" s="48"/>
+      <c r="H116" s="48"/>
+      <c r="I116" s="48"/>
+      <c r="J116" s="49"/>
+      <c r="K116" s="47"/>
+      <c r="L116" s="49"/>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" s="1"/>
-      <c r="B117" s="48"/>
-      <c r="C117" s="40"/>
-      <c r="D117" s="40"/>
-      <c r="E117" s="40"/>
-      <c r="F117" s="40"/>
-      <c r="G117" s="40"/>
-      <c r="H117" s="40"/>
-      <c r="I117" s="40"/>
-      <c r="J117" s="49"/>
-      <c r="K117" s="48"/>
-      <c r="L117" s="49"/>
+      <c r="B117" s="50"/>
+      <c r="C117" s="42"/>
+      <c r="D117" s="42"/>
+      <c r="E117" s="42"/>
+      <c r="F117" s="42"/>
+      <c r="G117" s="42"/>
+      <c r="H117" s="42"/>
+      <c r="I117" s="42"/>
+      <c r="J117" s="51"/>
+      <c r="K117" s="50"/>
+      <c r="L117" s="51"/>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" s="1"/>
-      <c r="B118" s="48"/>
-      <c r="C118" s="40"/>
-      <c r="D118" s="40"/>
-      <c r="E118" s="40"/>
-      <c r="F118" s="40"/>
-      <c r="G118" s="40"/>
-      <c r="H118" s="40"/>
-      <c r="I118" s="40"/>
-      <c r="J118" s="49"/>
-      <c r="K118" s="48"/>
-      <c r="L118" s="49"/>
+      <c r="B118" s="50"/>
+      <c r="C118" s="42"/>
+      <c r="D118" s="42"/>
+      <c r="E118" s="42"/>
+      <c r="F118" s="42"/>
+      <c r="G118" s="42"/>
+      <c r="H118" s="42"/>
+      <c r="I118" s="42"/>
+      <c r="J118" s="51"/>
+      <c r="K118" s="50"/>
+      <c r="L118" s="51"/>
     </row>
     <row r="119" spans="1:12" ht="45" customHeight="1">
       <c r="A119" s="1"/>
-      <c r="B119" s="50"/>
-      <c r="C119" s="51"/>
-      <c r="D119" s="51"/>
-      <c r="E119" s="51"/>
-      <c r="F119" s="51"/>
-      <c r="G119" s="51"/>
-      <c r="H119" s="51"/>
-      <c r="I119" s="51"/>
-      <c r="J119" s="52"/>
-      <c r="K119" s="50"/>
-      <c r="L119" s="52"/>
+      <c r="B119" s="52"/>
+      <c r="C119" s="53"/>
+      <c r="D119" s="53"/>
+      <c r="E119" s="53"/>
+      <c r="F119" s="53"/>
+      <c r="G119" s="53"/>
+      <c r="H119" s="53"/>
+      <c r="I119" s="53"/>
+      <c r="J119" s="54"/>
+      <c r="K119" s="52"/>
+      <c r="L119" s="54"/>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" s="1"/>
@@ -3968,65 +3962,65 @@
     </row>
     <row r="121" spans="1:12" ht="30" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="66"/>
-      <c r="C121" s="67"/>
-      <c r="D121" s="66"/>
-      <c r="E121" s="72"/>
-      <c r="F121" s="67"/>
-      <c r="G121" s="109"/>
-      <c r="H121" s="110"/>
-      <c r="I121" s="110"/>
-      <c r="J121" s="111"/>
-      <c r="K121" s="109"/>
-      <c r="L121" s="111"/>
+      <c r="B121" s="68"/>
+      <c r="C121" s="69"/>
+      <c r="D121" s="68"/>
+      <c r="E121" s="74"/>
+      <c r="F121" s="69"/>
+      <c r="G121" s="111"/>
+      <c r="H121" s="112"/>
+      <c r="I121" s="112"/>
+      <c r="J121" s="113"/>
+      <c r="K121" s="111"/>
+      <c r="L121" s="113"/>
     </row>
     <row r="122" spans="1:12">
-      <c r="B122" s="68"/>
-      <c r="C122" s="69"/>
-      <c r="D122" s="68"/>
-      <c r="E122" s="73"/>
-      <c r="F122" s="69"/>
-      <c r="G122" s="112"/>
-      <c r="H122" s="113"/>
-      <c r="I122" s="113"/>
-      <c r="J122" s="114"/>
-      <c r="K122" s="112"/>
-      <c r="L122" s="114"/>
+      <c r="B122" s="70"/>
+      <c r="C122" s="71"/>
+      <c r="D122" s="70"/>
+      <c r="E122" s="75"/>
+      <c r="F122" s="71"/>
+      <c r="G122" s="114"/>
+      <c r="H122" s="115"/>
+      <c r="I122" s="115"/>
+      <c r="J122" s="116"/>
+      <c r="K122" s="114"/>
+      <c r="L122" s="116"/>
     </row>
     <row r="123" spans="1:12">
-      <c r="B123" s="70"/>
-      <c r="C123" s="71"/>
-      <c r="D123" s="70"/>
-      <c r="E123" s="74"/>
-      <c r="F123" s="71"/>
-      <c r="G123" s="115"/>
-      <c r="H123" s="116"/>
-      <c r="I123" s="116"/>
-      <c r="J123" s="117"/>
-      <c r="K123" s="115"/>
-      <c r="L123" s="117"/>
+      <c r="B123" s="72"/>
+      <c r="C123" s="73"/>
+      <c r="D123" s="72"/>
+      <c r="E123" s="76"/>
+      <c r="F123" s="73"/>
+      <c r="G123" s="117"/>
+      <c r="H123" s="118"/>
+      <c r="I123" s="118"/>
+      <c r="J123" s="119"/>
+      <c r="K123" s="117"/>
+      <c r="L123" s="119"/>
     </row>
     <row r="124" spans="1:12" s="31" customFormat="1" ht="47.25" customHeight="1">
       <c r="A124" s="25"/>
-      <c r="B124" s="137" t="s">
+      <c r="B124" s="139" t="s">
         <v>31</v>
       </c>
-      <c r="C124" s="138"/>
-      <c r="D124" s="123" t="s">
+      <c r="C124" s="140"/>
+      <c r="D124" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="E124" s="125"/>
-      <c r="F124" s="124"/>
-      <c r="G124" s="123" t="s">
+      <c r="E124" s="127"/>
+      <c r="F124" s="126"/>
+      <c r="G124" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="H124" s="125"/>
-      <c r="I124" s="125"/>
-      <c r="J124" s="124"/>
-      <c r="K124" s="123" t="s">
+      <c r="H124" s="127"/>
+      <c r="I124" s="127"/>
+      <c r="J124" s="126"/>
+      <c r="K124" s="125" t="s">
         <v>34</v>
       </c>
-      <c r="L124" s="124"/>
+      <c r="L124" s="126"/>
     </row>
     <row r="126" spans="1:12" ht="27" customHeight="1"/>
     <row r="127" spans="1:12" ht="27" customHeight="1"/>
@@ -4040,13 +4034,13 @@
         <v>0</v>
       </c>
       <c r="C132" s="2"/>
-      <c r="D132" s="120" t="str">
+      <c r="D132" s="122" t="str">
         <f>D68</f>
         <v>MHOS-SSM-EL-0001</v>
       </c>
-      <c r="E132" s="121"/>
-      <c r="F132" s="121"/>
-      <c r="G132" s="122"/>
+      <c r="E132" s="123"/>
+      <c r="F132" s="123"/>
+      <c r="G132" s="124"/>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
@@ -4059,10 +4053,10 @@
         <v>1</v>
       </c>
       <c r="C133" s="2"/>
-      <c r="D133" s="139"/>
-      <c r="E133" s="139"/>
-      <c r="F133" s="139"/>
-      <c r="G133" s="139"/>
+      <c r="D133" s="141"/>
+      <c r="E133" s="141"/>
+      <c r="F133" s="141"/>
+      <c r="G133" s="141"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
@@ -4088,11 +4082,11 @@
       <c r="B135" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C135" s="38"/>
-      <c r="D135" s="38"/>
-      <c r="E135" s="38"/>
-      <c r="F135" s="38"/>
-      <c r="G135" s="38"/>
+      <c r="C135" s="40"/>
+      <c r="D135" s="40"/>
+      <c r="E135" s="40"/>
+      <c r="F135" s="40"/>
+      <c r="G135" s="40"/>
       <c r="H135" s="23"/>
       <c r="I135" s="23"/>
       <c r="J135" s="23"/>
@@ -4102,34 +4096,34 @@
     <row r="136" spans="1:12">
       <c r="A136" s="1"/>
       <c r="B136" s="4"/>
-      <c r="C136" s="141"/>
-      <c r="D136" s="141"/>
+      <c r="C136" s="142"/>
+      <c r="D136" s="142"/>
       <c r="E136" s="2"/>
-      <c r="F136" s="141"/>
-      <c r="G136" s="141"/>
+      <c r="F136" s="142"/>
+      <c r="G136" s="142"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
-      <c r="J136" s="141"/>
-      <c r="K136" s="141"/>
-      <c r="L136" s="142"/>
+      <c r="J136" s="142"/>
+      <c r="K136" s="142"/>
+      <c r="L136" s="143"/>
     </row>
     <row r="137" spans="1:12">
       <c r="A137" s="1"/>
       <c r="B137" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C137" s="61"/>
-      <c r="D137" s="61"/>
-      <c r="E137" s="61"/>
-      <c r="F137" s="61"/>
-      <c r="G137" s="61"/>
+      <c r="C137" s="63"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="63"/>
+      <c r="G137" s="63"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J137" s="61"/>
-      <c r="K137" s="61"/>
-      <c r="L137" s="62"/>
+      <c r="J137" s="63"/>
+      <c r="K137" s="63"/>
+      <c r="L137" s="64"/>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="1"/>
@@ -4161,19 +4155,19 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="1"/>
-      <c r="B140" s="75" t="s">
+      <c r="B140" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="C140" s="77"/>
-      <c r="D140" s="77"/>
-      <c r="E140" s="77"/>
-      <c r="F140" s="77"/>
-      <c r="G140" s="77"/>
-      <c r="H140" s="77"/>
-      <c r="I140" s="77"/>
-      <c r="J140" s="77"/>
-      <c r="K140" s="77"/>
-      <c r="L140" s="76"/>
+      <c r="C140" s="79"/>
+      <c r="D140" s="79"/>
+      <c r="E140" s="79"/>
+      <c r="F140" s="79"/>
+      <c r="G140" s="79"/>
+      <c r="H140" s="79"/>
+      <c r="I140" s="79"/>
+      <c r="J140" s="79"/>
+      <c r="K140" s="79"/>
+      <c r="L140" s="78"/>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" s="1"/>
@@ -4205,115 +4199,115 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" s="1"/>
-      <c r="B143" s="140"/>
-      <c r="C143" s="140"/>
-      <c r="D143" s="140"/>
-      <c r="E143" s="140"/>
-      <c r="F143" s="140"/>
-      <c r="G143" s="140"/>
-      <c r="H143" s="140"/>
-      <c r="I143" s="140"/>
-      <c r="J143" s="140"/>
-      <c r="K143" s="140"/>
-      <c r="L143" s="140"/>
+      <c r="B143" s="161"/>
+      <c r="C143" s="161"/>
+      <c r="D143" s="161"/>
+      <c r="E143" s="161"/>
+      <c r="F143" s="161"/>
+      <c r="G143" s="161"/>
+      <c r="H143" s="161"/>
+      <c r="I143" s="161"/>
+      <c r="J143" s="161"/>
+      <c r="K143" s="161"/>
+      <c r="L143" s="161"/>
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="1"/>
-      <c r="B144" s="140"/>
-      <c r="C144" s="140"/>
-      <c r="D144" s="140"/>
-      <c r="E144" s="140"/>
-      <c r="F144" s="140"/>
-      <c r="G144" s="140"/>
-      <c r="H144" s="140"/>
-      <c r="I144" s="140"/>
-      <c r="J144" s="140"/>
-      <c r="K144" s="140"/>
-      <c r="L144" s="140"/>
+      <c r="B144" s="161"/>
+      <c r="C144" s="161"/>
+      <c r="D144" s="161"/>
+      <c r="E144" s="161"/>
+      <c r="F144" s="161"/>
+      <c r="G144" s="161"/>
+      <c r="H144" s="161"/>
+      <c r="I144" s="161"/>
+      <c r="J144" s="161"/>
+      <c r="K144" s="161"/>
+      <c r="L144" s="161"/>
     </row>
     <row r="145" spans="1:12">
       <c r="A145" s="1"/>
-      <c r="B145" s="140"/>
-      <c r="C145" s="140"/>
-      <c r="D145" s="140"/>
-      <c r="E145" s="140"/>
-      <c r="F145" s="140"/>
-      <c r="G145" s="140"/>
-      <c r="H145" s="140"/>
-      <c r="I145" s="140"/>
-      <c r="J145" s="140"/>
-      <c r="K145" s="140"/>
-      <c r="L145" s="140"/>
+      <c r="B145" s="161"/>
+      <c r="C145" s="161"/>
+      <c r="D145" s="161"/>
+      <c r="E145" s="161"/>
+      <c r="F145" s="161"/>
+      <c r="G145" s="161"/>
+      <c r="H145" s="161"/>
+      <c r="I145" s="161"/>
+      <c r="J145" s="161"/>
+      <c r="K145" s="161"/>
+      <c r="L145" s="161"/>
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="1"/>
-      <c r="B146" s="140"/>
-      <c r="C146" s="140"/>
-      <c r="D146" s="140"/>
-      <c r="E146" s="140"/>
-      <c r="F146" s="140"/>
-      <c r="G146" s="140"/>
-      <c r="H146" s="140"/>
-      <c r="I146" s="140"/>
-      <c r="J146" s="140"/>
-      <c r="K146" s="140"/>
-      <c r="L146" s="140"/>
+      <c r="B146" s="161"/>
+      <c r="C146" s="161"/>
+      <c r="D146" s="161"/>
+      <c r="E146" s="161"/>
+      <c r="F146" s="161"/>
+      <c r="G146" s="161"/>
+      <c r="H146" s="161"/>
+      <c r="I146" s="161"/>
+      <c r="J146" s="161"/>
+      <c r="K146" s="161"/>
+      <c r="L146" s="161"/>
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="1"/>
-      <c r="B147" s="140"/>
-      <c r="C147" s="140"/>
-      <c r="D147" s="140"/>
-      <c r="E147" s="140"/>
-      <c r="F147" s="140"/>
-      <c r="G147" s="140"/>
-      <c r="H147" s="140"/>
-      <c r="I147" s="140"/>
-      <c r="J147" s="140"/>
-      <c r="K147" s="140"/>
-      <c r="L147" s="140"/>
+      <c r="B147" s="161"/>
+      <c r="C147" s="161"/>
+      <c r="D147" s="161"/>
+      <c r="E147" s="161"/>
+      <c r="F147" s="161"/>
+      <c r="G147" s="161"/>
+      <c r="H147" s="161"/>
+      <c r="I147" s="161"/>
+      <c r="J147" s="161"/>
+      <c r="K147" s="161"/>
+      <c r="L147" s="161"/>
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="1"/>
-      <c r="B148" s="140"/>
-      <c r="C148" s="140"/>
-      <c r="D148" s="140"/>
-      <c r="E148" s="140"/>
-      <c r="F148" s="140"/>
-      <c r="G148" s="140"/>
-      <c r="H148" s="140"/>
-      <c r="I148" s="140"/>
-      <c r="J148" s="140"/>
-      <c r="K148" s="140"/>
-      <c r="L148" s="140"/>
+      <c r="B148" s="161"/>
+      <c r="C148" s="161"/>
+      <c r="D148" s="161"/>
+      <c r="E148" s="161"/>
+      <c r="F148" s="161"/>
+      <c r="G148" s="161"/>
+      <c r="H148" s="161"/>
+      <c r="I148" s="161"/>
+      <c r="J148" s="161"/>
+      <c r="K148" s="161"/>
+      <c r="L148" s="161"/>
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="1"/>
-      <c r="B149" s="140"/>
-      <c r="C149" s="140"/>
-      <c r="D149" s="140"/>
-      <c r="E149" s="140"/>
-      <c r="F149" s="140"/>
-      <c r="G149" s="140"/>
-      <c r="H149" s="140"/>
-      <c r="I149" s="140"/>
-      <c r="J149" s="140"/>
-      <c r="K149" s="140"/>
-      <c r="L149" s="140"/>
+      <c r="B149" s="161"/>
+      <c r="C149" s="161"/>
+      <c r="D149" s="161"/>
+      <c r="E149" s="161"/>
+      <c r="F149" s="161"/>
+      <c r="G149" s="161"/>
+      <c r="H149" s="161"/>
+      <c r="I149" s="161"/>
+      <c r="J149" s="161"/>
+      <c r="K149" s="161"/>
+      <c r="L149" s="161"/>
     </row>
     <row r="150" spans="1:12" ht="31.5" customHeight="1">
       <c r="A150" s="1"/>
-      <c r="B150" s="140"/>
-      <c r="C150" s="140"/>
-      <c r="D150" s="140"/>
-      <c r="E150" s="140"/>
-      <c r="F150" s="140"/>
-      <c r="G150" s="140"/>
-      <c r="H150" s="140"/>
-      <c r="I150" s="140"/>
-      <c r="J150" s="140"/>
-      <c r="K150" s="140"/>
-      <c r="L150" s="140"/>
+      <c r="B150" s="161"/>
+      <c r="C150" s="161"/>
+      <c r="D150" s="161"/>
+      <c r="E150" s="161"/>
+      <c r="F150" s="161"/>
+      <c r="G150" s="161"/>
+      <c r="H150" s="161"/>
+      <c r="I150" s="161"/>
+      <c r="J150" s="161"/>
+      <c r="K150" s="161"/>
+      <c r="L150" s="161"/>
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="1"/>
@@ -4331,21 +4325,21 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" s="1"/>
-      <c r="B152" s="40" t="s">
+      <c r="B152" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C152" s="40"/>
-      <c r="D152" s="40"/>
-      <c r="E152" s="40"/>
+      <c r="C152" s="42"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="42"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="40" t="s">
+      <c r="G152" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="H152" s="40"/>
-      <c r="I152" s="40"/>
-      <c r="J152" s="40"/>
-      <c r="K152" s="40"/>
-      <c r="L152" s="40"/>
+      <c r="H152" s="42"/>
+      <c r="I152" s="42"/>
+      <c r="J152" s="42"/>
+      <c r="K152" s="42"/>
+      <c r="L152" s="42"/>
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="1"/>
@@ -4393,117 +4387,117 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" s="1"/>
-      <c r="B156" s="159"/>
-      <c r="C156" s="159"/>
-      <c r="D156" s="40"/>
-      <c r="E156" s="40"/>
-      <c r="F156" s="40"/>
-      <c r="G156" s="2"/>
-      <c r="H156" s="40"/>
-      <c r="I156" s="40"/>
-      <c r="J156" s="40"/>
-      <c r="K156" s="40"/>
-      <c r="L156" s="40"/>
+      <c r="B156" s="160"/>
+      <c r="C156" s="160"/>
+      <c r="D156" s="160"/>
+      <c r="E156" s="160"/>
+      <c r="F156" s="160"/>
+      <c r="G156" s="160"/>
+      <c r="H156" s="160"/>
+      <c r="I156" s="160"/>
+      <c r="J156" s="160"/>
+      <c r="K156" s="160"/>
+      <c r="L156" s="160"/>
     </row>
     <row r="157" spans="1:12">
       <c r="A157" s="1"/>
-      <c r="B157" s="159"/>
-      <c r="C157" s="159"/>
-      <c r="D157" s="40"/>
-      <c r="E157" s="40"/>
-      <c r="F157" s="40"/>
-      <c r="G157" s="2"/>
-      <c r="H157" s="40"/>
-      <c r="I157" s="40"/>
-      <c r="J157" s="40"/>
-      <c r="K157" s="40"/>
-      <c r="L157" s="40"/>
+      <c r="B157" s="160"/>
+      <c r="C157" s="160"/>
+      <c r="D157" s="160"/>
+      <c r="E157" s="160"/>
+      <c r="F157" s="160"/>
+      <c r="G157" s="160"/>
+      <c r="H157" s="160"/>
+      <c r="I157" s="160"/>
+      <c r="J157" s="160"/>
+      <c r="K157" s="160"/>
+      <c r="L157" s="160"/>
     </row>
     <row r="158" spans="1:12">
       <c r="A158" s="1"/>
-      <c r="B158" s="159"/>
-      <c r="C158" s="159"/>
-      <c r="D158" s="40"/>
-      <c r="E158" s="40"/>
-      <c r="F158" s="40"/>
-      <c r="G158" s="2"/>
-      <c r="H158" s="40"/>
-      <c r="I158" s="40"/>
-      <c r="J158" s="40"/>
-      <c r="K158" s="40"/>
-      <c r="L158" s="40"/>
+      <c r="B158" s="160"/>
+      <c r="C158" s="160"/>
+      <c r="D158" s="160"/>
+      <c r="E158" s="160"/>
+      <c r="F158" s="160"/>
+      <c r="G158" s="160"/>
+      <c r="H158" s="160"/>
+      <c r="I158" s="160"/>
+      <c r="J158" s="160"/>
+      <c r="K158" s="160"/>
+      <c r="L158" s="160"/>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" s="1"/>
-      <c r="B159" s="159"/>
-      <c r="C159" s="159"/>
-      <c r="D159" s="40"/>
-      <c r="E159" s="40"/>
-      <c r="F159" s="40"/>
-      <c r="G159" s="2"/>
-      <c r="H159" s="40"/>
-      <c r="I159" s="40"/>
-      <c r="J159" s="40"/>
-      <c r="K159" s="40"/>
-      <c r="L159" s="40"/>
+      <c r="B159" s="160"/>
+      <c r="C159" s="160"/>
+      <c r="D159" s="160"/>
+      <c r="E159" s="160"/>
+      <c r="F159" s="160"/>
+      <c r="G159" s="160"/>
+      <c r="H159" s="160"/>
+      <c r="I159" s="160"/>
+      <c r="J159" s="160"/>
+      <c r="K159" s="160"/>
+      <c r="L159" s="160"/>
     </row>
     <row r="160" spans="1:12">
       <c r="A160" s="1"/>
-      <c r="B160" s="159"/>
-      <c r="C160" s="159"/>
-      <c r="D160" s="40"/>
-      <c r="E160" s="40"/>
-      <c r="F160" s="40"/>
-      <c r="G160" s="2"/>
-      <c r="H160" s="40"/>
-      <c r="I160" s="40"/>
-      <c r="J160" s="40"/>
-      <c r="K160" s="40"/>
-      <c r="L160" s="40"/>
+      <c r="B160" s="160"/>
+      <c r="C160" s="160"/>
+      <c r="D160" s="160"/>
+      <c r="E160" s="160"/>
+      <c r="F160" s="160"/>
+      <c r="G160" s="160"/>
+      <c r="H160" s="160"/>
+      <c r="I160" s="160"/>
+      <c r="J160" s="160"/>
+      <c r="K160" s="160"/>
+      <c r="L160" s="160"/>
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="1"/>
-      <c r="B161" s="159"/>
-      <c r="C161" s="159"/>
-      <c r="D161" s="40"/>
-      <c r="E161" s="40"/>
-      <c r="F161" s="40"/>
-      <c r="G161" s="2"/>
-      <c r="H161" s="40"/>
-      <c r="I161" s="40"/>
-      <c r="J161" s="40"/>
-      <c r="K161" s="40"/>
-      <c r="L161" s="40"/>
+      <c r="B161" s="160"/>
+      <c r="C161" s="160"/>
+      <c r="D161" s="160"/>
+      <c r="E161" s="160"/>
+      <c r="F161" s="160"/>
+      <c r="G161" s="160"/>
+      <c r="H161" s="160"/>
+      <c r="I161" s="160"/>
+      <c r="J161" s="160"/>
+      <c r="K161" s="160"/>
+      <c r="L161" s="160"/>
     </row>
     <row r="162" spans="1:12" ht="51" customHeight="1">
       <c r="A162" s="1"/>
-      <c r="B162" s="159"/>
-      <c r="C162" s="159"/>
-      <c r="D162" s="40"/>
-      <c r="E162" s="40"/>
-      <c r="F162" s="40"/>
-      <c r="G162" s="2"/>
-      <c r="H162" s="40"/>
-      <c r="I162" s="40"/>
-      <c r="J162" s="40"/>
-      <c r="K162" s="40"/>
-      <c r="L162" s="40"/>
+      <c r="B162" s="160"/>
+      <c r="C162" s="160"/>
+      <c r="D162" s="160"/>
+      <c r="E162" s="160"/>
+      <c r="F162" s="160"/>
+      <c r="G162" s="160"/>
+      <c r="H162" s="160"/>
+      <c r="I162" s="160"/>
+      <c r="J162" s="160"/>
+      <c r="K162" s="160"/>
+      <c r="L162" s="160"/>
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="1"/>
-      <c r="B163" s="40" t="s">
+      <c r="B163" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="C163" s="40"/>
+      <c r="C163" s="42"/>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
-      <c r="I163" s="40" t="s">
+      <c r="I163" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="J163" s="40"/>
+      <c r="J163" s="42"/>
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
     </row>
@@ -4565,15 +4559,15 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="1"/>
-      <c r="B168" s="40"/>
-      <c r="C168" s="40"/>
+      <c r="B168" s="42"/>
+      <c r="C168" s="42"/>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
-      <c r="I168" s="40"/>
-      <c r="J168" s="40"/>
+      <c r="I168" s="42"/>
+      <c r="J168" s="42"/>
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
     </row>
@@ -4663,67 +4657,67 @@
     </row>
     <row r="175" spans="1:12">
       <c r="A175" s="1"/>
-      <c r="B175" s="150"/>
-      <c r="C175" s="151"/>
-      <c r="D175" s="150"/>
-      <c r="E175" s="156"/>
-      <c r="F175" s="151"/>
-      <c r="G175" s="150"/>
-      <c r="H175" s="156"/>
-      <c r="I175" s="156"/>
-      <c r="J175" s="151"/>
-      <c r="K175" s="150"/>
-      <c r="L175" s="151"/>
+      <c r="B175" s="151"/>
+      <c r="C175" s="152"/>
+      <c r="D175" s="151"/>
+      <c r="E175" s="157"/>
+      <c r="F175" s="152"/>
+      <c r="G175" s="151"/>
+      <c r="H175" s="157"/>
+      <c r="I175" s="157"/>
+      <c r="J175" s="152"/>
+      <c r="K175" s="151"/>
+      <c r="L175" s="152"/>
     </row>
     <row r="176" spans="1:12">
       <c r="A176" s="1"/>
-      <c r="B176" s="152"/>
-      <c r="C176" s="153"/>
-      <c r="D176" s="152"/>
-      <c r="E176" s="157"/>
-      <c r="F176" s="153"/>
-      <c r="G176" s="152"/>
-      <c r="H176" s="157"/>
-      <c r="I176" s="157"/>
-      <c r="J176" s="153"/>
-      <c r="K176" s="152"/>
-      <c r="L176" s="153"/>
+      <c r="B176" s="153"/>
+      <c r="C176" s="154"/>
+      <c r="D176" s="153"/>
+      <c r="E176" s="158"/>
+      <c r="F176" s="154"/>
+      <c r="G176" s="153"/>
+      <c r="H176" s="158"/>
+      <c r="I176" s="158"/>
+      <c r="J176" s="154"/>
+      <c r="K176" s="153"/>
+      <c r="L176" s="154"/>
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="1"/>
-      <c r="B177" s="154"/>
-      <c r="C177" s="155"/>
-      <c r="D177" s="154"/>
-      <c r="E177" s="158"/>
-      <c r="F177" s="155"/>
-      <c r="G177" s="154"/>
-      <c r="H177" s="158"/>
-      <c r="I177" s="158"/>
-      <c r="J177" s="155"/>
-      <c r="K177" s="154"/>
-      <c r="L177" s="155"/>
+      <c r="B177" s="155"/>
+      <c r="C177" s="156"/>
+      <c r="D177" s="155"/>
+      <c r="E177" s="159"/>
+      <c r="F177" s="156"/>
+      <c r="G177" s="155"/>
+      <c r="H177" s="159"/>
+      <c r="I177" s="159"/>
+      <c r="J177" s="156"/>
+      <c r="K177" s="155"/>
+      <c r="L177" s="156"/>
     </row>
     <row r="178" spans="1:12">
       <c r="A178" s="25"/>
-      <c r="B178" s="137" t="s">
+      <c r="B178" s="139" t="s">
         <v>31</v>
       </c>
-      <c r="C178" s="138"/>
-      <c r="D178" s="123" t="s">
+      <c r="C178" s="140"/>
+      <c r="D178" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="E178" s="125"/>
-      <c r="F178" s="124"/>
-      <c r="G178" s="143" t="s">
+      <c r="E178" s="127"/>
+      <c r="F178" s="126"/>
+      <c r="G178" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="H178" s="144"/>
-      <c r="I178" s="144"/>
-      <c r="J178" s="145"/>
-      <c r="K178" s="120" t="s">
+      <c r="H178" s="145"/>
+      <c r="I178" s="145"/>
+      <c r="J178" s="146"/>
+      <c r="K178" s="122" t="s">
         <v>34</v>
       </c>
-      <c r="L178" s="122"/>
+      <c r="L178" s="124"/>
     </row>
     <row r="187" spans="1:12" ht="30" customHeight="1"/>
     <row r="188" spans="1:12" ht="30" customHeight="1"/>
@@ -4731,7 +4725,7 @@
     <row r="191" spans="1:12" ht="30" customHeight="1"/>
     <row r="192" spans="1:12" ht="27" customHeight="1"/>
   </sheetData>
-  <mergeCells count="177">
+  <mergeCells count="167">
     <mergeCell ref="B178:C178"/>
     <mergeCell ref="D178:F178"/>
     <mergeCell ref="G178:J178"/>
@@ -4748,18 +4742,9 @@
     <mergeCell ref="D175:F177"/>
     <mergeCell ref="G175:J177"/>
     <mergeCell ref="K175:L177"/>
-    <mergeCell ref="D156:F162"/>
-    <mergeCell ref="H156:L162"/>
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="I163:J163"/>
     <mergeCell ref="B140:L140"/>
-    <mergeCell ref="B156:B162"/>
-    <mergeCell ref="C156:C162"/>
-    <mergeCell ref="B143:B150"/>
-    <mergeCell ref="C143:D150"/>
-    <mergeCell ref="E143:F150"/>
-    <mergeCell ref="G143:I150"/>
-    <mergeCell ref="J143:L150"/>
     <mergeCell ref="C135:G135"/>
     <mergeCell ref="C136:D136"/>
     <mergeCell ref="F136:G136"/>
@@ -4861,7 +4846,7 @@
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="K60:L60"/>
-    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
     <mergeCell ref="C8:L8"/>
     <mergeCell ref="C9:L10"/>
     <mergeCell ref="C11:L11"/>
@@ -4891,7 +4876,6 @@
     <mergeCell ref="G152:L152"/>
     <mergeCell ref="D32:L32"/>
     <mergeCell ref="B33:L33"/>
-    <mergeCell ref="D6:F6"/>
     <mergeCell ref="B116:J119"/>
     <mergeCell ref="K116:L119"/>
     <mergeCell ref="L20:L21"/>

--- a/templates/Plantilla_Preventivo.xlsx
+++ b/templates/Plantilla_Preventivo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDD56DA4-7A03-4F04-A895-0D2F7C2456B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{351ACD58-EFEC-4DE6-84D7-F9753C7C44A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2256,7 +2256,7 @@
     <col min="2" max="2" width="26.42578125" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" customWidth="1"/>
     <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" customWidth="1"/>
     <col min="8" max="8" width="0.28515625" customWidth="1"/>
@@ -2266,8 +2266,24 @@
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1"/>
     <row r="3" spans="1:12" ht="30" customHeight="1"/>
+    <row r="4" spans="1:12">
+      <c r="B4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="57"/>
+    </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1"/>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2277,13 +2293,6 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="57"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -2293,13 +2302,6 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -4846,7 +4848,7 @@
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="K60:L60"/>
-    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="C8:L8"/>
     <mergeCell ref="C9:L10"/>
     <mergeCell ref="C11:L11"/>

--- a/templates/Plantilla_Preventivo.xlsx
+++ b/templates/Plantilla_Preventivo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{351ACD58-EFEC-4DE6-84D7-F9753C7C44A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AD13991-BD38-4718-9A11-4278A0241140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2254,36 +2254,27 @@
   <cols>
     <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
     <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" customWidth="1"/>
     <col min="8" max="8" width="0.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1"/>
     <row r="3" spans="1:12" ht="30" customHeight="1"/>
-    <row r="4" spans="1:12">
-      <c r="B4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="57"/>
-    </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="57"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2293,6 +2284,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1"/>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -4848,7 +4846,7 @@
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="K60:L60"/>
-    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="C8:L8"/>
     <mergeCell ref="C9:L10"/>
     <mergeCell ref="C11:L11"/>
@@ -4898,8 +4896,10 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>
-  <rowBreaks count="2" manualBreakCount="2">
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="62" max="16383" man="1"/>
     <brk id="63" max="16383" man="1"/>
+    <brk id="126" max="16383" man="1"/>
     <brk id="127" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>

--- a/templates/Plantilla_Preventivo.xlsx
+++ b/templates/Plantilla_Preventivo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AD13991-BD38-4718-9A11-4278A0241140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49B8F7F2-E031-4701-ACFD-FCC09E7FBB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1473,7 +1473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1541,36 +1541,312 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1580,126 +1856,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1707,15 +1872,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1727,15 +1883,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1763,155 +1910,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2272,9 +2270,9 @@
         <v>0</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="57"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="122"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2312,69 +2310,69 @@
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="60"/>
+      <c r="C8" s="115"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="123"/>
+      <c r="H8" s="123"/>
+      <c r="I8" s="123"/>
+      <c r="J8" s="123"/>
+      <c r="K8" s="123"/>
+      <c r="L8" s="124"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="62"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="116"/>
+      <c r="H9" s="116"/>
+      <c r="I9" s="116"/>
+      <c r="J9" s="116"/>
+      <c r="K9" s="116"/>
+      <c r="L9" s="117"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1"/>
       <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="64"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="71"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="65"/>
-      <c r="L11" s="66"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="101"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -2405,9 +2403,9 @@
       <c r="I13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="64"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="71"/>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="1"/>
@@ -2456,44 +2454,44 @@
       <c r="B17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="98"/>
-      <c r="E17" s="147" t="s">
+      <c r="D17" s="150"/>
+      <c r="E17" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="93"/>
+      <c r="F17" s="53"/>
       <c r="G17" s="4"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="147" t="s">
+      <c r="I17" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="J17" s="93"/>
+      <c r="J17" s="53"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="42"/>
+      <c r="L17" s="37"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="1"/>
       <c r="B18" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="95"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="150"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="54"/>
       <c r="G18" s="4"/>
       <c r="H18" s="8"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="95"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="42"/>
+      <c r="L18" s="37"/>
     </row>
     <row r="19" spans="1:12" ht="15" hidden="1" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="9"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="98"/>
+      <c r="D19" s="150"/>
       <c r="E19" s="9"/>
       <c r="F19" s="11"/>
       <c r="G19" s="4"/>
@@ -2508,42 +2506,42 @@
       <c r="B20" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="150"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="147" t="s">
+      <c r="C20" s="51"/>
+      <c r="D20" s="136"/>
+      <c r="E20" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="93"/>
+      <c r="F20" s="53"/>
       <c r="G20" s="4"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="147" t="s">
+      <c r="I20" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="93"/>
+      <c r="J20" s="53"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="42"/>
+      <c r="L20" s="37"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="1"/>
       <c r="B21" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="94"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="94"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="52"/>
       <c r="G21" s="4"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="149"/>
-      <c r="J21" s="94"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="42"/>
+      <c r="L21" s="37"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="42"/>
+      <c r="D22" s="37"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -2569,19 +2567,19 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="1"/>
-      <c r="B24" s="90" t="s">
+      <c r="B24" s="145" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="91"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="92"/>
+      <c r="C24" s="146"/>
+      <c r="D24" s="146"/>
+      <c r="E24" s="146"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="146"/>
+      <c r="H24" s="146"/>
+      <c r="I24" s="146"/>
+      <c r="J24" s="146"/>
+      <c r="K24" s="146"/>
+      <c r="L24" s="147"/>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="1"/>
@@ -2602,54 +2600,54 @@
       <c r="B26" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="41"/>
+      <c r="C26" s="97"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="98"/>
       <c r="F26" s="13"/>
-      <c r="G26" s="86" t="s">
+      <c r="G26" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="65"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="100"/>
-      <c r="L26" s="101"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="103"/>
+      <c r="L26" s="104"/>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="1"/>
       <c r="B27" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
+      <c r="C27" s="97"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="98"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="86" t="s">
+      <c r="G27" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="H27" s="65"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="88"/>
-      <c r="L27" s="89"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="134"/>
+      <c r="L27" s="135"/>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="1"/>
       <c r="B28" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="98"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="86" t="s">
+      <c r="G28" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="65"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="58"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="115"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="1"/>
@@ -2670,74 +2668,74 @@
       <c r="B30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="38"/>
-      <c r="L30" s="43"/>
+      <c r="C30" s="131"/>
+      <c r="D30" s="131"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="131"/>
+      <c r="I30" s="131"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="132"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="1"/>
-      <c r="B31" s="83"/>
-      <c r="C31" s="84"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84"/>
-      <c r="G31" s="84"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="85"/>
+      <c r="B31" s="128"/>
+      <c r="C31" s="129"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="129"/>
+      <c r="F31" s="129"/>
+      <c r="G31" s="129"/>
+      <c r="H31" s="129"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="129"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="130"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="1"/>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="38"/>
-      <c r="L32" s="43"/>
+      <c r="C32" s="131"/>
+      <c r="D32" s="131"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="131"/>
+      <c r="G32" s="131"/>
+      <c r="H32" s="131"/>
+      <c r="I32" s="131"/>
+      <c r="J32" s="131"/>
+      <c r="K32" s="131"/>
+      <c r="L32" s="132"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="1"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="138"/>
+      <c r="H33" s="138"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="138"/>
+      <c r="K33" s="138"/>
+      <c r="L33" s="138"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="1"/>
-      <c r="B34" s="83"/>
-      <c r="C34" s="84"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="84"/>
-      <c r="F34" s="84"/>
-      <c r="G34" s="84"/>
-      <c r="H34" s="84"/>
-      <c r="I34" s="84"/>
-      <c r="J34" s="84"/>
-      <c r="K34" s="84"/>
-      <c r="L34" s="85"/>
+      <c r="B34" s="128"/>
+      <c r="C34" s="129"/>
+      <c r="D34" s="129"/>
+      <c r="E34" s="129"/>
+      <c r="F34" s="129"/>
+      <c r="G34" s="129"/>
+      <c r="H34" s="129"/>
+      <c r="I34" s="129"/>
+      <c r="J34" s="129"/>
+      <c r="K34" s="129"/>
+      <c r="L34" s="130"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="1"/>
@@ -2755,159 +2753,159 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="1"/>
-      <c r="B36" s="102" t="s">
+      <c r="B36" s="151" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="103"/>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="103"/>
-      <c r="H36" s="103"/>
-      <c r="I36" s="103"/>
-      <c r="J36" s="103"/>
-      <c r="K36" s="103"/>
-      <c r="L36" s="104"/>
+      <c r="C36" s="152"/>
+      <c r="D36" s="152"/>
+      <c r="E36" s="152"/>
+      <c r="F36" s="152"/>
+      <c r="G36" s="152"/>
+      <c r="H36" s="152"/>
+      <c r="I36" s="152"/>
+      <c r="J36" s="152"/>
+      <c r="K36" s="152"/>
+      <c r="L36" s="153"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="105"/>
-      <c r="C37" s="106"/>
-      <c r="D37" s="106"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="106"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="106"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="106"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="107"/>
+      <c r="B37" s="154"/>
+      <c r="C37" s="155"/>
+      <c r="D37" s="155"/>
+      <c r="E37" s="155"/>
+      <c r="F37" s="155"/>
+      <c r="G37" s="155"/>
+      <c r="H37" s="155"/>
+      <c r="I37" s="155"/>
+      <c r="J37" s="155"/>
+      <c r="K37" s="155"/>
+      <c r="L37" s="156"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="1"/>
-      <c r="B38" s="105"/>
-      <c r="C38" s="106"/>
-      <c r="D38" s="106"/>
-      <c r="E38" s="106"/>
-      <c r="F38" s="106"/>
-      <c r="G38" s="106"/>
-      <c r="H38" s="106"/>
-      <c r="I38" s="106"/>
-      <c r="J38" s="106"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="107"/>
+      <c r="B38" s="154"/>
+      <c r="C38" s="155"/>
+      <c r="D38" s="155"/>
+      <c r="E38" s="155"/>
+      <c r="F38" s="155"/>
+      <c r="G38" s="155"/>
+      <c r="H38" s="155"/>
+      <c r="I38" s="155"/>
+      <c r="J38" s="155"/>
+      <c r="K38" s="155"/>
+      <c r="L38" s="156"/>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="1"/>
-      <c r="B39" s="105"/>
-      <c r="C39" s="106"/>
-      <c r="D39" s="106"/>
-      <c r="E39" s="106"/>
-      <c r="F39" s="106"/>
-      <c r="G39" s="106"/>
-      <c r="H39" s="106"/>
-      <c r="I39" s="106"/>
-      <c r="J39" s="106"/>
-      <c r="K39" s="106"/>
-      <c r="L39" s="107"/>
+      <c r="B39" s="154"/>
+      <c r="C39" s="155"/>
+      <c r="D39" s="155"/>
+      <c r="E39" s="155"/>
+      <c r="F39" s="155"/>
+      <c r="G39" s="155"/>
+      <c r="H39" s="155"/>
+      <c r="I39" s="155"/>
+      <c r="J39" s="155"/>
+      <c r="K39" s="155"/>
+      <c r="L39" s="156"/>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="1"/>
-      <c r="B40" s="105"/>
-      <c r="C40" s="106"/>
-      <c r="D40" s="106"/>
-      <c r="E40" s="106"/>
-      <c r="F40" s="106"/>
-      <c r="G40" s="106"/>
-      <c r="H40" s="106"/>
-      <c r="I40" s="106"/>
-      <c r="J40" s="106"/>
-      <c r="K40" s="106"/>
-      <c r="L40" s="107"/>
+      <c r="B40" s="154"/>
+      <c r="C40" s="155"/>
+      <c r="D40" s="155"/>
+      <c r="E40" s="155"/>
+      <c r="F40" s="155"/>
+      <c r="G40" s="155"/>
+      <c r="H40" s="155"/>
+      <c r="I40" s="155"/>
+      <c r="J40" s="155"/>
+      <c r="K40" s="155"/>
+      <c r="L40" s="156"/>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="1"/>
-      <c r="B41" s="105"/>
-      <c r="C41" s="106"/>
-      <c r="D41" s="106"/>
-      <c r="E41" s="106"/>
-      <c r="F41" s="106"/>
-      <c r="G41" s="106"/>
-      <c r="H41" s="106"/>
-      <c r="I41" s="106"/>
-      <c r="J41" s="106"/>
-      <c r="K41" s="106"/>
-      <c r="L41" s="107"/>
+      <c r="B41" s="154"/>
+      <c r="C41" s="155"/>
+      <c r="D41" s="155"/>
+      <c r="E41" s="155"/>
+      <c r="F41" s="155"/>
+      <c r="G41" s="155"/>
+      <c r="H41" s="155"/>
+      <c r="I41" s="155"/>
+      <c r="J41" s="155"/>
+      <c r="K41" s="155"/>
+      <c r="L41" s="156"/>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="1"/>
-      <c r="B42" s="105"/>
-      <c r="C42" s="106"/>
-      <c r="D42" s="106"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="106"/>
-      <c r="G42" s="106"/>
-      <c r="H42" s="106"/>
-      <c r="I42" s="106"/>
-      <c r="J42" s="106"/>
-      <c r="K42" s="106"/>
-      <c r="L42" s="107"/>
+      <c r="B42" s="154"/>
+      <c r="C42" s="155"/>
+      <c r="D42" s="155"/>
+      <c r="E42" s="155"/>
+      <c r="F42" s="155"/>
+      <c r="G42" s="155"/>
+      <c r="H42" s="155"/>
+      <c r="I42" s="155"/>
+      <c r="J42" s="155"/>
+      <c r="K42" s="155"/>
+      <c r="L42" s="156"/>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="1"/>
-      <c r="B43" s="105"/>
-      <c r="C43" s="106"/>
-      <c r="D43" s="106"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="106"/>
-      <c r="G43" s="106"/>
-      <c r="H43" s="106"/>
-      <c r="I43" s="106"/>
-      <c r="J43" s="106"/>
-      <c r="K43" s="106"/>
-      <c r="L43" s="107"/>
+      <c r="B43" s="154"/>
+      <c r="C43" s="155"/>
+      <c r="D43" s="155"/>
+      <c r="E43" s="155"/>
+      <c r="F43" s="155"/>
+      <c r="G43" s="155"/>
+      <c r="H43" s="155"/>
+      <c r="I43" s="155"/>
+      <c r="J43" s="155"/>
+      <c r="K43" s="155"/>
+      <c r="L43" s="156"/>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="1"/>
-      <c r="B44" s="105"/>
-      <c r="C44" s="106"/>
-      <c r="D44" s="106"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="106"/>
-      <c r="H44" s="106"/>
-      <c r="I44" s="106"/>
-      <c r="J44" s="106"/>
-      <c r="K44" s="106"/>
-      <c r="L44" s="107"/>
+      <c r="B44" s="154"/>
+      <c r="C44" s="155"/>
+      <c r="D44" s="155"/>
+      <c r="E44" s="155"/>
+      <c r="F44" s="155"/>
+      <c r="G44" s="155"/>
+      <c r="H44" s="155"/>
+      <c r="I44" s="155"/>
+      <c r="J44" s="155"/>
+      <c r="K44" s="155"/>
+      <c r="L44" s="156"/>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="1"/>
-      <c r="B45" s="105"/>
-      <c r="C45" s="106"/>
-      <c r="D45" s="106"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="106"/>
-      <c r="G45" s="106"/>
-      <c r="H45" s="106"/>
-      <c r="I45" s="106"/>
-      <c r="J45" s="106"/>
-      <c r="K45" s="106"/>
-      <c r="L45" s="107"/>
+      <c r="B45" s="154"/>
+      <c r="C45" s="155"/>
+      <c r="D45" s="155"/>
+      <c r="E45" s="155"/>
+      <c r="F45" s="155"/>
+      <c r="G45" s="155"/>
+      <c r="H45" s="155"/>
+      <c r="I45" s="155"/>
+      <c r="J45" s="155"/>
+      <c r="K45" s="155"/>
+      <c r="L45" s="156"/>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="1"/>
-      <c r="B46" s="108"/>
-      <c r="C46" s="109"/>
-      <c r="D46" s="109"/>
-      <c r="E46" s="109"/>
-      <c r="F46" s="109"/>
-      <c r="G46" s="109"/>
-      <c r="H46" s="109"/>
-      <c r="I46" s="109"/>
-      <c r="J46" s="109"/>
-      <c r="K46" s="109"/>
-      <c r="L46" s="110"/>
+      <c r="B46" s="157"/>
+      <c r="C46" s="158"/>
+      <c r="D46" s="158"/>
+      <c r="E46" s="158"/>
+      <c r="F46" s="158"/>
+      <c r="G46" s="158"/>
+      <c r="H46" s="158"/>
+      <c r="I46" s="158"/>
+      <c r="J46" s="158"/>
+      <c r="K46" s="158"/>
+      <c r="L46" s="159"/>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="1"/>
@@ -2930,14 +2928,14 @@
       </c>
       <c r="C48" s="18"/>
       <c r="D48" s="18"/>
-      <c r="E48" s="79"/>
-      <c r="F48" s="79"/>
-      <c r="G48" s="79"/>
-      <c r="H48" s="79"/>
-      <c r="I48" s="79"/>
-      <c r="J48" s="79"/>
-      <c r="K48" s="79"/>
-      <c r="L48" s="78"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="65"/>
+      <c r="K48" s="65"/>
+      <c r="L48" s="66"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="1"/>
@@ -2997,131 +2995,131 @@
     </row>
     <row r="53" spans="1:12" ht="30" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="53" t="s">
+      <c r="B53" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="C53" s="53"/>
-      <c r="D53" s="53"/>
-      <c r="E53" s="53"/>
-      <c r="F53" s="53"/>
-      <c r="G53" s="53"/>
-      <c r="H53" s="53"/>
-      <c r="I53" s="53"/>
-      <c r="J53" s="53"/>
-      <c r="K53" s="53"/>
-      <c r="L53" s="53"/>
+      <c r="C53" s="105"/>
+      <c r="D53" s="105"/>
+      <c r="E53" s="105"/>
+      <c r="F53" s="105"/>
+      <c r="G53" s="105"/>
+      <c r="H53" s="105"/>
+      <c r="I53" s="105"/>
+      <c r="J53" s="105"/>
+      <c r="K53" s="105"/>
+      <c r="L53" s="105"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="1"/>
-      <c r="B54" s="77" t="s">
+      <c r="B54" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="C54" s="78"/>
-      <c r="D54" s="77" t="s">
+      <c r="C54" s="66"/>
+      <c r="D54" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E54" s="79"/>
-      <c r="F54" s="78"/>
-      <c r="G54" s="77" t="s">
+      <c r="E54" s="65"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="H54" s="79"/>
-      <c r="I54" s="79"/>
-      <c r="J54" s="78"/>
-      <c r="K54" s="77" t="s">
+      <c r="H54" s="65"/>
+      <c r="I54" s="65"/>
+      <c r="J54" s="66"/>
+      <c r="K54" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="L54" s="78"/>
+      <c r="L54" s="66"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="1"/>
-      <c r="B55" s="77"/>
-      <c r="C55" s="78"/>
-      <c r="D55" s="77"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="78"/>
-      <c r="G55" s="80"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="82"/>
-      <c r="K55" s="80"/>
-      <c r="L55" s="82"/>
+      <c r="B55" s="64"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="64"/>
+      <c r="E55" s="65"/>
+      <c r="F55" s="66"/>
+      <c r="G55" s="125"/>
+      <c r="H55" s="126"/>
+      <c r="I55" s="126"/>
+      <c r="J55" s="127"/>
+      <c r="K55" s="125"/>
+      <c r="L55" s="127"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="1"/>
-      <c r="B56" s="77"/>
-      <c r="C56" s="78"/>
-      <c r="D56" s="77"/>
-      <c r="E56" s="79"/>
-      <c r="F56" s="78"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="81"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="82"/>
-      <c r="K56" s="80"/>
-      <c r="L56" s="82"/>
+      <c r="B56" s="64"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="66"/>
+      <c r="G56" s="125"/>
+      <c r="H56" s="126"/>
+      <c r="I56" s="126"/>
+      <c r="J56" s="127"/>
+      <c r="K56" s="125"/>
+      <c r="L56" s="127"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="1"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="69"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="74"/>
-      <c r="F57" s="69"/>
-      <c r="G57" s="111"/>
-      <c r="H57" s="112"/>
-      <c r="I57" s="112"/>
-      <c r="J57" s="113"/>
-      <c r="K57" s="111"/>
-      <c r="L57" s="113"/>
+      <c r="B57" s="79"/>
+      <c r="C57" s="80"/>
+      <c r="D57" s="79"/>
+      <c r="E57" s="85"/>
+      <c r="F57" s="80"/>
+      <c r="G57" s="88"/>
+      <c r="H57" s="89"/>
+      <c r="I57" s="89"/>
+      <c r="J57" s="90"/>
+      <c r="K57" s="88"/>
+      <c r="L57" s="90"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="B58" s="70"/>
-      <c r="C58" s="71"/>
-      <c r="D58" s="70"/>
-      <c r="E58" s="75"/>
-      <c r="F58" s="71"/>
-      <c r="G58" s="114"/>
-      <c r="H58" s="115"/>
-      <c r="I58" s="115"/>
-      <c r="J58" s="116"/>
-      <c r="K58" s="114"/>
-      <c r="L58" s="116"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="82"/>
+      <c r="G58" s="91"/>
+      <c r="H58" s="92"/>
+      <c r="I58" s="92"/>
+      <c r="J58" s="93"/>
+      <c r="K58" s="91"/>
+      <c r="L58" s="93"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="B59" s="72"/>
-      <c r="C59" s="73"/>
-      <c r="D59" s="72"/>
-      <c r="E59" s="76"/>
-      <c r="F59" s="73"/>
-      <c r="G59" s="117"/>
-      <c r="H59" s="118"/>
-      <c r="I59" s="118"/>
-      <c r="J59" s="119"/>
-      <c r="K59" s="120"/>
-      <c r="L59" s="121"/>
+      <c r="B59" s="83"/>
+      <c r="C59" s="84"/>
+      <c r="D59" s="83"/>
+      <c r="E59" s="87"/>
+      <c r="F59" s="84"/>
+      <c r="G59" s="94"/>
+      <c r="H59" s="95"/>
+      <c r="I59" s="95"/>
+      <c r="J59" s="96"/>
+      <c r="K59" s="112"/>
+      <c r="L59" s="113"/>
     </row>
     <row r="60" spans="1:12" s="34" customFormat="1" ht="90.75" customHeight="1">
       <c r="A60" s="33"/>
-      <c r="B60" s="125" t="s">
+      <c r="B60" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="126"/>
-      <c r="D60" s="125" t="s">
+      <c r="C60" s="42"/>
+      <c r="D60" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E60" s="127"/>
-      <c r="F60" s="126"/>
-      <c r="G60" s="125" t="s">
+      <c r="E60" s="41"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="H60" s="127"/>
-      <c r="I60" s="127"/>
-      <c r="J60" s="126"/>
-      <c r="K60" s="128" t="s">
+      <c r="H60" s="41"/>
+      <c r="I60" s="41"/>
+      <c r="J60" s="42"/>
+      <c r="K60" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="L60" s="129"/>
+      <c r="L60" s="119"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1"/>
     <row r="62" spans="1:12" ht="27" customHeight="1"/>
@@ -3136,11 +3134,11 @@
         <v>0</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="122" t="s">
+      <c r="D68" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E68" s="123"/>
-      <c r="F68" s="124"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="47"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -3154,9 +3152,9 @@
         <v>1</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
+      <c r="D69" s="114"/>
+      <c r="E69" s="114"/>
+      <c r="F69" s="114"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -3183,69 +3181,69 @@
       <c r="B71" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C71" s="40"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40"/>
-      <c r="J71" s="40"/>
-      <c r="K71" s="40"/>
-      <c r="L71" s="58"/>
+      <c r="C71" s="67"/>
+      <c r="D71" s="67"/>
+      <c r="E71" s="67"/>
+      <c r="F71" s="67"/>
+      <c r="G71" s="67"/>
+      <c r="H71" s="67"/>
+      <c r="I71" s="67"/>
+      <c r="J71" s="67"/>
+      <c r="K71" s="67"/>
+      <c r="L71" s="115"/>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="1"/>
       <c r="B72" s="4"/>
-      <c r="C72" s="61"/>
-      <c r="D72" s="61"/>
-      <c r="E72" s="61"/>
-      <c r="F72" s="61"/>
-      <c r="G72" s="61"/>
-      <c r="H72" s="61"/>
-      <c r="I72" s="61"/>
-      <c r="J72" s="61"/>
-      <c r="K72" s="61"/>
-      <c r="L72" s="62"/>
+      <c r="C72" s="116"/>
+      <c r="D72" s="116"/>
+      <c r="E72" s="116"/>
+      <c r="F72" s="116"/>
+      <c r="G72" s="116"/>
+      <c r="H72" s="116"/>
+      <c r="I72" s="116"/>
+      <c r="J72" s="116"/>
+      <c r="K72" s="116"/>
+      <c r="L72" s="117"/>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="1"/>
       <c r="B73" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C73" s="63"/>
-      <c r="D73" s="63"/>
-      <c r="E73" s="63"/>
-      <c r="F73" s="63"/>
-      <c r="G73" s="63"/>
-      <c r="H73" s="63"/>
-      <c r="I73" s="63"/>
-      <c r="J73" s="63"/>
-      <c r="K73" s="63"/>
-      <c r="L73" s="64"/>
+      <c r="C73" s="70"/>
+      <c r="D73" s="70"/>
+      <c r="E73" s="70"/>
+      <c r="F73" s="70"/>
+      <c r="G73" s="70"/>
+      <c r="H73" s="70"/>
+      <c r="I73" s="70"/>
+      <c r="J73" s="70"/>
+      <c r="K73" s="70"/>
+      <c r="L73" s="71"/>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="1"/>
       <c r="B74" s="4"/>
-      <c r="C74" s="65"/>
-      <c r="D74" s="65"/>
-      <c r="E74" s="65"/>
-      <c r="F74" s="65"/>
-      <c r="G74" s="65"/>
-      <c r="H74" s="65"/>
-      <c r="I74" s="65"/>
-      <c r="J74" s="65"/>
-      <c r="K74" s="65"/>
-      <c r="L74" s="66"/>
+      <c r="C74" s="100"/>
+      <c r="D74" s="100"/>
+      <c r="E74" s="100"/>
+      <c r="F74" s="100"/>
+      <c r="G74" s="100"/>
+      <c r="H74" s="100"/>
+      <c r="I74" s="100"/>
+      <c r="J74" s="100"/>
+      <c r="K74" s="100"/>
+      <c r="L74" s="101"/>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="1"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="67"/>
-      <c r="D75" s="67"/>
-      <c r="E75" s="67"/>
-      <c r="F75" s="67"/>
-      <c r="G75" s="67"/>
+      <c r="C75" s="111"/>
+      <c r="D75" s="111"/>
+      <c r="E75" s="111"/>
+      <c r="F75" s="111"/>
+      <c r="G75" s="111"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3266,9 +3264,9 @@
       <c r="I76" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J76" s="63"/>
-      <c r="K76" s="63"/>
-      <c r="L76" s="64"/>
+      <c r="J76" s="70"/>
+      <c r="K76" s="70"/>
+      <c r="L76" s="71"/>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="1"/>
@@ -3314,19 +3312,19 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="1"/>
-      <c r="B80" s="77" t="s">
+      <c r="B80" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="79"/>
-      <c r="D80" s="79"/>
-      <c r="E80" s="79"/>
-      <c r="F80" s="79"/>
-      <c r="G80" s="79"/>
-      <c r="H80" s="79"/>
-      <c r="I80" s="79"/>
-      <c r="J80" s="79"/>
-      <c r="K80" s="79"/>
-      <c r="L80" s="78"/>
+      <c r="C80" s="65"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="65"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="65"/>
+      <c r="J80" s="65"/>
+      <c r="K80" s="65"/>
+      <c r="L80" s="66"/>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="1"/>
@@ -3347,54 +3345,54 @@
       <c r="B82" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C82" s="39"/>
-      <c r="D82" s="40"/>
-      <c r="E82" s="41"/>
+      <c r="C82" s="97"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="98"/>
       <c r="F82" s="13"/>
-      <c r="G82" s="86" t="s">
+      <c r="G82" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="H82" s="65"/>
-      <c r="I82" s="66"/>
-      <c r="J82" s="99"/>
-      <c r="K82" s="100"/>
-      <c r="L82" s="101"/>
+      <c r="H82" s="100"/>
+      <c r="I82" s="101"/>
+      <c r="J82" s="102"/>
+      <c r="K82" s="103"/>
+      <c r="L82" s="104"/>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="1"/>
       <c r="B83" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C83" s="39"/>
-      <c r="D83" s="40"/>
-      <c r="E83" s="41"/>
+      <c r="C83" s="97"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="98"/>
       <c r="F83" s="2"/>
-      <c r="G83" s="86" t="s">
+      <c r="G83" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="H83" s="65"/>
-      <c r="I83" s="66"/>
-      <c r="J83" s="99"/>
-      <c r="K83" s="100"/>
-      <c r="L83" s="101"/>
+      <c r="H83" s="100"/>
+      <c r="I83" s="101"/>
+      <c r="J83" s="102"/>
+      <c r="K83" s="103"/>
+      <c r="L83" s="104"/>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="1"/>
       <c r="B84" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C84" s="39"/>
-      <c r="D84" s="40"/>
-      <c r="E84" s="41"/>
+      <c r="C84" s="97"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="98"/>
       <c r="F84" s="8"/>
-      <c r="G84" s="86" t="s">
+      <c r="G84" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="H84" s="65"/>
-      <c r="I84" s="66"/>
-      <c r="J84" s="99"/>
-      <c r="K84" s="100"/>
-      <c r="L84" s="101"/>
+      <c r="H84" s="100"/>
+      <c r="I84" s="101"/>
+      <c r="J84" s="102"/>
+      <c r="K84" s="103"/>
+      <c r="L84" s="104"/>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="1"/>
@@ -3426,525 +3424,525 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="1"/>
-      <c r="B87" s="77" t="s">
+      <c r="B87" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="79"/>
-      <c r="D87" s="79"/>
-      <c r="E87" s="79"/>
-      <c r="F87" s="79"/>
-      <c r="G87" s="79"/>
-      <c r="H87" s="79"/>
-      <c r="I87" s="79"/>
-      <c r="J87" s="78"/>
-      <c r="K87" s="77" t="s">
+      <c r="C87" s="65"/>
+      <c r="D87" s="65"/>
+      <c r="E87" s="65"/>
+      <c r="F87" s="65"/>
+      <c r="G87" s="65"/>
+      <c r="H87" s="65"/>
+      <c r="I87" s="65"/>
+      <c r="J87" s="66"/>
+      <c r="K87" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="L87" s="78"/>
+      <c r="L87" s="66"/>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="1"/>
-      <c r="B88" s="130" t="s">
+      <c r="B88" s="106" t="s">
         <v>38</v>
       </c>
-      <c r="C88" s="131"/>
-      <c r="D88" s="131"/>
-      <c r="E88" s="131"/>
-      <c r="F88" s="131"/>
-      <c r="G88" s="131"/>
-      <c r="H88" s="131"/>
-      <c r="I88" s="131"/>
-      <c r="J88" s="132"/>
-      <c r="K88" s="133"/>
-      <c r="L88" s="134"/>
+      <c r="C88" s="107"/>
+      <c r="D88" s="107"/>
+      <c r="E88" s="107"/>
+      <c r="F88" s="107"/>
+      <c r="G88" s="107"/>
+      <c r="H88" s="107"/>
+      <c r="I88" s="107"/>
+      <c r="J88" s="108"/>
+      <c r="K88" s="109"/>
+      <c r="L88" s="110"/>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" s="1"/>
-      <c r="B89" s="135" t="s">
+      <c r="B89" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="C89" s="136"/>
-      <c r="D89" s="136"/>
-      <c r="E89" s="136"/>
-      <c r="F89" s="136"/>
-      <c r="G89" s="136"/>
-      <c r="H89" s="136"/>
-      <c r="I89" s="136"/>
-      <c r="J89" s="137"/>
-      <c r="K89" s="44"/>
-      <c r="L89" s="138"/>
+      <c r="C89" s="75"/>
+      <c r="D89" s="75"/>
+      <c r="E89" s="75"/>
+      <c r="F89" s="75"/>
+      <c r="G89" s="75"/>
+      <c r="H89" s="75"/>
+      <c r="I89" s="75"/>
+      <c r="J89" s="76"/>
+      <c r="K89" s="77"/>
+      <c r="L89" s="78"/>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="1"/>
-      <c r="B90" s="135" t="s">
+      <c r="B90" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="C90" s="136"/>
-      <c r="D90" s="136"/>
-      <c r="E90" s="136"/>
-      <c r="F90" s="136"/>
-      <c r="G90" s="136"/>
-      <c r="H90" s="136"/>
-      <c r="I90" s="136"/>
-      <c r="J90" s="137"/>
-      <c r="K90" s="44"/>
-      <c r="L90" s="138"/>
+      <c r="C90" s="75"/>
+      <c r="D90" s="75"/>
+      <c r="E90" s="75"/>
+      <c r="F90" s="75"/>
+      <c r="G90" s="75"/>
+      <c r="H90" s="75"/>
+      <c r="I90" s="75"/>
+      <c r="J90" s="76"/>
+      <c r="K90" s="77"/>
+      <c r="L90" s="78"/>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="1"/>
-      <c r="B91" s="135" t="s">
+      <c r="B91" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="C91" s="136"/>
-      <c r="D91" s="136"/>
-      <c r="E91" s="136"/>
-      <c r="F91" s="136"/>
-      <c r="G91" s="136"/>
-      <c r="H91" s="136"/>
-      <c r="I91" s="136"/>
-      <c r="J91" s="137"/>
-      <c r="K91" s="44"/>
-      <c r="L91" s="138"/>
+      <c r="C91" s="75"/>
+      <c r="D91" s="75"/>
+      <c r="E91" s="75"/>
+      <c r="F91" s="75"/>
+      <c r="G91" s="75"/>
+      <c r="H91" s="75"/>
+      <c r="I91" s="75"/>
+      <c r="J91" s="76"/>
+      <c r="K91" s="77"/>
+      <c r="L91" s="78"/>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="1"/>
-      <c r="B92" s="135" t="s">
+      <c r="B92" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="C92" s="136"/>
-      <c r="D92" s="136"/>
-      <c r="E92" s="136"/>
-      <c r="F92" s="136"/>
-      <c r="G92" s="136"/>
-      <c r="H92" s="136"/>
-      <c r="I92" s="136"/>
-      <c r="J92" s="137"/>
-      <c r="K92" s="44"/>
-      <c r="L92" s="138"/>
+      <c r="C92" s="75"/>
+      <c r="D92" s="75"/>
+      <c r="E92" s="75"/>
+      <c r="F92" s="75"/>
+      <c r="G92" s="75"/>
+      <c r="H92" s="75"/>
+      <c r="I92" s="75"/>
+      <c r="J92" s="76"/>
+      <c r="K92" s="77"/>
+      <c r="L92" s="78"/>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="1"/>
-      <c r="B93" s="135" t="s">
+      <c r="B93" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="C93" s="136"/>
-      <c r="D93" s="136"/>
-      <c r="E93" s="136"/>
-      <c r="F93" s="136"/>
-      <c r="G93" s="136"/>
-      <c r="H93" s="136"/>
-      <c r="I93" s="136"/>
-      <c r="J93" s="137"/>
-      <c r="K93" s="44"/>
-      <c r="L93" s="138"/>
+      <c r="C93" s="75"/>
+      <c r="D93" s="75"/>
+      <c r="E93" s="75"/>
+      <c r="F93" s="75"/>
+      <c r="G93" s="75"/>
+      <c r="H93" s="75"/>
+      <c r="I93" s="75"/>
+      <c r="J93" s="76"/>
+      <c r="K93" s="77"/>
+      <c r="L93" s="78"/>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" s="1"/>
-      <c r="B94" s="135" t="s">
+      <c r="B94" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="C94" s="136"/>
-      <c r="D94" s="136"/>
-      <c r="E94" s="136"/>
-      <c r="F94" s="136"/>
-      <c r="G94" s="136"/>
-      <c r="H94" s="136"/>
-      <c r="I94" s="136"/>
-      <c r="J94" s="137"/>
-      <c r="K94" s="44"/>
-      <c r="L94" s="138"/>
+      <c r="C94" s="75"/>
+      <c r="D94" s="75"/>
+      <c r="E94" s="75"/>
+      <c r="F94" s="75"/>
+      <c r="G94" s="75"/>
+      <c r="H94" s="75"/>
+      <c r="I94" s="75"/>
+      <c r="J94" s="76"/>
+      <c r="K94" s="77"/>
+      <c r="L94" s="78"/>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="1"/>
-      <c r="B95" s="135" t="s">
+      <c r="B95" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="C95" s="136"/>
-      <c r="D95" s="136"/>
-      <c r="E95" s="136"/>
-      <c r="F95" s="136"/>
-      <c r="G95" s="136"/>
-      <c r="H95" s="136"/>
-      <c r="I95" s="136"/>
-      <c r="J95" s="137"/>
-      <c r="K95" s="44"/>
-      <c r="L95" s="138"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="75"/>
+      <c r="E95" s="75"/>
+      <c r="F95" s="75"/>
+      <c r="G95" s="75"/>
+      <c r="H95" s="75"/>
+      <c r="I95" s="75"/>
+      <c r="J95" s="76"/>
+      <c r="K95" s="77"/>
+      <c r="L95" s="78"/>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="1"/>
-      <c r="B96" s="135" t="s">
+      <c r="B96" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="C96" s="136"/>
-      <c r="D96" s="136"/>
-      <c r="E96" s="136"/>
-      <c r="F96" s="136"/>
-      <c r="G96" s="136"/>
-      <c r="H96" s="136"/>
-      <c r="I96" s="136"/>
-      <c r="J96" s="137"/>
-      <c r="K96" s="44"/>
-      <c r="L96" s="138"/>
+      <c r="C96" s="75"/>
+      <c r="D96" s="75"/>
+      <c r="E96" s="75"/>
+      <c r="F96" s="75"/>
+      <c r="G96" s="75"/>
+      <c r="H96" s="75"/>
+      <c r="I96" s="75"/>
+      <c r="J96" s="76"/>
+      <c r="K96" s="77"/>
+      <c r="L96" s="78"/>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="1"/>
-      <c r="B97" s="135" t="s">
+      <c r="B97" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="C97" s="136"/>
-      <c r="D97" s="136"/>
-      <c r="E97" s="136"/>
-      <c r="F97" s="136"/>
-      <c r="G97" s="136"/>
-      <c r="H97" s="136"/>
-      <c r="I97" s="136"/>
-      <c r="J97" s="137"/>
-      <c r="K97" s="44"/>
-      <c r="L97" s="138"/>
+      <c r="C97" s="75"/>
+      <c r="D97" s="75"/>
+      <c r="E97" s="75"/>
+      <c r="F97" s="75"/>
+      <c r="G97" s="75"/>
+      <c r="H97" s="75"/>
+      <c r="I97" s="75"/>
+      <c r="J97" s="76"/>
+      <c r="K97" s="77"/>
+      <c r="L97" s="78"/>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="1"/>
-      <c r="B98" s="135" t="s">
+      <c r="B98" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="C98" s="136"/>
-      <c r="D98" s="136"/>
-      <c r="E98" s="136"/>
-      <c r="F98" s="136"/>
-      <c r="G98" s="136"/>
-      <c r="H98" s="136"/>
-      <c r="I98" s="136"/>
-      <c r="J98" s="137"/>
-      <c r="K98" s="44"/>
-      <c r="L98" s="138"/>
+      <c r="C98" s="75"/>
+      <c r="D98" s="75"/>
+      <c r="E98" s="75"/>
+      <c r="F98" s="75"/>
+      <c r="G98" s="75"/>
+      <c r="H98" s="75"/>
+      <c r="I98" s="75"/>
+      <c r="J98" s="76"/>
+      <c r="K98" s="77"/>
+      <c r="L98" s="78"/>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="1"/>
-      <c r="B99" s="135" t="s">
+      <c r="B99" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="C99" s="136"/>
-      <c r="D99" s="136"/>
-      <c r="E99" s="136"/>
-      <c r="F99" s="136"/>
-      <c r="G99" s="136"/>
-      <c r="H99" s="136"/>
-      <c r="I99" s="136"/>
-      <c r="J99" s="137"/>
-      <c r="K99" s="44"/>
-      <c r="L99" s="138"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="75"/>
+      <c r="G99" s="75"/>
+      <c r="H99" s="75"/>
+      <c r="I99" s="75"/>
+      <c r="J99" s="76"/>
+      <c r="K99" s="77"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="1"/>
-      <c r="B100" s="135" t="s">
+      <c r="B100" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="C100" s="136"/>
-      <c r="D100" s="136"/>
-      <c r="E100" s="136"/>
-      <c r="F100" s="136"/>
-      <c r="G100" s="136"/>
-      <c r="H100" s="136"/>
-      <c r="I100" s="136"/>
-      <c r="J100" s="137"/>
-      <c r="K100" s="44"/>
-      <c r="L100" s="138"/>
+      <c r="C100" s="75"/>
+      <c r="D100" s="75"/>
+      <c r="E100" s="75"/>
+      <c r="F100" s="75"/>
+      <c r="G100" s="75"/>
+      <c r="H100" s="75"/>
+      <c r="I100" s="75"/>
+      <c r="J100" s="76"/>
+      <c r="K100" s="77"/>
+      <c r="L100" s="78"/>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" s="1"/>
-      <c r="B101" s="135" t="s">
+      <c r="B101" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="C101" s="136"/>
-      <c r="D101" s="136"/>
-      <c r="E101" s="136"/>
-      <c r="F101" s="136"/>
-      <c r="G101" s="136"/>
-      <c r="H101" s="136"/>
-      <c r="I101" s="136"/>
-      <c r="J101" s="137"/>
-      <c r="K101" s="44"/>
-      <c r="L101" s="138"/>
+      <c r="C101" s="75"/>
+      <c r="D101" s="75"/>
+      <c r="E101" s="75"/>
+      <c r="F101" s="75"/>
+      <c r="G101" s="75"/>
+      <c r="H101" s="75"/>
+      <c r="I101" s="75"/>
+      <c r="J101" s="76"/>
+      <c r="K101" s="77"/>
+      <c r="L101" s="78"/>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" s="1"/>
-      <c r="B102" s="135" t="s">
+      <c r="B102" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="C102" s="136"/>
-      <c r="D102" s="136"/>
-      <c r="E102" s="136"/>
-      <c r="F102" s="136"/>
-      <c r="G102" s="136"/>
-      <c r="H102" s="136"/>
-      <c r="I102" s="136"/>
-      <c r="J102" s="137"/>
-      <c r="K102" s="44"/>
-      <c r="L102" s="138"/>
+      <c r="C102" s="75"/>
+      <c r="D102" s="75"/>
+      <c r="E102" s="75"/>
+      <c r="F102" s="75"/>
+      <c r="G102" s="75"/>
+      <c r="H102" s="75"/>
+      <c r="I102" s="75"/>
+      <c r="J102" s="76"/>
+      <c r="K102" s="77"/>
+      <c r="L102" s="78"/>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" s="1"/>
-      <c r="B103" s="135" t="s">
+      <c r="B103" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="C103" s="136"/>
-      <c r="D103" s="136"/>
-      <c r="E103" s="136"/>
-      <c r="F103" s="136"/>
-      <c r="G103" s="136"/>
-      <c r="H103" s="136"/>
-      <c r="I103" s="136"/>
-      <c r="J103" s="137"/>
-      <c r="K103" s="44"/>
-      <c r="L103" s="138"/>
+      <c r="C103" s="75"/>
+      <c r="D103" s="75"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="75"/>
+      <c r="G103" s="75"/>
+      <c r="H103" s="75"/>
+      <c r="I103" s="75"/>
+      <c r="J103" s="76"/>
+      <c r="K103" s="77"/>
+      <c r="L103" s="78"/>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" s="1"/>
-      <c r="B104" s="135" t="s">
+      <c r="B104" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="C104" s="136"/>
-      <c r="D104" s="136"/>
-      <c r="E104" s="136"/>
-      <c r="F104" s="136"/>
-      <c r="G104" s="136"/>
-      <c r="H104" s="136"/>
-      <c r="I104" s="136"/>
-      <c r="J104" s="137"/>
-      <c r="K104" s="44"/>
-      <c r="L104" s="138"/>
+      <c r="C104" s="75"/>
+      <c r="D104" s="75"/>
+      <c r="E104" s="75"/>
+      <c r="F104" s="75"/>
+      <c r="G104" s="75"/>
+      <c r="H104" s="75"/>
+      <c r="I104" s="75"/>
+      <c r="J104" s="76"/>
+      <c r="K104" s="77"/>
+      <c r="L104" s="78"/>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" s="1"/>
-      <c r="B105" s="135" t="s">
+      <c r="B105" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="C105" s="136"/>
-      <c r="D105" s="136"/>
-      <c r="E105" s="136"/>
-      <c r="F105" s="136"/>
-      <c r="G105" s="136"/>
-      <c r="H105" s="136"/>
-      <c r="I105" s="136"/>
-      <c r="J105" s="137"/>
-      <c r="K105" s="44"/>
-      <c r="L105" s="138"/>
+      <c r="C105" s="75"/>
+      <c r="D105" s="75"/>
+      <c r="E105" s="75"/>
+      <c r="F105" s="75"/>
+      <c r="G105" s="75"/>
+      <c r="H105" s="75"/>
+      <c r="I105" s="75"/>
+      <c r="J105" s="76"/>
+      <c r="K105" s="77"/>
+      <c r="L105" s="78"/>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" s="1"/>
-      <c r="B106" s="135" t="s">
+      <c r="B106" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="C106" s="136"/>
-      <c r="D106" s="136"/>
-      <c r="E106" s="136"/>
-      <c r="F106" s="136"/>
-      <c r="G106" s="136"/>
-      <c r="H106" s="136"/>
-      <c r="I106" s="136"/>
-      <c r="J106" s="137"/>
-      <c r="K106" s="44"/>
-      <c r="L106" s="138"/>
+      <c r="C106" s="75"/>
+      <c r="D106" s="75"/>
+      <c r="E106" s="75"/>
+      <c r="F106" s="75"/>
+      <c r="G106" s="75"/>
+      <c r="H106" s="75"/>
+      <c r="I106" s="75"/>
+      <c r="J106" s="76"/>
+      <c r="K106" s="77"/>
+      <c r="L106" s="78"/>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="1"/>
-      <c r="B107" s="135" t="s">
+      <c r="B107" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="C107" s="136"/>
-      <c r="D107" s="136"/>
-      <c r="E107" s="136"/>
-      <c r="F107" s="136"/>
-      <c r="G107" s="136"/>
-      <c r="H107" s="136"/>
-      <c r="I107" s="136"/>
-      <c r="J107" s="137"/>
-      <c r="K107" s="44"/>
-      <c r="L107" s="138"/>
+      <c r="C107" s="75"/>
+      <c r="D107" s="75"/>
+      <c r="E107" s="75"/>
+      <c r="F107" s="75"/>
+      <c r="G107" s="75"/>
+      <c r="H107" s="75"/>
+      <c r="I107" s="75"/>
+      <c r="J107" s="76"/>
+      <c r="K107" s="77"/>
+      <c r="L107" s="78"/>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" s="1"/>
-      <c r="B108" s="135" t="s">
+      <c r="B108" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="C108" s="136"/>
-      <c r="D108" s="136"/>
-      <c r="E108" s="136"/>
-      <c r="F108" s="136"/>
-      <c r="G108" s="136"/>
-      <c r="H108" s="136"/>
-      <c r="I108" s="136"/>
-      <c r="J108" s="137"/>
-      <c r="K108" s="44"/>
-      <c r="L108" s="138"/>
+      <c r="C108" s="75"/>
+      <c r="D108" s="75"/>
+      <c r="E108" s="75"/>
+      <c r="F108" s="75"/>
+      <c r="G108" s="75"/>
+      <c r="H108" s="75"/>
+      <c r="I108" s="75"/>
+      <c r="J108" s="76"/>
+      <c r="K108" s="77"/>
+      <c r="L108" s="78"/>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" s="1"/>
-      <c r="B109" s="135" t="s">
+      <c r="B109" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="C109" s="136"/>
-      <c r="D109" s="136"/>
-      <c r="E109" s="136"/>
-      <c r="F109" s="136"/>
-      <c r="G109" s="136"/>
-      <c r="H109" s="136"/>
-      <c r="I109" s="136"/>
-      <c r="J109" s="137"/>
-      <c r="K109" s="44"/>
-      <c r="L109" s="138"/>
+      <c r="C109" s="75"/>
+      <c r="D109" s="75"/>
+      <c r="E109" s="75"/>
+      <c r="F109" s="75"/>
+      <c r="G109" s="75"/>
+      <c r="H109" s="75"/>
+      <c r="I109" s="75"/>
+      <c r="J109" s="76"/>
+      <c r="K109" s="77"/>
+      <c r="L109" s="78"/>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" s="1"/>
-      <c r="B110" s="135" t="s">
+      <c r="B110" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="C110" s="136"/>
-      <c r="D110" s="136"/>
-      <c r="E110" s="136"/>
-      <c r="F110" s="136"/>
-      <c r="G110" s="136"/>
-      <c r="H110" s="136"/>
-      <c r="I110" s="136"/>
-      <c r="J110" s="137"/>
-      <c r="K110" s="44"/>
-      <c r="L110" s="138"/>
+      <c r="C110" s="75"/>
+      <c r="D110" s="75"/>
+      <c r="E110" s="75"/>
+      <c r="F110" s="75"/>
+      <c r="G110" s="75"/>
+      <c r="H110" s="75"/>
+      <c r="I110" s="75"/>
+      <c r="J110" s="76"/>
+      <c r="K110" s="77"/>
+      <c r="L110" s="78"/>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" s="1"/>
-      <c r="B111" s="135" t="s">
+      <c r="B111" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="C111" s="136"/>
-      <c r="D111" s="136"/>
-      <c r="E111" s="136"/>
-      <c r="F111" s="136"/>
-      <c r="G111" s="136"/>
-      <c r="H111" s="136"/>
-      <c r="I111" s="136"/>
-      <c r="J111" s="137"/>
-      <c r="K111" s="44"/>
-      <c r="L111" s="138"/>
+      <c r="C111" s="75"/>
+      <c r="D111" s="75"/>
+      <c r="E111" s="75"/>
+      <c r="F111" s="75"/>
+      <c r="G111" s="75"/>
+      <c r="H111" s="75"/>
+      <c r="I111" s="75"/>
+      <c r="J111" s="76"/>
+      <c r="K111" s="77"/>
+      <c r="L111" s="78"/>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" s="1"/>
-      <c r="B112" s="135" t="s">
+      <c r="B112" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="C112" s="136"/>
-      <c r="D112" s="136"/>
-      <c r="E112" s="136"/>
-      <c r="F112" s="136"/>
-      <c r="G112" s="136"/>
-      <c r="H112" s="136"/>
-      <c r="I112" s="136"/>
-      <c r="J112" s="137"/>
-      <c r="K112" s="44"/>
-      <c r="L112" s="138"/>
+      <c r="C112" s="75"/>
+      <c r="D112" s="75"/>
+      <c r="E112" s="75"/>
+      <c r="F112" s="75"/>
+      <c r="G112" s="75"/>
+      <c r="H112" s="75"/>
+      <c r="I112" s="75"/>
+      <c r="J112" s="76"/>
+      <c r="K112" s="77"/>
+      <c r="L112" s="78"/>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" s="1"/>
-      <c r="B113" s="135" t="s">
+      <c r="B113" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="C113" s="136"/>
-      <c r="D113" s="136"/>
-      <c r="E113" s="136"/>
-      <c r="F113" s="136"/>
-      <c r="G113" s="136"/>
-      <c r="H113" s="136"/>
-      <c r="I113" s="136"/>
-      <c r="J113" s="137"/>
-      <c r="K113" s="44"/>
-      <c r="L113" s="138"/>
+      <c r="C113" s="75"/>
+      <c r="D113" s="75"/>
+      <c r="E113" s="75"/>
+      <c r="F113" s="75"/>
+      <c r="G113" s="75"/>
+      <c r="H113" s="75"/>
+      <c r="I113" s="75"/>
+      <c r="J113" s="76"/>
+      <c r="K113" s="77"/>
+      <c r="L113" s="78"/>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" s="1"/>
-      <c r="B114" s="135" t="s">
+      <c r="B114" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C114" s="136"/>
-      <c r="D114" s="136"/>
-      <c r="E114" s="136"/>
-      <c r="F114" s="136"/>
-      <c r="G114" s="136"/>
-      <c r="H114" s="136"/>
-      <c r="I114" s="136"/>
-      <c r="J114" s="137"/>
-      <c r="K114" s="44"/>
-      <c r="L114" s="138"/>
+      <c r="C114" s="75"/>
+      <c r="D114" s="75"/>
+      <c r="E114" s="75"/>
+      <c r="F114" s="75"/>
+      <c r="G114" s="75"/>
+      <c r="H114" s="75"/>
+      <c r="I114" s="75"/>
+      <c r="J114" s="76"/>
+      <c r="K114" s="77"/>
+      <c r="L114" s="78"/>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" s="1"/>
-      <c r="B115" s="135" t="s">
+      <c r="B115" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C115" s="136"/>
-      <c r="D115" s="136"/>
-      <c r="E115" s="136"/>
-      <c r="F115" s="136"/>
-      <c r="G115" s="136"/>
-      <c r="H115" s="136"/>
-      <c r="I115" s="136"/>
-      <c r="J115" s="137"/>
-      <c r="K115" s="44"/>
-      <c r="L115" s="138"/>
+      <c r="C115" s="75"/>
+      <c r="D115" s="75"/>
+      <c r="E115" s="75"/>
+      <c r="F115" s="75"/>
+      <c r="G115" s="75"/>
+      <c r="H115" s="75"/>
+      <c r="I115" s="75"/>
+      <c r="J115" s="76"/>
+      <c r="K115" s="77"/>
+      <c r="L115" s="78"/>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" s="1"/>
-      <c r="B116" s="47"/>
-      <c r="C116" s="48"/>
-      <c r="D116" s="48"/>
-      <c r="E116" s="48"/>
-      <c r="F116" s="48"/>
-      <c r="G116" s="48"/>
-      <c r="H116" s="48"/>
-      <c r="I116" s="48"/>
-      <c r="J116" s="49"/>
-      <c r="K116" s="47"/>
-      <c r="L116" s="49"/>
+      <c r="B116" s="139"/>
+      <c r="C116" s="140"/>
+      <c r="D116" s="140"/>
+      <c r="E116" s="140"/>
+      <c r="F116" s="140"/>
+      <c r="G116" s="140"/>
+      <c r="H116" s="140"/>
+      <c r="I116" s="140"/>
+      <c r="J116" s="141"/>
+      <c r="K116" s="139"/>
+      <c r="L116" s="141"/>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" s="1"/>
-      <c r="B117" s="50"/>
-      <c r="C117" s="42"/>
-      <c r="D117" s="42"/>
-      <c r="E117" s="42"/>
-      <c r="F117" s="42"/>
-      <c r="G117" s="42"/>
-      <c r="H117" s="42"/>
-      <c r="I117" s="42"/>
-      <c r="J117" s="51"/>
-      <c r="K117" s="50"/>
-      <c r="L117" s="51"/>
+      <c r="B117" s="136"/>
+      <c r="C117" s="37"/>
+      <c r="D117" s="37"/>
+      <c r="E117" s="37"/>
+      <c r="F117" s="37"/>
+      <c r="G117" s="37"/>
+      <c r="H117" s="37"/>
+      <c r="I117" s="37"/>
+      <c r="J117" s="142"/>
+      <c r="K117" s="136"/>
+      <c r="L117" s="142"/>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" s="1"/>
-      <c r="B118" s="50"/>
-      <c r="C118" s="42"/>
-      <c r="D118" s="42"/>
-      <c r="E118" s="42"/>
-      <c r="F118" s="42"/>
-      <c r="G118" s="42"/>
-      <c r="H118" s="42"/>
-      <c r="I118" s="42"/>
-      <c r="J118" s="51"/>
-      <c r="K118" s="50"/>
-      <c r="L118" s="51"/>
+      <c r="B118" s="136"/>
+      <c r="C118" s="37"/>
+      <c r="D118" s="37"/>
+      <c r="E118" s="37"/>
+      <c r="F118" s="37"/>
+      <c r="G118" s="37"/>
+      <c r="H118" s="37"/>
+      <c r="I118" s="37"/>
+      <c r="J118" s="142"/>
+      <c r="K118" s="136"/>
+      <c r="L118" s="142"/>
     </row>
     <row r="119" spans="1:12" ht="45" customHeight="1">
       <c r="A119" s="1"/>
-      <c r="B119" s="52"/>
-      <c r="C119" s="53"/>
-      <c r="D119" s="53"/>
-      <c r="E119" s="53"/>
-      <c r="F119" s="53"/>
-      <c r="G119" s="53"/>
-      <c r="H119" s="53"/>
-      <c r="I119" s="53"/>
-      <c r="J119" s="54"/>
-      <c r="K119" s="52"/>
-      <c r="L119" s="54"/>
+      <c r="B119" s="143"/>
+      <c r="C119" s="105"/>
+      <c r="D119" s="105"/>
+      <c r="E119" s="105"/>
+      <c r="F119" s="105"/>
+      <c r="G119" s="105"/>
+      <c r="H119" s="105"/>
+      <c r="I119" s="105"/>
+      <c r="J119" s="144"/>
+      <c r="K119" s="143"/>
+      <c r="L119" s="144"/>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" s="1"/>
@@ -3962,65 +3960,65 @@
     </row>
     <row r="121" spans="1:12" ht="30" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="68"/>
-      <c r="C121" s="69"/>
-      <c r="D121" s="68"/>
-      <c r="E121" s="74"/>
-      <c r="F121" s="69"/>
-      <c r="G121" s="111"/>
-      <c r="H121" s="112"/>
-      <c r="I121" s="112"/>
-      <c r="J121" s="113"/>
-      <c r="K121" s="111"/>
-      <c r="L121" s="113"/>
+      <c r="B121" s="79"/>
+      <c r="C121" s="80"/>
+      <c r="D121" s="79"/>
+      <c r="E121" s="85"/>
+      <c r="F121" s="80"/>
+      <c r="G121" s="88"/>
+      <c r="H121" s="89"/>
+      <c r="I121" s="89"/>
+      <c r="J121" s="90"/>
+      <c r="K121" s="88"/>
+      <c r="L121" s="90"/>
     </row>
     <row r="122" spans="1:12">
-      <c r="B122" s="70"/>
-      <c r="C122" s="71"/>
-      <c r="D122" s="70"/>
-      <c r="E122" s="75"/>
-      <c r="F122" s="71"/>
-      <c r="G122" s="114"/>
-      <c r="H122" s="115"/>
-      <c r="I122" s="115"/>
-      <c r="J122" s="116"/>
-      <c r="K122" s="114"/>
-      <c r="L122" s="116"/>
+      <c r="B122" s="81"/>
+      <c r="C122" s="82"/>
+      <c r="D122" s="81"/>
+      <c r="E122" s="86"/>
+      <c r="F122" s="82"/>
+      <c r="G122" s="91"/>
+      <c r="H122" s="92"/>
+      <c r="I122" s="92"/>
+      <c r="J122" s="93"/>
+      <c r="K122" s="91"/>
+      <c r="L122" s="93"/>
     </row>
     <row r="123" spans="1:12">
-      <c r="B123" s="72"/>
-      <c r="C123" s="73"/>
-      <c r="D123" s="72"/>
-      <c r="E123" s="76"/>
-      <c r="F123" s="73"/>
-      <c r="G123" s="117"/>
-      <c r="H123" s="118"/>
-      <c r="I123" s="118"/>
-      <c r="J123" s="119"/>
-      <c r="K123" s="117"/>
-      <c r="L123" s="119"/>
+      <c r="B123" s="83"/>
+      <c r="C123" s="84"/>
+      <c r="D123" s="83"/>
+      <c r="E123" s="87"/>
+      <c r="F123" s="84"/>
+      <c r="G123" s="94"/>
+      <c r="H123" s="95"/>
+      <c r="I123" s="95"/>
+      <c r="J123" s="96"/>
+      <c r="K123" s="94"/>
+      <c r="L123" s="96"/>
     </row>
     <row r="124" spans="1:12" s="31" customFormat="1" ht="47.25" customHeight="1">
       <c r="A124" s="25"/>
-      <c r="B124" s="139" t="s">
+      <c r="B124" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C124" s="140"/>
-      <c r="D124" s="125" t="s">
+      <c r="C124" s="39"/>
+      <c r="D124" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E124" s="127"/>
-      <c r="F124" s="126"/>
-      <c r="G124" s="125" t="s">
+      <c r="E124" s="41"/>
+      <c r="F124" s="42"/>
+      <c r="G124" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="H124" s="127"/>
-      <c r="I124" s="127"/>
-      <c r="J124" s="126"/>
-      <c r="K124" s="125" t="s">
+      <c r="H124" s="41"/>
+      <c r="I124" s="41"/>
+      <c r="J124" s="42"/>
+      <c r="K124" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="L124" s="126"/>
+      <c r="L124" s="42"/>
     </row>
     <row r="126" spans="1:12" ht="27" customHeight="1"/>
     <row r="127" spans="1:12" ht="27" customHeight="1"/>
@@ -4034,13 +4032,13 @@
         <v>0</v>
       </c>
       <c r="C132" s="2"/>
-      <c r="D132" s="122" t="str">
+      <c r="D132" s="46" t="str">
         <f>D68</f>
         <v>MHOS-SSM-EL-0001</v>
       </c>
-      <c r="E132" s="123"/>
-      <c r="F132" s="123"/>
-      <c r="G132" s="124"/>
+      <c r="E132" s="72"/>
+      <c r="F132" s="72"/>
+      <c r="G132" s="47"/>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
@@ -4053,10 +4051,10 @@
         <v>1</v>
       </c>
       <c r="C133" s="2"/>
-      <c r="D133" s="141"/>
-      <c r="E133" s="141"/>
-      <c r="F133" s="141"/>
-      <c r="G133" s="141"/>
+      <c r="D133" s="73"/>
+      <c r="E133" s="73"/>
+      <c r="F133" s="73"/>
+      <c r="G133" s="73"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
@@ -4082,11 +4080,11 @@
       <c r="B135" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C135" s="40"/>
-      <c r="D135" s="40"/>
-      <c r="E135" s="40"/>
-      <c r="F135" s="40"/>
-      <c r="G135" s="40"/>
+      <c r="C135" s="67"/>
+      <c r="D135" s="67"/>
+      <c r="E135" s="67"/>
+      <c r="F135" s="67"/>
+      <c r="G135" s="67"/>
       <c r="H135" s="23"/>
       <c r="I135" s="23"/>
       <c r="J135" s="23"/>
@@ -4096,34 +4094,34 @@
     <row r="136" spans="1:12">
       <c r="A136" s="1"/>
       <c r="B136" s="4"/>
-      <c r="C136" s="142"/>
-      <c r="D136" s="142"/>
+      <c r="C136" s="68"/>
+      <c r="D136" s="68"/>
       <c r="E136" s="2"/>
-      <c r="F136" s="142"/>
-      <c r="G136" s="142"/>
+      <c r="F136" s="68"/>
+      <c r="G136" s="68"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
-      <c r="J136" s="142"/>
-      <c r="K136" s="142"/>
-      <c r="L136" s="143"/>
+      <c r="J136" s="68"/>
+      <c r="K136" s="68"/>
+      <c r="L136" s="69"/>
     </row>
     <row r="137" spans="1:12">
       <c r="A137" s="1"/>
       <c r="B137" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C137" s="63"/>
-      <c r="D137" s="63"/>
-      <c r="E137" s="63"/>
-      <c r="F137" s="63"/>
-      <c r="G137" s="63"/>
+      <c r="C137" s="70"/>
+      <c r="D137" s="70"/>
+      <c r="E137" s="70"/>
+      <c r="F137" s="70"/>
+      <c r="G137" s="70"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J137" s="63"/>
-      <c r="K137" s="63"/>
-      <c r="L137" s="64"/>
+      <c r="J137" s="70"/>
+      <c r="K137" s="70"/>
+      <c r="L137" s="71"/>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="1"/>
@@ -4155,19 +4153,19 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="1"/>
-      <c r="B140" s="77" t="s">
+      <c r="B140" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="C140" s="79"/>
-      <c r="D140" s="79"/>
-      <c r="E140" s="79"/>
-      <c r="F140" s="79"/>
-      <c r="G140" s="79"/>
-      <c r="H140" s="79"/>
-      <c r="I140" s="79"/>
-      <c r="J140" s="79"/>
-      <c r="K140" s="79"/>
-      <c r="L140" s="78"/>
+      <c r="C140" s="65"/>
+      <c r="D140" s="65"/>
+      <c r="E140" s="65"/>
+      <c r="F140" s="65"/>
+      <c r="G140" s="65"/>
+      <c r="H140" s="65"/>
+      <c r="I140" s="65"/>
+      <c r="J140" s="65"/>
+      <c r="K140" s="65"/>
+      <c r="L140" s="66"/>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" s="1"/>
@@ -4199,115 +4197,115 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" s="1"/>
-      <c r="B143" s="161"/>
-      <c r="C143" s="161"/>
-      <c r="D143" s="161"/>
-      <c r="E143" s="161"/>
-      <c r="F143" s="161"/>
-      <c r="G143" s="161"/>
-      <c r="H143" s="161"/>
-      <c r="I143" s="161"/>
-      <c r="J143" s="161"/>
-      <c r="K143" s="161"/>
-      <c r="L143" s="161"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="29"/>
+      <c r="D143" s="29"/>
+      <c r="E143" s="29"/>
+      <c r="F143" s="29"/>
+      <c r="G143" s="29"/>
+      <c r="H143" s="29"/>
+      <c r="I143" s="29"/>
+      <c r="J143" s="29"/>
+      <c r="K143" s="29"/>
+      <c r="L143" s="29"/>
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="1"/>
-      <c r="B144" s="161"/>
-      <c r="C144" s="161"/>
-      <c r="D144" s="161"/>
-      <c r="E144" s="161"/>
-      <c r="F144" s="161"/>
-      <c r="G144" s="161"/>
-      <c r="H144" s="161"/>
-      <c r="I144" s="161"/>
-      <c r="J144" s="161"/>
-      <c r="K144" s="161"/>
-      <c r="L144" s="161"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="29"/>
+      <c r="D144" s="29"/>
+      <c r="E144" s="29"/>
+      <c r="F144" s="29"/>
+      <c r="G144" s="29"/>
+      <c r="H144" s="29"/>
+      <c r="I144" s="29"/>
+      <c r="J144" s="29"/>
+      <c r="K144" s="29"/>
+      <c r="L144" s="29"/>
     </row>
     <row r="145" spans="1:12">
       <c r="A145" s="1"/>
-      <c r="B145" s="161"/>
-      <c r="C145" s="161"/>
-      <c r="D145" s="161"/>
-      <c r="E145" s="161"/>
-      <c r="F145" s="161"/>
-      <c r="G145" s="161"/>
-      <c r="H145" s="161"/>
-      <c r="I145" s="161"/>
-      <c r="J145" s="161"/>
-      <c r="K145" s="161"/>
-      <c r="L145" s="161"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="29"/>
+      <c r="D145" s="29"/>
+      <c r="E145" s="29"/>
+      <c r="F145" s="29"/>
+      <c r="G145" s="29"/>
+      <c r="H145" s="29"/>
+      <c r="I145" s="29"/>
+      <c r="J145" s="29"/>
+      <c r="K145" s="29"/>
+      <c r="L145" s="29"/>
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="1"/>
-      <c r="B146" s="161"/>
-      <c r="C146" s="161"/>
-      <c r="D146" s="161"/>
-      <c r="E146" s="161"/>
-      <c r="F146" s="161"/>
-      <c r="G146" s="161"/>
-      <c r="H146" s="161"/>
-      <c r="I146" s="161"/>
-      <c r="J146" s="161"/>
-      <c r="K146" s="161"/>
-      <c r="L146" s="161"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="29"/>
+      <c r="D146" s="29"/>
+      <c r="E146" s="29"/>
+      <c r="F146" s="29"/>
+      <c r="G146" s="29"/>
+      <c r="H146" s="29"/>
+      <c r="I146" s="29"/>
+      <c r="J146" s="29"/>
+      <c r="K146" s="29"/>
+      <c r="L146" s="29"/>
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="1"/>
-      <c r="B147" s="161"/>
-      <c r="C147" s="161"/>
-      <c r="D147" s="161"/>
-      <c r="E147" s="161"/>
-      <c r="F147" s="161"/>
-      <c r="G147" s="161"/>
-      <c r="H147" s="161"/>
-      <c r="I147" s="161"/>
-      <c r="J147" s="161"/>
-      <c r="K147" s="161"/>
-      <c r="L147" s="161"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="29"/>
+      <c r="D147" s="29"/>
+      <c r="E147" s="29"/>
+      <c r="F147" s="29"/>
+      <c r="G147" s="29"/>
+      <c r="H147" s="29"/>
+      <c r="I147" s="29"/>
+      <c r="J147" s="29"/>
+      <c r="K147" s="29"/>
+      <c r="L147" s="29"/>
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="1"/>
-      <c r="B148" s="161"/>
-      <c r="C148" s="161"/>
-      <c r="D148" s="161"/>
-      <c r="E148" s="161"/>
-      <c r="F148" s="161"/>
-      <c r="G148" s="161"/>
-      <c r="H148" s="161"/>
-      <c r="I148" s="161"/>
-      <c r="J148" s="161"/>
-      <c r="K148" s="161"/>
-      <c r="L148" s="161"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
+      <c r="D148" s="29"/>
+      <c r="E148" s="29"/>
+      <c r="F148" s="29"/>
+      <c r="G148" s="29"/>
+      <c r="H148" s="29"/>
+      <c r="I148" s="29"/>
+      <c r="J148" s="29"/>
+      <c r="K148" s="29"/>
+      <c r="L148" s="29"/>
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="1"/>
-      <c r="B149" s="161"/>
-      <c r="C149" s="161"/>
-      <c r="D149" s="161"/>
-      <c r="E149" s="161"/>
-      <c r="F149" s="161"/>
-      <c r="G149" s="161"/>
-      <c r="H149" s="161"/>
-      <c r="I149" s="161"/>
-      <c r="J149" s="161"/>
-      <c r="K149" s="161"/>
-      <c r="L149" s="161"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="29"/>
+      <c r="D149" s="29"/>
+      <c r="E149" s="29"/>
+      <c r="F149" s="29"/>
+      <c r="G149" s="29"/>
+      <c r="H149" s="29"/>
+      <c r="I149" s="29"/>
+      <c r="J149" s="29"/>
+      <c r="K149" s="29"/>
+      <c r="L149" s="29"/>
     </row>
     <row r="150" spans="1:12" ht="31.5" customHeight="1">
       <c r="A150" s="1"/>
-      <c r="B150" s="161"/>
-      <c r="C150" s="161"/>
-      <c r="D150" s="161"/>
-      <c r="E150" s="161"/>
-      <c r="F150" s="161"/>
-      <c r="G150" s="161"/>
-      <c r="H150" s="161"/>
-      <c r="I150" s="161"/>
-      <c r="J150" s="161"/>
-      <c r="K150" s="161"/>
-      <c r="L150" s="161"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="29"/>
+      <c r="D150" s="29"/>
+      <c r="E150" s="29"/>
+      <c r="F150" s="29"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+      <c r="I150" s="29"/>
+      <c r="J150" s="29"/>
+      <c r="K150" s="29"/>
+      <c r="L150" s="29"/>
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="1"/>
@@ -4325,21 +4323,21 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" s="1"/>
-      <c r="B152" s="42" t="s">
+      <c r="B152" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="C152" s="42"/>
-      <c r="D152" s="42"/>
-      <c r="E152" s="42"/>
+      <c r="C152" s="37"/>
+      <c r="D152" s="37"/>
+      <c r="E152" s="37"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="42" t="s">
+      <c r="G152" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="H152" s="42"/>
-      <c r="I152" s="42"/>
-      <c r="J152" s="42"/>
-      <c r="K152" s="42"/>
-      <c r="L152" s="42"/>
+      <c r="H152" s="37"/>
+      <c r="I152" s="37"/>
+      <c r="J152" s="37"/>
+      <c r="K152" s="37"/>
+      <c r="L152" s="37"/>
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="1"/>
@@ -4387,117 +4385,117 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" s="1"/>
-      <c r="B156" s="160"/>
-      <c r="C156" s="160"/>
-      <c r="D156" s="160"/>
-      <c r="E156" s="160"/>
-      <c r="F156" s="160"/>
-      <c r="G156" s="160"/>
-      <c r="H156" s="160"/>
-      <c r="I156" s="160"/>
-      <c r="J156" s="160"/>
-      <c r="K156" s="160"/>
-      <c r="L156" s="160"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="30"/>
+      <c r="D156" s="30"/>
+      <c r="E156" s="30"/>
+      <c r="F156" s="30"/>
+      <c r="G156" s="30"/>
+      <c r="H156" s="30"/>
+      <c r="I156" s="30"/>
+      <c r="J156" s="30"/>
+      <c r="K156" s="30"/>
+      <c r="L156" s="30"/>
     </row>
     <row r="157" spans="1:12">
       <c r="A157" s="1"/>
-      <c r="B157" s="160"/>
-      <c r="C157" s="160"/>
-      <c r="D157" s="160"/>
-      <c r="E157" s="160"/>
-      <c r="F157" s="160"/>
-      <c r="G157" s="160"/>
-      <c r="H157" s="160"/>
-      <c r="I157" s="160"/>
-      <c r="J157" s="160"/>
-      <c r="K157" s="160"/>
-      <c r="L157" s="160"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="30"/>
+      <c r="D157" s="30"/>
+      <c r="E157" s="30"/>
+      <c r="F157" s="30"/>
+      <c r="G157" s="30"/>
+      <c r="H157" s="30"/>
+      <c r="I157" s="30"/>
+      <c r="J157" s="30"/>
+      <c r="K157" s="30"/>
+      <c r="L157" s="30"/>
     </row>
     <row r="158" spans="1:12">
       <c r="A158" s="1"/>
-      <c r="B158" s="160"/>
-      <c r="C158" s="160"/>
-      <c r="D158" s="160"/>
-      <c r="E158" s="160"/>
-      <c r="F158" s="160"/>
-      <c r="G158" s="160"/>
-      <c r="H158" s="160"/>
-      <c r="I158" s="160"/>
-      <c r="J158" s="160"/>
-      <c r="K158" s="160"/>
-      <c r="L158" s="160"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="30"/>
+      <c r="D158" s="30"/>
+      <c r="E158" s="30"/>
+      <c r="F158" s="30"/>
+      <c r="G158" s="30"/>
+      <c r="H158" s="30"/>
+      <c r="I158" s="30"/>
+      <c r="J158" s="30"/>
+      <c r="K158" s="30"/>
+      <c r="L158" s="30"/>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" s="1"/>
-      <c r="B159" s="160"/>
-      <c r="C159" s="160"/>
-      <c r="D159" s="160"/>
-      <c r="E159" s="160"/>
-      <c r="F159" s="160"/>
-      <c r="G159" s="160"/>
-      <c r="H159" s="160"/>
-      <c r="I159" s="160"/>
-      <c r="J159" s="160"/>
-      <c r="K159" s="160"/>
-      <c r="L159" s="160"/>
+      <c r="B159" s="30"/>
+      <c r="C159" s="30"/>
+      <c r="D159" s="30"/>
+      <c r="E159" s="30"/>
+      <c r="F159" s="30"/>
+      <c r="G159" s="30"/>
+      <c r="H159" s="30"/>
+      <c r="I159" s="30"/>
+      <c r="J159" s="30"/>
+      <c r="K159" s="30"/>
+      <c r="L159" s="30"/>
     </row>
     <row r="160" spans="1:12">
       <c r="A160" s="1"/>
-      <c r="B160" s="160"/>
-      <c r="C160" s="160"/>
-      <c r="D160" s="160"/>
-      <c r="E160" s="160"/>
-      <c r="F160" s="160"/>
-      <c r="G160" s="160"/>
-      <c r="H160" s="160"/>
-      <c r="I160" s="160"/>
-      <c r="J160" s="160"/>
-      <c r="K160" s="160"/>
-      <c r="L160" s="160"/>
+      <c r="B160" s="30"/>
+      <c r="C160" s="30"/>
+      <c r="D160" s="30"/>
+      <c r="E160" s="30"/>
+      <c r="F160" s="30"/>
+      <c r="G160" s="30"/>
+      <c r="H160" s="30"/>
+      <c r="I160" s="30"/>
+      <c r="J160" s="30"/>
+      <c r="K160" s="30"/>
+      <c r="L160" s="30"/>
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="1"/>
-      <c r="B161" s="160"/>
-      <c r="C161" s="160"/>
-      <c r="D161" s="160"/>
-      <c r="E161" s="160"/>
-      <c r="F161" s="160"/>
-      <c r="G161" s="160"/>
-      <c r="H161" s="160"/>
-      <c r="I161" s="160"/>
-      <c r="J161" s="160"/>
-      <c r="K161" s="160"/>
-      <c r="L161" s="160"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="30"/>
+      <c r="D161" s="30"/>
+      <c r="E161" s="30"/>
+      <c r="F161" s="30"/>
+      <c r="G161" s="30"/>
+      <c r="H161" s="30"/>
+      <c r="I161" s="30"/>
+      <c r="J161" s="30"/>
+      <c r="K161" s="30"/>
+      <c r="L161" s="30"/>
     </row>
     <row r="162" spans="1:12" ht="51" customHeight="1">
       <c r="A162" s="1"/>
-      <c r="B162" s="160"/>
-      <c r="C162" s="160"/>
-      <c r="D162" s="160"/>
-      <c r="E162" s="160"/>
-      <c r="F162" s="160"/>
-      <c r="G162" s="160"/>
-      <c r="H162" s="160"/>
-      <c r="I162" s="160"/>
-      <c r="J162" s="160"/>
-      <c r="K162" s="160"/>
-      <c r="L162" s="160"/>
+      <c r="B162" s="30"/>
+      <c r="C162" s="30"/>
+      <c r="D162" s="30"/>
+      <c r="E162" s="30"/>
+      <c r="F162" s="30"/>
+      <c r="G162" s="30"/>
+      <c r="H162" s="30"/>
+      <c r="I162" s="30"/>
+      <c r="J162" s="30"/>
+      <c r="K162" s="30"/>
+      <c r="L162" s="30"/>
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="1"/>
-      <c r="B163" s="42" t="s">
+      <c r="B163" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C163" s="42"/>
-      <c r="D163" s="2"/>
-      <c r="E163" s="2"/>
+      <c r="C163" s="37"/>
+      <c r="D163" s="37"/>
+      <c r="E163" s="37"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
-      <c r="I163" s="42" t="s">
+      <c r="I163" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="J163" s="42"/>
+      <c r="J163" s="37"/>
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
     </row>
@@ -4559,15 +4557,15 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="1"/>
-      <c r="B168" s="42"/>
-      <c r="C168" s="42"/>
+      <c r="B168" s="37"/>
+      <c r="C168" s="37"/>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
-      <c r="I168" s="42"/>
-      <c r="J168" s="42"/>
+      <c r="I168" s="37"/>
+      <c r="J168" s="37"/>
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
     </row>
@@ -4657,67 +4655,67 @@
     </row>
     <row r="175" spans="1:12">
       <c r="A175" s="1"/>
-      <c r="B175" s="151"/>
-      <c r="C175" s="152"/>
-      <c r="D175" s="151"/>
-      <c r="E175" s="157"/>
-      <c r="F175" s="152"/>
-      <c r="G175" s="151"/>
-      <c r="H175" s="157"/>
-      <c r="I175" s="157"/>
-      <c r="J175" s="152"/>
-      <c r="K175" s="151"/>
-      <c r="L175" s="152"/>
+      <c r="B175" s="55"/>
+      <c r="C175" s="56"/>
+      <c r="D175" s="55"/>
+      <c r="E175" s="61"/>
+      <c r="F175" s="56"/>
+      <c r="G175" s="55"/>
+      <c r="H175" s="61"/>
+      <c r="I175" s="61"/>
+      <c r="J175" s="56"/>
+      <c r="K175" s="55"/>
+      <c r="L175" s="56"/>
     </row>
     <row r="176" spans="1:12">
       <c r="A176" s="1"/>
-      <c r="B176" s="153"/>
-      <c r="C176" s="154"/>
-      <c r="D176" s="153"/>
-      <c r="E176" s="158"/>
-      <c r="F176" s="154"/>
-      <c r="G176" s="153"/>
-      <c r="H176" s="158"/>
-      <c r="I176" s="158"/>
-      <c r="J176" s="154"/>
-      <c r="K176" s="153"/>
-      <c r="L176" s="154"/>
+      <c r="B176" s="57"/>
+      <c r="C176" s="58"/>
+      <c r="D176" s="57"/>
+      <c r="E176" s="62"/>
+      <c r="F176" s="58"/>
+      <c r="G176" s="57"/>
+      <c r="H176" s="62"/>
+      <c r="I176" s="62"/>
+      <c r="J176" s="58"/>
+      <c r="K176" s="57"/>
+      <c r="L176" s="58"/>
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="1"/>
-      <c r="B177" s="155"/>
-      <c r="C177" s="156"/>
-      <c r="D177" s="155"/>
-      <c r="E177" s="159"/>
-      <c r="F177" s="156"/>
-      <c r="G177" s="155"/>
-      <c r="H177" s="159"/>
-      <c r="I177" s="159"/>
-      <c r="J177" s="156"/>
-      <c r="K177" s="155"/>
-      <c r="L177" s="156"/>
+      <c r="B177" s="59"/>
+      <c r="C177" s="60"/>
+      <c r="D177" s="59"/>
+      <c r="E177" s="63"/>
+      <c r="F177" s="60"/>
+      <c r="G177" s="59"/>
+      <c r="H177" s="63"/>
+      <c r="I177" s="63"/>
+      <c r="J177" s="60"/>
+      <c r="K177" s="59"/>
+      <c r="L177" s="60"/>
     </row>
     <row r="178" spans="1:12">
       <c r="A178" s="25"/>
-      <c r="B178" s="139" t="s">
+      <c r="B178" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C178" s="140"/>
-      <c r="D178" s="125" t="s">
+      <c r="C178" s="39"/>
+      <c r="D178" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E178" s="127"/>
-      <c r="F178" s="126"/>
-      <c r="G178" s="144" t="s">
+      <c r="E178" s="41"/>
+      <c r="F178" s="42"/>
+      <c r="G178" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="H178" s="145"/>
-      <c r="I178" s="145"/>
-      <c r="J178" s="146"/>
-      <c r="K178" s="122" t="s">
+      <c r="H178" s="44"/>
+      <c r="I178" s="44"/>
+      <c r="J178" s="45"/>
+      <c r="K178" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="L178" s="124"/>
+      <c r="L178" s="47"/>
     </row>
     <row r="187" spans="1:12" ht="30" customHeight="1"/>
     <row r="188" spans="1:12" ht="30" customHeight="1"/>
@@ -4726,101 +4724,54 @@
     <row r="192" spans="1:12" ht="27" customHeight="1"/>
   </sheetData>
   <mergeCells count="167">
-    <mergeCell ref="B178:C178"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="G178:J178"/>
-    <mergeCell ref="K178:L178"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="B168:C168"/>
-    <mergeCell ref="I168:J168"/>
-    <mergeCell ref="B175:C177"/>
-    <mergeCell ref="D175:F177"/>
-    <mergeCell ref="G175:J177"/>
-    <mergeCell ref="K175:L177"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="B140:L140"/>
-    <mergeCell ref="C135:G135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="J136:L136"/>
-    <mergeCell ref="C137:G137"/>
-    <mergeCell ref="J137:L137"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="K124:L124"/>
-    <mergeCell ref="D132:G132"/>
-    <mergeCell ref="D133:G133"/>
-    <mergeCell ref="B114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="B115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="B121:C123"/>
-    <mergeCell ref="D121:F123"/>
-    <mergeCell ref="G121:J123"/>
-    <mergeCell ref="K121:L123"/>
-    <mergeCell ref="B111:J111"/>
-    <mergeCell ref="K111:L111"/>
-    <mergeCell ref="B112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="B113:J113"/>
-    <mergeCell ref="K113:L113"/>
-    <mergeCell ref="B108:J108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="B109:J109"/>
-    <mergeCell ref="K109:L109"/>
-    <mergeCell ref="B110:J110"/>
-    <mergeCell ref="K110:L110"/>
-    <mergeCell ref="B105:J105"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="B106:J106"/>
-    <mergeCell ref="K106:L106"/>
-    <mergeCell ref="B107:J107"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="B102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="B103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="B104:J104"/>
-    <mergeCell ref="K104:L104"/>
-    <mergeCell ref="B99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="B100:J100"/>
-    <mergeCell ref="K100:L100"/>
-    <mergeCell ref="B101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="B96:J96"/>
-    <mergeCell ref="K96:L96"/>
-    <mergeCell ref="B97:J97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="B98:J98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="B94:J94"/>
-    <mergeCell ref="K94:L94"/>
-    <mergeCell ref="B95:J95"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="B90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="B91:J91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="K92:L92"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="G83:I83"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="G84:I84"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="B93:J93"/>
-    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="B152:E152"/>
+    <mergeCell ref="G152:L152"/>
+    <mergeCell ref="D32:L32"/>
+    <mergeCell ref="B33:L33"/>
+    <mergeCell ref="B116:J119"/>
+    <mergeCell ref="K116:L119"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="B24:L24"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B36:L46"/>
+    <mergeCell ref="E48:L48"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="C8:L8"/>
+    <mergeCell ref="C9:L10"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="B57:C59"/>
+    <mergeCell ref="D57:F59"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="G56:J56"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="G55:J55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="B31:L31"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="L17:L18"/>
     <mergeCell ref="B53:L53"/>
     <mergeCell ref="B54:C54"/>
     <mergeCell ref="D54:F54"/>
@@ -4845,54 +4796,101 @@
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="G60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="C8:L8"/>
-    <mergeCell ref="C9:L10"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="B57:C59"/>
-    <mergeCell ref="D57:F59"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="G56:J56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="G55:J55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="C30:L30"/>
-    <mergeCell ref="B31:L31"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B152:E152"/>
-    <mergeCell ref="G152:L152"/>
-    <mergeCell ref="D32:L32"/>
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="B116:J119"/>
-    <mergeCell ref="K116:L119"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="B24:L24"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="B36:L46"/>
-    <mergeCell ref="E48:L48"/>
-    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="G83:I83"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="B93:J93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="B94:J94"/>
+    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="B95:J95"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="B90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="B91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="B99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="B100:J100"/>
+    <mergeCell ref="K100:L100"/>
+    <mergeCell ref="B101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="B96:J96"/>
+    <mergeCell ref="K96:L96"/>
+    <mergeCell ref="B97:J97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="B98:J98"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="B105:J105"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="B106:J106"/>
+    <mergeCell ref="K106:L106"/>
+    <mergeCell ref="B107:J107"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="B102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="B103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="K104:L104"/>
+    <mergeCell ref="B111:J111"/>
+    <mergeCell ref="K111:L111"/>
+    <mergeCell ref="B112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="B113:J113"/>
+    <mergeCell ref="K113:L113"/>
+    <mergeCell ref="B108:J108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="B109:J109"/>
+    <mergeCell ref="K109:L109"/>
+    <mergeCell ref="B110:J110"/>
+    <mergeCell ref="K110:L110"/>
+    <mergeCell ref="J137:L137"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="K124:L124"/>
+    <mergeCell ref="D132:G132"/>
+    <mergeCell ref="D133:G133"/>
+    <mergeCell ref="B114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="B115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="B121:C123"/>
+    <mergeCell ref="D121:F123"/>
+    <mergeCell ref="G121:J123"/>
+    <mergeCell ref="K121:L123"/>
+    <mergeCell ref="B163:E163"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="D178:F178"/>
+    <mergeCell ref="G178:J178"/>
+    <mergeCell ref="K178:L178"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="I168:J168"/>
+    <mergeCell ref="B175:C177"/>
+    <mergeCell ref="D175:F177"/>
+    <mergeCell ref="G175:J177"/>
+    <mergeCell ref="K175:L177"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="B140:L140"/>
+    <mergeCell ref="C135:G135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="J136:L136"/>
+    <mergeCell ref="C137:G137"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>

--- a/templates/Plantilla_Preventivo.xlsx
+++ b/templates/Plantilla_Preventivo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49B8F7F2-E031-4701-ACFD-FCC09E7FBB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7971BA34-0A84-4A28-B921-EB0E7B45B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3099,7 +3099,7 @@
       <c r="K59" s="112"/>
       <c r="L59" s="113"/>
     </row>
-    <row r="60" spans="1:12" s="34" customFormat="1" ht="90.75" customHeight="1">
+    <row r="60" spans="1:12" s="34" customFormat="1" ht="95.25" customHeight="1">
       <c r="A60" s="33"/>
       <c r="B60" s="40" t="s">
         <v>31</v>
@@ -3121,9 +3121,9 @@
       </c>
       <c r="L60" s="119"/>
     </row>
-    <row r="61" spans="1:12" ht="15" customHeight="1"/>
-    <row r="62" spans="1:12" ht="27" customHeight="1"/>
-    <row r="63" spans="1:12" ht="27" customHeight="1"/>
+    <row r="61" spans="1:12" ht="30" customHeight="1"/>
+    <row r="62" spans="1:12" ht="30" customHeight="1"/>
+    <row r="63" spans="1:12" ht="30" customHeight="1"/>
     <row r="64" spans="1:12" ht="15" customHeight="1"/>
     <row r="65" spans="1:12" ht="33" customHeight="1"/>
     <row r="66" spans="1:12" ht="15" customHeight="1"/>
@@ -3998,7 +3998,7 @@
       <c r="K123" s="94"/>
       <c r="L123" s="96"/>
     </row>
-    <row r="124" spans="1:12" s="31" customFormat="1" ht="47.25" customHeight="1">
+    <row r="124" spans="1:12" s="31" customFormat="1" ht="50.25" customHeight="1">
       <c r="A124" s="25"/>
       <c r="B124" s="38" t="s">
         <v>31</v>
@@ -4020,8 +4020,9 @@
       </c>
       <c r="L124" s="42"/>
     </row>
-    <row r="126" spans="1:12" ht="27" customHeight="1"/>
-    <row r="127" spans="1:12" ht="27" customHeight="1"/>
+    <row r="125" spans="1:12" ht="30" customHeight="1"/>
+    <row r="126" spans="1:12" ht="30" customHeight="1"/>
+    <row r="127" spans="1:12" ht="30" customHeight="1"/>
     <row r="128" spans="1:12" ht="15" customHeight="1"/>
     <row r="129" spans="1:12" ht="33" customHeight="1"/>
     <row r="130" spans="1:12" ht="15" customHeight="1"/>
@@ -4719,9 +4720,9 @@
     </row>
     <row r="187" spans="1:12" ht="30" customHeight="1"/>
     <row r="188" spans="1:12" ht="30" customHeight="1"/>
-    <row r="190" spans="1:12" ht="15" customHeight="1"/>
+    <row r="190" spans="1:12" ht="30" customHeight="1"/>
     <row r="191" spans="1:12" ht="30" customHeight="1"/>
-    <row r="192" spans="1:12" ht="27" customHeight="1"/>
+    <row r="192" spans="1:12" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="167">
     <mergeCell ref="J17:J18"/>
